--- a/products-storage/10-avans-usloviya-i-pribyl/02-kalkulyator-usloviy-avansa.xlsx
+++ b/products-storage/10-avans-usloviya-i-pribyl/02-kalkulyator-usloviy-avansa.xlsx
@@ -1,21 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Условия" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="График КС" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Профиль А" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Профиль Б" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Сравнение" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Как читать" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Пример заполнения" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Условия" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="График КС" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Профиль А" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Профиль Б" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сравнение" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Как читать" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Пример заполнения" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'График КС'!$A$1:$D$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Профиль А'!$A$1:$P$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Профиль Б'!$A$1:$P$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Сравнение'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Пример заполнения'!$A$1:$D$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Условия'!$A$1:$D$38</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Условия'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'График КС'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Профиль А'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Профиль Б'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Как читать'!$A$1:$B$21</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -116,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,6 +174,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -545,7 +560,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -566,7 +581,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Заполните жёлтые ячейки в двух колонках. Синим — то, что вводите вы; чёрным — то, что считают формулы. Сценарий А — условия, которые вам предлагают. Сценарий Б — условия, которые вы просите. Разницу между ними покажет лист «Сравнение»: она и есть предмет переговоров.</t>
+          <t xml:space="preserve">Заполните исходные условия в сценариях А и Б по договору, графику работ и предложению банка. В сценарии А укажите предложенные условия, в Б — вариант для согласования. Сопоставьте результаты на листе «Сравнение».</t>
         </is>
       </c>
     </row>
@@ -588,7 +603,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Что это и откуда взять</t>
+          <t xml:space="preserve">Содержание показателя и источник данных</t>
         </is>
       </c>
     </row>
@@ -602,7 +617,7 @@
       <c r="C5" s="5" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Цена работ по вашему договору субподряда. С НДС или без — как угодно, важно одно: все поля этого листа в одной базе.</t>
+          <t xml:space="preserve">Цена договора. Используйте единый порядок учёта НДС во всех исходных суммах и расходах.</t>
         </is>
       </c>
     </row>
@@ -616,7 +631,7 @@
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Сколько процентов цены выплачивается авансом. Нулевой аванс — это тоже сценарий, и его полезно посчитать: он показывает цену вопроса целиком.</t>
+          <t xml:space="preserve">Доля цены договора, выплачиваемая авансом. Для оценки потребности в финансировании рассмотрите также сценарий без аванса.</t>
         </is>
       </c>
     </row>
@@ -630,7 +645,7 @@
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Номер месяца от старта объекта, в котором деньги реально приходят на счёт, а не в котором подписан договор. Разница обычно и есть месяц-два своих денег.</t>
+          <t xml:space="preserve">Порядковый месяц фактического поступления аванса, считая от начала расчётного периода.</t>
         </is>
       </c>
     </row>
@@ -644,7 +659,7 @@
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Выберите из списка одно из трёх значений. Список — внизу этого листа.</t>
+          <t xml:space="preserve">Выберите предусмотренный договором порядок погашения из справочника этого листа.</t>
         </is>
       </c>
     </row>
@@ -672,7 +687,7 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Банковская гарантия или страхование возврата аванса. Ставку берите из предложения банка или страховщика на сегодня. Если обеспечение не требуется — 0.</t>
+          <t xml:space="preserve">Годовая ставка комиссии за обеспечение по предложению банка или страховщика на дату расчёта. При отсутствии обеспечения укажите 0.</t>
         </is>
       </c>
     </row>
@@ -686,7 +701,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Из требования генподрядчика: обычно срок объекта плюс запас. Ставка годовая, поэтому длина срока прямо умножает стоимость.</t>
+          <t xml:space="preserve">Срок действия обеспечения по договору и условиям банка, в месяцах.</t>
         </is>
       </c>
     </row>
@@ -700,7 +715,7 @@
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Комиссия чаще всего платится вперёд, до выдачи аванса. Поставьте месяц, в котором вы её фактически платите.</t>
+          <t xml:space="preserve">Порядковый месяц фактической оплаты комиссии за обеспечение.</t>
         </is>
       </c>
     </row>
@@ -714,7 +729,7 @@
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Сколько генподрядчик удерживает из каждого акта. Удержание вычитается из той же КС, из которой гасится аванс: два изъятия из одного платежа складываются.</t>
+          <t xml:space="preserve">Доля стоимости каждого акта, удерживаемая в качестве гарантийного обеспечения. Рассматривается совместно с погашением аванса.</t>
         </is>
       </c>
     </row>
@@ -728,7 +743,7 @@
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Из договора. Если возврат наступает за пределами горизонта расчёта — поставьте 0, и удержанные деньги останутся замороженными до конца расчёта.</t>
+          <t xml:space="preserve">Месяц возврата удержания по договору. Значение 0 означает отсутствие возврата в пределах 36 месяцев расчёта.</t>
         </is>
       </c>
     </row>
@@ -742,7 +757,7 @@
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Если договор возвращает удержание частями, укажите долю той части, которая приходит в указанный месяц.</t>
+          <t xml:space="preserve">Доля удержания, возвращаемая в указанном месяце. Остальная часть сохраняется в расчёте как невозвращённая.</t>
         </is>
       </c>
     </row>
@@ -770,7 +785,7 @@
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Сколько месяцев проходит от подписания акта до денег на счёте. Это поле двигает кассу сильнее размера аванса — проверьте его в договоре, а не по памяти.</t>
+          <t xml:space="preserve">Количество месяцев между подписанием акта и поступлением оплаты, предусмотренное договором.</t>
         </is>
       </c>
     </row>
@@ -784,7 +799,7 @@
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Ваши прямые затраты на выполнение: материалы, люди, техника, без прибыли и накладных, если вы их не считаете здесь.</t>
+          <t xml:space="preserve">Доля расходов на выполнение работ в цене договора. Включите учитываемые в расчёте материалы, оплату труда, эксплуатацию техники и иные расходы.</t>
         </is>
       </c>
     </row>
@@ -798,7 +813,7 @@
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>На сколько месяцев затраты идут впереди выполнения: закупка, завоз, мобилизация. Ради этого опережения аванс и берут.</t>
+          <t xml:space="preserve">Количество месяцев между несением расходов и соответствующим выполнением работ: закупка, доставка и мобилизация.</t>
         </is>
       </c>
     </row>
@@ -812,14 +827,14 @@
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Мобилизация, бытовки, залоги, первый завоз — то, что тратится до первого акта.</t>
+          <t xml:space="preserve">Расходы до первого акта: мобилизация, временные сооружения, обеспечительные платежи и первоначальная поставка.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Считается по введённому</t>
+          <t xml:space="preserve">Расчётные показатели</t>
         </is>
       </c>
     </row>
@@ -875,12 +890,10 @@
         </is>
       </c>
       <c r="B26" s="13">
-        <f>IF('Условия'!$B$5="","Не заполнена сумма договора",IF('Условия'!$B$25=0,"Порядок погашения не выбран из списка",IF(AND('Условия'!$B$25=3,'Условия'!$B$9=""),"Для порядка с отсрочкой укажите долю выполнения",IF('Условия'!$B$16="","Не заполнен срок объекта",IF('Условия'!$B$10&gt;0,"Условия заполнены. Обеспечение платное — его стоимость уже вычтена из кассы","Условия заполнены")))))</f>
-        <v/>
+        <f>IF('Условия'!$B$5="","Не заполнена сумма договора",IF('Условия'!$B$25=0,"Порядок погашения не выбран из списка",IF(AND('Условия'!$B$25=3,'Условия'!$B$9=""),"Для порядка с отсрочкой укажите долю выполнения",IF('Условия'!$B$16="","Не заполнен срок объекта",IF('Условия'!$B$10&gt;0,"Условия заполнены. Стоимость обеспечения учтена в денежных расходах.","Условия заполнены")))))</f>
       </c>
       <c r="C26" s="13">
-        <f>IF('Условия'!$C$5="","Не заполнена сумма договора",IF('Условия'!$C$25=0,"Порядок погашения не выбран из списка",IF(AND('Условия'!$C$25=3,'Условия'!$C$9=""),"Для порядка с отсрочкой укажите долю выполнения",IF('Условия'!$C$16="","Не заполнен срок объекта",IF('Условия'!$C$10&gt;0,"Условия заполнены. Обеспечение платное — его стоимость уже вычтена из кассы","Условия заполнены")))))</f>
-        <v/>
+        <f>IF('Условия'!$C$5="","Не заполнена сумма договора",IF('Условия'!$C$25=0,"Порядок погашения не выбран из списка",IF(AND('Условия'!$C$25=3,'Условия'!$C$9=""),"Для порядка с отсрочкой укажите долю выполнения",IF('Условия'!$C$16="","Не заполнен срок объекта",IF('Условия'!$C$10&gt;0,"Условия заполнены. Стоимость обеспечения учтена в денежных расходах.","Условия заполнены")))))</f>
       </c>
     </row>
     <row r="28">
@@ -901,11 +914,11 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Погашение равными долями от каждой КС: удержали процент — и дальше по тому же проценту.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
+          <t xml:space="preserve">Из стоимости каждого акта погашается согласованная доля аванса.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24.0" customHeight="1">
       <c r="A30" s="14" t="inlineStr">
         <is>
           <t>единовременно из последней КС</t>
@@ -916,11 +929,11 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Весь аванс удерживается из последнего акта. До него касса выглядит лучше, в конце — резко хуже.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
+          <t xml:space="preserve">Аванс погашается из стоимости последнего акта. Проверьте остаток к оплате в соответствующем месяце.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24.0" customHeight="1">
       <c r="A31" s="14" t="inlineStr">
         <is>
           <t>с отсрочкой до доли выполнения</t>
@@ -931,35 +944,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Погашение не начинается, пока не выполнена указанная доля; дальше догоняет на оставшемся объёме.</t>
+          <t xml:space="preserve">Погашение начинается после достижения указанной доли выполнения и распределяется на оставшийся объём.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Чего в этом файле нет намеренно</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1">
+          <t>Проверка исходных ставок и сроков</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Ни одной ставки и ни одного срока законодательства числом. Ставка обеспечения, гарантийное удержание, отсрочка оплаты, сроки — всё вводится вами из вашего договора и предложения банка на дату расчёта. Зашитое число в скачанном файле опаснее его отсутствия: файл выглядит готовым и даёт неверную цифру, с которой вы пойдёте на переговоры.</t>
+          <t>Введите ставку обеспечения, сроки оплаты и гарантийное удержание из договора и банковского предложения на дату расчёта. Сверьте оба сценария.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Важно, прочитайте до использования</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="92" customHeight="1">
+          <t>Контроль условий перед переговорами</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Это расчётный и переговорный инструмент, а не юридическая консультация и не гарантия того, что условия аванса удастся изменить. Генподрядчик вправе не согласиться ни на один пункт: файл даёт аргумент и цифру, а не рычаг. Расчёт рассчитан на типовую ситуацию: договор обсуждается либо уже подписан, спора о выполненных объёмах и качестве нет. Сюда не применять: возврат неотработанного аванса при расторжении, требование генподрядчика вернуть аванс, зачёт, дело о банкротстве генподрядчика, налоговые последствия аванса — НДС и момент признания дохода. Это не расчёт, а спор или учёт: там нужен юрист или бухгалтер, а не таблица.</t>
+          <t>Сверьте введённые условия с договором, графиком платежей и стоимостью обеспечения. Сравните сценарии по максимальному дефициту и месяцу его возникновения.</t>
         </is>
       </c>
     </row>
@@ -971,11 +984,12 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B8 C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Значение не из списка" error="Выберите один из трёх порядков погашения из списка внизу листа «Условия»." type="list">
+    <dataValidation sqref="B8 C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Значение не из списка" error="Выберите один из трёх порядков погашения из списка внизу листа «Условия»." type="list">
       <formula1>='Условия'!$A$29:$A$31</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
@@ -984,7 +998,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -995,10 +1009,10 @@
     <col width="56" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>График КС: сколько процентов объёма закрывается в каждом месяце</t>
+          <t xml:space="preserve">Помесячное распределение стоимости выполненных работ</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1441,7 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="42" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Итого</t>
@@ -1441,15 +1455,14 @@
         <f>ROUND(SUM($C$5:$C$40),4)</f>
         <v/>
       </c>
-      <c r="D42" s="18">
-        <f>IF(AND(ROUND($B42,2)=100,ROUND($C42,2)=100),"Оба графика закрывают 100% объёма","Сумма долей не равна 100: расчёт закроет не весь договор")</f>
-        <v/>
+      <c r="D42" s="31">
+        <f>IF(AND(ROUND($B42,2)=100,ROUND($C42,2)=100),"Сумма долей выполнения в каждом сценарии составляет 100%.","Сумма долей выполнения отличается от 100%: проверьте полноту графика.")</f>
       </c>
     </row>
     <row r="44" ht="46" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Горизонт расчёта — 36 месяцев. Если объект длиннее, укрупните шаг: считайте два месяца одной строкой. Если после расчёта на листе «Сравнение» строка «Начислено, но не поступило» больше нуля — деньги за последние акты приходят за горизонтом, и график стоит сдвинуть на несколько месяцев к началу.</t>
+          <t xml:space="preserve">Горизонт расчёта составляет 36 месяцев с месячным шагом. Для более длительного проекта подготовьте отдельный график с соответствующим горизонтом. Единицу периода в данном расчёте сохраняйте. Остаток «Начислено, но не поступило» сопоставьте с договорными датами платежей после окончания расчёта.</t>
         </is>
       </c>
     </row>
@@ -1459,6 +1472,7 @@
     <mergeCell ref="A44:D44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1466,7 +1480,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1499,7 +1513,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Здесь не заполняется ничего: всё считается из листов «Условия» и «График КС». Читать слева направо: сколько выполнено, сколько из этого удержали, сколько дошло до счёта, сколько потрачено и что осталось накопленным итогом. Колонка «Накопленный остаток» — это и есть ваши деньги в объекте: минус в ней означает, что объект финансируется вами.</t>
+          <t xml:space="preserve">Расчёт по листам «Условия» и «График КС»: выполненные работы, погашение аванса, удержание, поступления и расходы. Отрицательный накопленный остаток показывает потребность в собственном или привлечённом финансировании.</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1590,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Месяц в минусе</t>
+          <t xml:space="preserve">Отрицательный остаток</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -1646,8 +1660,7 @@
         <v/>
       </c>
       <c r="P5" s="13">
-        <f>IF($H5&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B5&gt;0,'Условия'!$B$16&lt;&gt;"",$A5&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H5&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B5&gt;0,'Условия'!$B$16&lt;&gt;"",$A5&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="6">
@@ -1711,8 +1724,7 @@
         <v/>
       </c>
       <c r="P6" s="13">
-        <f>IF($H6&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B6&gt;0,'Условия'!$B$16&lt;&gt;"",$A6&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H6&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B6&gt;0,'Условия'!$B$16&lt;&gt;"",$A6&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="7">
@@ -1776,8 +1788,7 @@
         <v/>
       </c>
       <c r="P7" s="13">
-        <f>IF($H7&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B7&gt;0,'Условия'!$B$16&lt;&gt;"",$A7&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H7&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B7&gt;0,'Условия'!$B$16&lt;&gt;"",$A7&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="8">
@@ -1841,8 +1852,7 @@
         <v/>
       </c>
       <c r="P8" s="13">
-        <f>IF($H8&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B8&gt;0,'Условия'!$B$16&lt;&gt;"",$A8&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H8&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B8&gt;0,'Условия'!$B$16&lt;&gt;"",$A8&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="9">
@@ -1906,8 +1916,7 @@
         <v/>
       </c>
       <c r="P9" s="13">
-        <f>IF($H9&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B9&gt;0,'Условия'!$B$16&lt;&gt;"",$A9&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H9&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B9&gt;0,'Условия'!$B$16&lt;&gt;"",$A9&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="10">
@@ -1971,8 +1980,7 @@
         <v/>
       </c>
       <c r="P10" s="13">
-        <f>IF($H10&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B10&gt;0,'Условия'!$B$16&lt;&gt;"",$A10&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H10&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B10&gt;0,'Условия'!$B$16&lt;&gt;"",$A10&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="11">
@@ -2036,8 +2044,7 @@
         <v/>
       </c>
       <c r="P11" s="13">
-        <f>IF($H11&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B11&gt;0,'Условия'!$B$16&lt;&gt;"",$A11&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H11&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B11&gt;0,'Условия'!$B$16&lt;&gt;"",$A11&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="12">
@@ -2101,8 +2108,7 @@
         <v/>
       </c>
       <c r="P12" s="13">
-        <f>IF($H12&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B12&gt;0,'Условия'!$B$16&lt;&gt;"",$A12&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H12&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B12&gt;0,'Условия'!$B$16&lt;&gt;"",$A12&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="13">
@@ -2166,8 +2172,7 @@
         <v/>
       </c>
       <c r="P13" s="13">
-        <f>IF($H13&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B13&gt;0,'Условия'!$B$16&lt;&gt;"",$A13&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H13&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B13&gt;0,'Условия'!$B$16&lt;&gt;"",$A13&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="14">
@@ -2231,8 +2236,7 @@
         <v/>
       </c>
       <c r="P14" s="13">
-        <f>IF($H14&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B14&gt;0,'Условия'!$B$16&lt;&gt;"",$A14&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H14&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B14&gt;0,'Условия'!$B$16&lt;&gt;"",$A14&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="15">
@@ -2296,8 +2300,7 @@
         <v/>
       </c>
       <c r="P15" s="13">
-        <f>IF($H15&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B15&gt;0,'Условия'!$B$16&lt;&gt;"",$A15&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H15&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B15&gt;0,'Условия'!$B$16&lt;&gt;"",$A15&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="16">
@@ -2361,8 +2364,7 @@
         <v/>
       </c>
       <c r="P16" s="13">
-        <f>IF($H16&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B16&gt;0,'Условия'!$B$16&lt;&gt;"",$A16&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H16&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B16&gt;0,'Условия'!$B$16&lt;&gt;"",$A16&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="17">
@@ -2426,8 +2428,7 @@
         <v/>
       </c>
       <c r="P17" s="13">
-        <f>IF($H17&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B17&gt;0,'Условия'!$B$16&lt;&gt;"",$A17&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H17&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B17&gt;0,'Условия'!$B$16&lt;&gt;"",$A17&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="18">
@@ -2491,8 +2492,7 @@
         <v/>
       </c>
       <c r="P18" s="13">
-        <f>IF($H18&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B18&gt;0,'Условия'!$B$16&lt;&gt;"",$A18&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H18&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B18&gt;0,'Условия'!$B$16&lt;&gt;"",$A18&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="19">
@@ -2556,8 +2556,7 @@
         <v/>
       </c>
       <c r="P19" s="13">
-        <f>IF($H19&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B19&gt;0,'Условия'!$B$16&lt;&gt;"",$A19&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H19&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B19&gt;0,'Условия'!$B$16&lt;&gt;"",$A19&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="20">
@@ -2621,8 +2620,7 @@
         <v/>
       </c>
       <c r="P20" s="13">
-        <f>IF($H20&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B20&gt;0,'Условия'!$B$16&lt;&gt;"",$A20&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H20&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B20&gt;0,'Условия'!$B$16&lt;&gt;"",$A20&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="21">
@@ -2686,8 +2684,7 @@
         <v/>
       </c>
       <c r="P21" s="13">
-        <f>IF($H21&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B21&gt;0,'Условия'!$B$16&lt;&gt;"",$A21&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H21&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B21&gt;0,'Условия'!$B$16&lt;&gt;"",$A21&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="22">
@@ -2751,8 +2748,7 @@
         <v/>
       </c>
       <c r="P22" s="13">
-        <f>IF($H22&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B22&gt;0,'Условия'!$B$16&lt;&gt;"",$A22&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H22&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B22&gt;0,'Условия'!$B$16&lt;&gt;"",$A22&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="23">
@@ -2816,8 +2812,7 @@
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IF($H23&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B23&gt;0,'Условия'!$B$16&lt;&gt;"",$A23&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H23&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B23&gt;0,'Условия'!$B$16&lt;&gt;"",$A23&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="24">
@@ -2881,8 +2876,7 @@
         <v/>
       </c>
       <c r="P24" s="13">
-        <f>IF($H24&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B24&gt;0,'Условия'!$B$16&lt;&gt;"",$A24&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H24&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B24&gt;0,'Условия'!$B$16&lt;&gt;"",$A24&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="25">
@@ -2946,8 +2940,7 @@
         <v/>
       </c>
       <c r="P25" s="13">
-        <f>IF($H25&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B25&gt;0,'Условия'!$B$16&lt;&gt;"",$A25&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H25&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B25&gt;0,'Условия'!$B$16&lt;&gt;"",$A25&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="26">
@@ -3011,8 +3004,7 @@
         <v/>
       </c>
       <c r="P26" s="13">
-        <f>IF($H26&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B26&gt;0,'Условия'!$B$16&lt;&gt;"",$A26&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H26&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B26&gt;0,'Условия'!$B$16&lt;&gt;"",$A26&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="27">
@@ -3076,8 +3068,7 @@
         <v/>
       </c>
       <c r="P27" s="13">
-        <f>IF($H27&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B27&gt;0,'Условия'!$B$16&lt;&gt;"",$A27&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H27&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B27&gt;0,'Условия'!$B$16&lt;&gt;"",$A27&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="28">
@@ -3141,8 +3132,7 @@
         <v/>
       </c>
       <c r="P28" s="13">
-        <f>IF($H28&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B28&gt;0,'Условия'!$B$16&lt;&gt;"",$A28&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H28&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B28&gt;0,'Условия'!$B$16&lt;&gt;"",$A28&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="29">
@@ -3206,8 +3196,7 @@
         <v/>
       </c>
       <c r="P29" s="13">
-        <f>IF($H29&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B29&gt;0,'Условия'!$B$16&lt;&gt;"",$A29&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H29&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B29&gt;0,'Условия'!$B$16&lt;&gt;"",$A29&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="30">
@@ -3271,8 +3260,7 @@
         <v/>
       </c>
       <c r="P30" s="13">
-        <f>IF($H30&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B30&gt;0,'Условия'!$B$16&lt;&gt;"",$A30&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H30&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B30&gt;0,'Условия'!$B$16&lt;&gt;"",$A30&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="31">
@@ -3336,8 +3324,7 @@
         <v/>
       </c>
       <c r="P31" s="13">
-        <f>IF($H31&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B31&gt;0,'Условия'!$B$16&lt;&gt;"",$A31&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H31&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B31&gt;0,'Условия'!$B$16&lt;&gt;"",$A31&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="32">
@@ -3401,8 +3388,7 @@
         <v/>
       </c>
       <c r="P32" s="13">
-        <f>IF($H32&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B32&gt;0,'Условия'!$B$16&lt;&gt;"",$A32&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H32&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B32&gt;0,'Условия'!$B$16&lt;&gt;"",$A32&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="33">
@@ -3466,8 +3452,7 @@
         <v/>
       </c>
       <c r="P33" s="13">
-        <f>IF($H33&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B33&gt;0,'Условия'!$B$16&lt;&gt;"",$A33&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H33&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B33&gt;0,'Условия'!$B$16&lt;&gt;"",$A33&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="34">
@@ -3531,8 +3516,7 @@
         <v/>
       </c>
       <c r="P34" s="13">
-        <f>IF($H34&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B34&gt;0,'Условия'!$B$16&lt;&gt;"",$A34&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H34&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B34&gt;0,'Условия'!$B$16&lt;&gt;"",$A34&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="35">
@@ -3596,8 +3580,7 @@
         <v/>
       </c>
       <c r="P35" s="13">
-        <f>IF($H35&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B35&gt;0,'Условия'!$B$16&lt;&gt;"",$A35&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H35&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B35&gt;0,'Условия'!$B$16&lt;&gt;"",$A35&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="36">
@@ -3661,8 +3644,7 @@
         <v/>
       </c>
       <c r="P36" s="13">
-        <f>IF($H36&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B36&gt;0,'Условия'!$B$16&lt;&gt;"",$A36&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H36&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B36&gt;0,'Условия'!$B$16&lt;&gt;"",$A36&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="37">
@@ -3726,8 +3708,7 @@
         <v/>
       </c>
       <c r="P37" s="13">
-        <f>IF($H37&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B37&gt;0,'Условия'!$B$16&lt;&gt;"",$A37&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H37&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B37&gt;0,'Условия'!$B$16&lt;&gt;"",$A37&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="38">
@@ -3791,8 +3772,7 @@
         <v/>
       </c>
       <c r="P38" s="13">
-        <f>IF($H38&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B38&gt;0,'Условия'!$B$16&lt;&gt;"",$A38&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H38&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B38&gt;0,'Условия'!$B$16&lt;&gt;"",$A38&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="39">
@@ -3856,8 +3836,7 @@
         <v/>
       </c>
       <c r="P39" s="13">
-        <f>IF($H39&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B39&gt;0,'Условия'!$B$16&lt;&gt;"",$A39&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H39&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B39&gt;0,'Условия'!$B$16&lt;&gt;"",$A39&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="40">
@@ -3921,8 +3900,7 @@
         <v/>
       </c>
       <c r="P40" s="13">
-        <f>IF($H40&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B40&gt;0,'Условия'!$B$16&lt;&gt;"",$A40&gt;'Условия'!$B$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H40&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B40&gt;0,'Условия'!$B$16&lt;&gt;"",$A40&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="42">
@@ -3982,6 +3960,7 @@
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3989,7 +3968,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4022,7 +4001,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Здесь не заполняется ничего: всё считается из листов «Условия» и «График КС». Читать слева направо: сколько выполнено, сколько из этого удержали, сколько дошло до счёта, сколько потрачено и что осталось накопленным итогом. Колонка «Накопленный остаток» — это и есть ваши деньги в объекте: минус в ней означает, что объект финансируется вами.</t>
+          <t xml:space="preserve">Расчёт по листам «Условия» и «График КС»: выполненные работы, погашение аванса, удержание, поступления и расходы. Отрицательный накопленный остаток показывает потребность в собственном или привлечённом финансировании.</t>
         </is>
       </c>
     </row>
@@ -4099,7 +4078,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Месяц в минусе</t>
+          <t xml:space="preserve">Отрицательный остаток</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
@@ -4169,8 +4148,7 @@
         <v/>
       </c>
       <c r="P5" s="13">
-        <f>IF($H5&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B5&gt;0,'Условия'!$C$16&lt;&gt;"",$A5&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H5&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B5&gt;0,'Условия'!$C$16&lt;&gt;"",$A5&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="6">
@@ -4234,8 +4212,7 @@
         <v/>
       </c>
       <c r="P6" s="13">
-        <f>IF($H6&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B6&gt;0,'Условия'!$C$16&lt;&gt;"",$A6&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H6&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B6&gt;0,'Условия'!$C$16&lt;&gt;"",$A6&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="7">
@@ -4299,8 +4276,7 @@
         <v/>
       </c>
       <c r="P7" s="13">
-        <f>IF($H7&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B7&gt;0,'Условия'!$C$16&lt;&gt;"",$A7&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H7&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B7&gt;0,'Условия'!$C$16&lt;&gt;"",$A7&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="8">
@@ -4364,8 +4340,7 @@
         <v/>
       </c>
       <c r="P8" s="13">
-        <f>IF($H8&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B8&gt;0,'Условия'!$C$16&lt;&gt;"",$A8&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H8&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B8&gt;0,'Условия'!$C$16&lt;&gt;"",$A8&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="9">
@@ -4429,8 +4404,7 @@
         <v/>
       </c>
       <c r="P9" s="13">
-        <f>IF($H9&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B9&gt;0,'Условия'!$C$16&lt;&gt;"",$A9&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H9&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B9&gt;0,'Условия'!$C$16&lt;&gt;"",$A9&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="10">
@@ -4494,8 +4468,7 @@
         <v/>
       </c>
       <c r="P10" s="13">
-        <f>IF($H10&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B10&gt;0,'Условия'!$C$16&lt;&gt;"",$A10&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H10&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B10&gt;0,'Условия'!$C$16&lt;&gt;"",$A10&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="11">
@@ -4559,8 +4532,7 @@
         <v/>
       </c>
       <c r="P11" s="13">
-        <f>IF($H11&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B11&gt;0,'Условия'!$C$16&lt;&gt;"",$A11&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H11&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B11&gt;0,'Условия'!$C$16&lt;&gt;"",$A11&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="12">
@@ -4624,8 +4596,7 @@
         <v/>
       </c>
       <c r="P12" s="13">
-        <f>IF($H12&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B12&gt;0,'Условия'!$C$16&lt;&gt;"",$A12&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H12&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B12&gt;0,'Условия'!$C$16&lt;&gt;"",$A12&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="13">
@@ -4689,8 +4660,7 @@
         <v/>
       </c>
       <c r="P13" s="13">
-        <f>IF($H13&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B13&gt;0,'Условия'!$C$16&lt;&gt;"",$A13&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H13&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B13&gt;0,'Условия'!$C$16&lt;&gt;"",$A13&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="14">
@@ -4754,8 +4724,7 @@
         <v/>
       </c>
       <c r="P14" s="13">
-        <f>IF($H14&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B14&gt;0,'Условия'!$C$16&lt;&gt;"",$A14&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H14&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B14&gt;0,'Условия'!$C$16&lt;&gt;"",$A14&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="15">
@@ -4819,8 +4788,7 @@
         <v/>
       </c>
       <c r="P15" s="13">
-        <f>IF($H15&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B15&gt;0,'Условия'!$C$16&lt;&gt;"",$A15&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H15&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B15&gt;0,'Условия'!$C$16&lt;&gt;"",$A15&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="16">
@@ -4884,8 +4852,7 @@
         <v/>
       </c>
       <c r="P16" s="13">
-        <f>IF($H16&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B16&gt;0,'Условия'!$C$16&lt;&gt;"",$A16&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H16&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B16&gt;0,'Условия'!$C$16&lt;&gt;"",$A16&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="17">
@@ -4949,8 +4916,7 @@
         <v/>
       </c>
       <c r="P17" s="13">
-        <f>IF($H17&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B17&gt;0,'Условия'!$C$16&lt;&gt;"",$A17&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H17&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B17&gt;0,'Условия'!$C$16&lt;&gt;"",$A17&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="18">
@@ -5014,8 +4980,7 @@
         <v/>
       </c>
       <c r="P18" s="13">
-        <f>IF($H18&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B18&gt;0,'Условия'!$C$16&lt;&gt;"",$A18&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H18&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B18&gt;0,'Условия'!$C$16&lt;&gt;"",$A18&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="19">
@@ -5079,8 +5044,7 @@
         <v/>
       </c>
       <c r="P19" s="13">
-        <f>IF($H19&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B19&gt;0,'Условия'!$C$16&lt;&gt;"",$A19&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H19&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B19&gt;0,'Условия'!$C$16&lt;&gt;"",$A19&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="20">
@@ -5144,8 +5108,7 @@
         <v/>
       </c>
       <c r="P20" s="13">
-        <f>IF($H20&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B20&gt;0,'Условия'!$C$16&lt;&gt;"",$A20&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H20&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B20&gt;0,'Условия'!$C$16&lt;&gt;"",$A20&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="21">
@@ -5209,8 +5172,7 @@
         <v/>
       </c>
       <c r="P21" s="13">
-        <f>IF($H21&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B21&gt;0,'Условия'!$C$16&lt;&gt;"",$A21&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H21&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B21&gt;0,'Условия'!$C$16&lt;&gt;"",$A21&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="22">
@@ -5274,8 +5236,7 @@
         <v/>
       </c>
       <c r="P22" s="13">
-        <f>IF($H22&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B22&gt;0,'Условия'!$C$16&lt;&gt;"",$A22&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H22&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B22&gt;0,'Условия'!$C$16&lt;&gt;"",$A22&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="23">
@@ -5339,8 +5300,7 @@
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IF($H23&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B23&gt;0,'Условия'!$C$16&lt;&gt;"",$A23&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H23&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B23&gt;0,'Условия'!$C$16&lt;&gt;"",$A23&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="24">
@@ -5404,8 +5364,7 @@
         <v/>
       </c>
       <c r="P24" s="13">
-        <f>IF($H24&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B24&gt;0,'Условия'!$C$16&lt;&gt;"",$A24&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H24&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B24&gt;0,'Условия'!$C$16&lt;&gt;"",$A24&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="25">
@@ -5469,8 +5428,7 @@
         <v/>
       </c>
       <c r="P25" s="13">
-        <f>IF($H25&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B25&gt;0,'Условия'!$C$16&lt;&gt;"",$A25&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H25&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B25&gt;0,'Условия'!$C$16&lt;&gt;"",$A25&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="26">
@@ -5534,8 +5492,7 @@
         <v/>
       </c>
       <c r="P26" s="13">
-        <f>IF($H26&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B26&gt;0,'Условия'!$C$16&lt;&gt;"",$A26&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H26&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B26&gt;0,'Условия'!$C$16&lt;&gt;"",$A26&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="27">
@@ -5599,8 +5556,7 @@
         <v/>
       </c>
       <c r="P27" s="13">
-        <f>IF($H27&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B27&gt;0,'Условия'!$C$16&lt;&gt;"",$A27&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H27&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B27&gt;0,'Условия'!$C$16&lt;&gt;"",$A27&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="28">
@@ -5664,8 +5620,7 @@
         <v/>
       </c>
       <c r="P28" s="13">
-        <f>IF($H28&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B28&gt;0,'Условия'!$C$16&lt;&gt;"",$A28&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H28&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B28&gt;0,'Условия'!$C$16&lt;&gt;"",$A28&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="29">
@@ -5729,8 +5684,7 @@
         <v/>
       </c>
       <c r="P29" s="13">
-        <f>IF($H29&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B29&gt;0,'Условия'!$C$16&lt;&gt;"",$A29&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H29&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B29&gt;0,'Условия'!$C$16&lt;&gt;"",$A29&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="30">
@@ -5794,8 +5748,7 @@
         <v/>
       </c>
       <c r="P30" s="13">
-        <f>IF($H30&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B30&gt;0,'Условия'!$C$16&lt;&gt;"",$A30&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H30&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B30&gt;0,'Условия'!$C$16&lt;&gt;"",$A30&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="31">
@@ -5859,8 +5812,7 @@
         <v/>
       </c>
       <c r="P31" s="13">
-        <f>IF($H31&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B31&gt;0,'Условия'!$C$16&lt;&gt;"",$A31&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H31&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B31&gt;0,'Условия'!$C$16&lt;&gt;"",$A31&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="32">
@@ -5924,8 +5876,7 @@
         <v/>
       </c>
       <c r="P32" s="13">
-        <f>IF($H32&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B32&gt;0,'Условия'!$C$16&lt;&gt;"",$A32&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H32&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B32&gt;0,'Условия'!$C$16&lt;&gt;"",$A32&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="33">
@@ -5989,8 +5940,7 @@
         <v/>
       </c>
       <c r="P33" s="13">
-        <f>IF($H33&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B33&gt;0,'Условия'!$C$16&lt;&gt;"",$A33&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H33&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B33&gt;0,'Условия'!$C$16&lt;&gt;"",$A33&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="34">
@@ -6054,8 +6004,7 @@
         <v/>
       </c>
       <c r="P34" s="13">
-        <f>IF($H34&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B34&gt;0,'Условия'!$C$16&lt;&gt;"",$A34&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H34&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B34&gt;0,'Условия'!$C$16&lt;&gt;"",$A34&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="35">
@@ -6119,8 +6068,7 @@
         <v/>
       </c>
       <c r="P35" s="13">
-        <f>IF($H35&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B35&gt;0,'Условия'!$C$16&lt;&gt;"",$A35&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H35&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B35&gt;0,'Условия'!$C$16&lt;&gt;"",$A35&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="36">
@@ -6184,8 +6132,7 @@
         <v/>
       </c>
       <c r="P36" s="13">
-        <f>IF($H36&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B36&gt;0,'Условия'!$C$16&lt;&gt;"",$A36&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H36&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B36&gt;0,'Условия'!$C$16&lt;&gt;"",$A36&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="37">
@@ -6249,8 +6196,7 @@
         <v/>
       </c>
       <c r="P37" s="13">
-        <f>IF($H37&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B37&gt;0,'Условия'!$C$16&lt;&gt;"",$A37&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H37&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B37&gt;0,'Условия'!$C$16&lt;&gt;"",$A37&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="38">
@@ -6314,8 +6260,7 @@
         <v/>
       </c>
       <c r="P38" s="13">
-        <f>IF($H38&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B38&gt;0,'Условия'!$C$16&lt;&gt;"",$A38&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H38&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B38&gt;0,'Условия'!$C$16&lt;&gt;"",$A38&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="39">
@@ -6379,8 +6324,7 @@
         <v/>
       </c>
       <c r="P39" s="13">
-        <f>IF($H39&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B39&gt;0,'Условия'!$C$16&lt;&gt;"",$A39&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H39&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B39&gt;0,'Условия'!$C$16&lt;&gt;"",$A39&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="40">
@@ -6444,8 +6388,7 @@
         <v/>
       </c>
       <c r="P40" s="13">
-        <f>IF($H40&lt;0,"Из КС этого месяца удерживают больше, чем она стоит: погашение аванса и гарантийное удержание вместе больше объёма",IF(AND($B40&gt;0,'Условия'!$C$16&lt;&gt;"",$A40&gt;'Условия'!$C$16),"Месяц за пределами срока объекта, а объём в графике есть",""))</f>
-        <v/>
+        <f>IF($H40&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B40&gt;0,'Условия'!$C$16&lt;&gt;"",$A40&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
       </c>
     </row>
     <row r="42">
@@ -6505,6 +6448,7 @@
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6512,7 +6456,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6524,17 +6468,17 @@
     <col width="54" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.8" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Сравнение двух сценариев: что меняет условие</t>
+          <t xml:space="preserve">Сравнение условий аванса</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Здесь не заполняется ничего. Главная строка — «Максимальная заморозка собственных денег»: столько ваших денег стоит в объекте в худший месяц. Разница между сценариями и есть цена условия, о котором идёт разговор.</t>
+          <t xml:space="preserve">Сопоставьте максимальную потребность в финансировании, срок отрицательного остатка и стоимость обеспечения. Изменение условий оценивайте по совокупности этих показателей.</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6529,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Сколько чужих денег зашло в объект.</t>
+          <t xml:space="preserve">Сумма аванса, предусмотренная расчётным сценарием.</t>
         </is>
       </c>
     </row>
@@ -6609,14 +6553,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Прямой вычет из маржи. Считается от суммы аванса, ставки и срока обеспечения.</t>
+          <t xml:space="preserve">Стоимость обеспечения уменьшает денежный результат. Расчёт учитывает сумму аванса, годовую ставку и срок.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Максимальная заморозка собственных денег, руб.</t>
+          <t xml:space="preserve">Максимальная потребность в финансировании, руб.</t>
         </is>
       </c>
       <c r="B7" s="24">
@@ -6633,23 +6577,21 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Худшая точка кассы. Столько денег нужно иметь или занять, чтобы объект не встал. Это и есть главная цифра файла.</t>
+          <t xml:space="preserve">Наибольший отрицательный накопленный остаток. Определяет требуемый объём собственных или заёмных средств.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Месяц максимальной заморозки</t>
+          <t xml:space="preserve">Месяц максимальной потребности</t>
         </is>
       </c>
       <c r="B8" s="25">
-        <f>IF(MIN('Профиль А'!$N$5:$N$40)&lt;0,INDEX('Профиль А'!$A$5:$A$40,MATCH(MIN('Профиль А'!$N$5:$N$40),'Профиль А'!$N$5:$N$40,0)),"минуса нет")</f>
-        <v/>
+        <f>IF(MIN('Профиль А'!$N$5:$N$40)&lt;0,INDEX('Профиль А'!$A$5:$A$40,MATCH(MIN('Профиль А'!$N$5:$N$40),'Профиль А'!$N$5:$N$40,0)),"Отсутствует")</f>
       </c>
       <c r="C8" s="25">
-        <f>IF(MIN('Профиль Б'!$N$5:$N$40)&lt;0,INDEX('Профиль Б'!$A$5:$A$40,MATCH(MIN('Профиль Б'!$N$5:$N$40),'Профиль Б'!$N$5:$N$40,0)),"минуса нет")</f>
-        <v/>
+        <f>IF(MIN('Профиль Б'!$N$5:$N$40)&lt;0,INDEX('Профиль Б'!$A$5:$A$40,MATCH(MIN('Профиль Б'!$N$5:$N$40),'Профиль Б'!$N$5:$N$40,0)),"Отсутствует")</f>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -6658,23 +6600,21 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Когда наступает худшая точка. Если она приходится на пик работ — риск срыва сроков, а не только процентов по кредиту.</t>
+          <t xml:space="preserve">Месяц наибольшего отрицательного остатка. Сопоставьте его с графиком закупок, работ и доступного финансирования.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Первый месяц в минусе</t>
+          <t xml:space="preserve">Первый месяц отрицательного остатка</t>
         </is>
       </c>
       <c r="B9" s="25">
-        <f>IF(COUNT('Профиль А'!$O$5:$O$40)=0,"минуса нет",MIN('Профиль А'!$O$5:$O$40))</f>
-        <v/>
+        <f>IF(COUNT('Профиль А'!$O$5:$O$40)=0,"Отсутствует",MIN('Профиль А'!$O$5:$O$40))</f>
       </c>
       <c r="C9" s="25">
-        <f>IF(COUNT('Профиль Б'!$O$5:$O$40)=0,"минуса нет",MIN('Профиль Б'!$O$5:$O$40))</f>
-        <v/>
+        <f>IF(COUNT('Профиль Б'!$O$5:$O$40)=0,"Отсутствует",MIN('Профиль Б'!$O$5:$O$40))</f>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
@@ -6683,14 +6623,14 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>С какого месяца объект финансируется вами.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
+          <t xml:space="preserve">Начало периода потребности во внешнем или собственном финансировании.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36.0" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Месяцев в минусе</t>
+          <t xml:space="preserve">Количество месяцев отрицательного остатка</t>
         </is>
       </c>
       <c r="B10" s="25">
@@ -6708,7 +6648,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Длина ямы. Стоимость денег считается от неё, а не от глубины.</t>
+          <t xml:space="preserve">Продолжительность потребности в финансировании. Его стоимость рассчитывайте по сумме задолженности, ставке и длительности каждого периода.</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6696,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Ваши деньги, оставшиеся у генподрядчика на конец расчёта.</t>
+          <t xml:space="preserve">Гарантийное удержание, не возвращённое до конца расчётного периода.</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6720,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Акты подписаны, деньги ещё идут. Если больше нуля — горизонт короче, чем объект плюс отсрочка оплаты.</t>
+          <t xml:space="preserve">Стоимость актированных работ, оплата которых поступит после окончания расчётного периода.</t>
         </is>
       </c>
     </row>
@@ -6828,53 +6768,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Денежный результат объекта на конец горизонта. Не прибыль по учёту: часть денег может быть ещё в пути.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
+          <t xml:space="preserve">Разница поступлений и расходов на конец расчётного периода. Для определения прибыли отдельно учитывайте начисления и обязательства.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Что изменилось между сценариями</t>
         </is>
       </c>
       <c r="B17" s="26">
-        <f>IF(OR($B7="",$C7=""),"",IF(ROUND($C7-$B7,2)&lt;0,"Сценарий Б замораживает меньше ваших денег в худшей точке",IF(ROUND($C7-$B7,2)&gt;0,"Сценарий Б замораживает больше ваших денег в худшей точке","Оба сценария дают одинаковую худшую точку")))</f>
-        <v/>
+        <f>IF(OR($B7="",$C7=""),"",IF(ROUND($C7-$B7,2)&lt;0,"Сценарий Б снижает максимальную потребность в финансировании.",IF(ROUND($C7-$B7,2)&gt;0,"Сценарий Б увеличивает максимальную потребность в финансировании.","Максимальная потребность в финансировании одинакова.")))</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Чего эта таблица не считает</t>
+          <t>Дополнительный расчёт стоимости финансирования</t>
         </is>
       </c>
     </row>
     <row r="20" ht="46" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>— Стоимость денег. Заморозка показана суммой и длиной, а не процентами по кредиту: ставку по своему кредиту или овердрафту вы знаете сами, и она меняется. Умножьте заморозку на свою ставку и на число месяцев в минусе — это и будет цена условия в рублях.</t>
+          <t>Для оценки стоимости собственных денег отдельно примените вашу ставку кредита или овердрафта к фактическому отрицательному остатку по месяцам.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>— Налоги. НДС с полученного аванса и момент признания дохода здесь не считаются вообще: это другой расчёт и другой специалист.</t>
+          <t xml:space="preserve">Налоговые платежи, включая НДС с аванса, включите в отдельный финансовый план по применимому налоговому режиму.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="46" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>— Возврат неотработанного аванса при расторжении. Это спор о квалификации отношений и объёме выполненного, а не расчёт кассы. Ситуацию надо назвать и остановиться: дальше юрист по вашему делу.</t>
+          <t>Если получено требование вернуть аванс после прекращения договора, отдельно заполните расчёт 09 по актам, платежам и основанию прекращения.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="46" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>— Вероятность согласия. Генподрядчик может не согласиться ни на один пункт. Файл даёт цифру для разговора, а не рычаг.</t>
+          <t xml:space="preserve">Зафиксируйте результаты согласования в протоколе разногласий или дополнительном соглашении. При отказе пересчитайте потребность в финансировании на предложенных условиях.</t>
         </is>
       </c>
     </row>
@@ -6888,6 +6827,7 @@
     <mergeCell ref="A22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6895,7 +6835,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6911,7 +6851,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="46" customHeight="1">
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Шаг 1</t>
@@ -6919,11 +6859,11 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t>На листе «Условия» заполните колонку «Сценарий А» — то, что вам предлагают сейчас. Всё из вашего договора или из проекта договора.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="46" customHeight="1">
+          <t xml:space="preserve">Внесите в сценарий А условия предложенного проекта договора или подписанного договора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Шаг 2</t>
@@ -6935,7 +6875,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Шаг 3</t>
@@ -6943,11 +6883,11 @@
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>Скопируйте колонку А в колонку Б на листе «Условия» и измените в ней ровно одно условие: размер аванса, порядок погашения, ставку обеспечения или гарантийное удержание. По одному условию за раз — иначе непонятно, что именно дало разницу.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
+          <t xml:space="preserve">Скопируйте исходные условия сценария А в сценарий Б. Для отдельной оценки измените один показатель: размер аванса, порядок погашения, ставку обеспечения или гарантийное удержание.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Шаг 4</t>
@@ -6955,11 +6895,11 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Откройте лист «Сравнение». Строка «Максимальная заморозка собственных денег» — цена этого условия для вас. Строка «Месяц максимальной заморозки» — когда вам понадобятся деньги.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
+          <t xml:space="preserve">На листе «Сравнение» проверьте максимальную потребность в финансировании и месяц её возникновения. Сопоставьте их со стоимостью обеспечения.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Шаг 5</t>
@@ -6967,11 +6907,11 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>Повторите для остальных условий. Получится список из четырёх цифр — это и есть повестка переговоров, отсортированная по деньгам.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
+          <t xml:space="preserve">Повторите сравнение для остальных условий. Составьте перечень изменений с оценкой денежного эффекта по каждому.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Шаг 6</t>
@@ -6979,7 +6919,7 @@
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>Договорённость закрывается документом: до подписания — протоколом разногласий, после подписания — дополнительным соглашением. Оба есть в этом комплекте.</t>
+          <t xml:space="preserve">До подписания договора оформите согласованные изменения протоколом разногласий, после подписания — дополнительным соглашением. Используйте формы 05 и 06.</t>
         </is>
       </c>
     </row>
@@ -7046,35 +6986,35 @@
       </c>
       <c r="B15" s="29" t="inlineStr">
         <is>
-          <t>проверка: если что-то написано, читайте и исправляйте</t>
+          <t xml:space="preserve">Сообщение проверки. Уточните исходные данные, к которым относится замечание.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Почему файл открывается и в LibreOffice</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1">
+          <t>Совместимость и контроль расчёта</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>В расчёте использованы только функции, которые вычисляют и Excel, и LibreOffice: IF, AND, OR, SUM, SUMIFS, MIN, MAX, COUNT, INDEX, MATCH, IFERROR, SUMPRODUCT, ROUND. Новых функций поиска здесь нет намеренно — в LibreOffice они дают ошибку вместо результата, и файл выглядел бы сломанным.</t>
+          <t>После заполнения проверьте итоговые строки в Excel или LibreOffice; при переносе файла сохраните формулы и исходные данные.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Проверьте себя перед переговорами</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="46" customHeight="1">
+          <t xml:space="preserve">Контроль перед согласованием условий</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Посчитайте сценарий с нулевым авансом. Разница с вашим сценарием по строке «Максимальная заморозка» — это то, сколько аванс стоит для вас на самом деле. Если она меньше стоимости обеспечения, аванс под платную гарантию вам невыгоден, и об этом стоит знать до подписания, а не после.</t>
+          <t xml:space="preserve">Сравните сценарии с авансом и без него. Отдельно рассчитайте стоимость финансирования по сумме, ставке и периоду привлечения средств. Решение принимайте с учётом ликвидности, комиссии за обеспечение и совокупных расходов.</t>
         </is>
       </c>
     </row>
@@ -7084,6 +7024,7 @@
     <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7091,7 +7032,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7112,7 +7053,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>Здесь показан формат ввода, а не ваш расчёт. Цифры условные и взяты для наглядности. Ничего отсюда не переносите в рабочие листы: считайте по своему договору.</t>
+          <t xml:space="preserve">Учебный пример показывает формат исходных данных. Для рабочего расчёта используйте условия своего договора, график выполнения и предложение банка.</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7370,7 @@
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Сценарий А получает аванс в первом месяце и гасит его равными долями из каждой КС; сценарий Б не получает ничего и живёт на своих с первого дня. Разница по строке «Максимальная заморозка собственных денег» — это цена аванса в вашу сторону; из неё надо вычесть стоимость обеспечения, если гарантия платная. Точные числа посчитает файл: здесь их нет намеренно, чтобы никто не переписал пример вместо своего расчёта.</t>
+          <t>Сценарий А использует аванс в первом месяце; сценарий Б показывает финансирование собственными средствами. Сравните максимальный отрицательный остаток и стоимость обеспечения на ваших данных.</t>
         </is>
       </c>
     </row>
@@ -7440,5 +7381,6 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/products-storage/10-avans-usloviya-i-pribyl/02-kalkulyator-usloviy-avansa.xlsx
+++ b/products-storage/10-avans-usloviya-i-pribyl/02-kalkulyator-usloviy-avansa.xlsx
@@ -581,7 +581,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Заполните исходные условия в сценариях А и Б по договору, графику работ и предложению банка. В сценарии А укажите предложенные условия, в Б — вариант для согласования. Сопоставьте результаты на листе «Сравнение».</t>
+          <t>Сравните сценарии А и Б. Числовые поля заполните числами; подтверждённое отсутствие расхода — 0, неизвестное значение не заменяйте нулём. Итоги доступны после проверки условий и профиля.</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       <c r="C7" s="7" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порядковый месяц фактического поступления аванса, считая от начала расчётного периода.</t>
+          <t>Целый месяц 1–36. При нулевом авансе — 0 или пусто. Погашение ранее получения аванса требует исправления графика.</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Только для порядка «с отсрочкой до доли выполнения». Для двух других порядков поле не используется.</t>
+          <t>Для третьего порядка: число от 0 до менее 100. Для других порядков — 0 или пусто.</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Срок действия обеспечения по договору и условиям банка, в месяцах.</t>
+          <t>При платном обеспечении: положительное целое число месяцев. Без обеспечения — 0 или пусто.</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       <c r="C12" s="7" t="n"/>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Порядковый месяц фактической оплаты комиссии за обеспечение.</t>
+          <t>При платном обеспечении: целый месяц 1–36. Без обеспечения — 0 или пусто.</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       <c r="C14" s="7" t="n"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Месяц возврата удержания по договору. Значение 0 означает отсутствие возврата в пределах 36 месяцев расчёта.</t>
+          <t>Целый месяц 0–36; 0 — возврата нет. Возврат возможен только в пределах удержания, накопленного к сроку оплаты КС.</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Доля удержания, возвращаемая в указанном месяце. Остальная часть сохраняется в расчёте как невозвращённая.</t>
+          <t>Процент от общего удержания по графику. Ранний возврат всей будущей суммы не допускается; проверьте остаток в выбранном месяце.</t>
         </is>
       </c>
     </row>
@@ -785,7 +785,7 @@
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Количество месяцев между подписанием акта и поступлением оплаты, предусмотренное договором.</t>
+          <t>Целое число месяцев 0–36. При дробных сроках используйте отдельный расчёт с меньшим шагом.</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Доля расходов на выполнение работ в цене договора. Включите учитываемые в расчёте материалы, оплату труда, эксплуатацию техники и иные расходы.</t>
+          <t>Число не меньше 0; доля затрат может превышать 100 при убыточном объекте. Пусто — затраты неизвестны, расчёт не завершён.</t>
         </is>
       </c>
     </row>
@@ -813,7 +813,7 @@
       <c r="C19" s="7" t="n"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Количество месяцев между несением расходов и соответствующим выполнением работ: закупка, доставка и мобилизация.</t>
+          <t>Целое число 0–35. Расходы, относящиеся к началу и более ранним периодам, объединены в первом месяце.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       <c r="C20" s="5" t="n"/>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Расходы до первого акта: мобилизация, временные сооружения, обеспечительные платежи и первоначальная поставка.</t>
+          <t>Дополнительные стартовые расходы в первом месяце. Не включайте повторно затраты, уже учтённые в себестоимости. При отсутствии — 0.</t>
         </is>
       </c>
     </row>
@@ -845,11 +845,11 @@
         </is>
       </c>
       <c r="B23" s="11">
-        <f>IF('Условия'!$B$5="",0,ROUND('Условия'!$B$5*'Условия'!$B$6/100,2))</f>
+        <f>IF(B26&lt;&gt;"Условия заполнены","",ROUND(B5*B6/100,2))</f>
         <v/>
       </c>
       <c r="C23" s="11">
-        <f>IF('Условия'!$C$5="",0,ROUND('Условия'!$C$5*'Условия'!$C$6/100,2))</f>
+        <f>IF(C26&lt;&gt;"Условия заполнены","",ROUND(C5*C6/100,2))</f>
         <v/>
       </c>
     </row>
@@ -860,11 +860,11 @@
         </is>
       </c>
       <c r="B24" s="11">
-        <f>ROUND('Условия'!$B$23*'Условия'!$B$10/100*'Условия'!$B$11/12,2)</f>
+        <f>IF(B26&lt;&gt;"Условия заполнены","",IF(OR(B6=0,B10=0),0,ROUND(B23*B10/100*B11/12,2)))</f>
         <v/>
       </c>
       <c r="C24" s="11">
-        <f>ROUND('Условия'!$C$23*'Условия'!$C$10/100*'Условия'!$C$11/12,2)</f>
+        <f>IF(C26&lt;&gt;"Условия заполнены","",IF(OR(C6=0,C10=0),0,ROUND(C23*C10/100*C11/12,2)))</f>
         <v/>
       </c>
     </row>
@@ -875,25 +875,27 @@
         </is>
       </c>
       <c r="B25" s="12">
-        <f>IFERROR(MATCH('Условия'!$B$8,'Условия'!$A$29:$A$31,0),0)</f>
+        <f>IF(B6=0,0,IFERROR(MATCH(B8,$A$29:$A$31,0),0))</f>
         <v/>
       </c>
       <c r="C25" s="12">
-        <f>IFERROR(MATCH('Условия'!$C$8,'Условия'!$A$29:$A$31,0),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
+        <f>IF(C6=0,0,IFERROR(MATCH(C8,$A$29:$A$31,0),0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="78" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Проверка условий</t>
         </is>
       </c>
       <c r="B26" s="13">
-        <f>IF('Условия'!$B$5="","Не заполнена сумма договора",IF('Условия'!$B$25=0,"Порядок погашения не выбран из списка",IF(AND('Условия'!$B$25=3,'Условия'!$B$9=""),"Для порядка с отсрочкой укажите долю выполнения",IF('Условия'!$B$16="","Не заполнен срок объекта",IF('Условия'!$B$10&gt;0,"Условия заполнены. Стоимость обеспечения учтена в денежных расходах.","Условия заполнены")))))</f>
+        <f>IFERROR(IF(OR(LEN(B5)=0,LEN(B6)=0,LEN(B10)=0,LEN(B13)=0,LEN(B16)=0,LEN(B17)=0,LEN(B18)=0,LEN(B19)=0,LEN(B20)=0),"НЕ ЗАПОЛНЕНО: обязательные суммы, проценты и сроки",IF(OR(NOT(ISNUMBER(B5)),NOT(ISNUMBER(B6)),NOT(ISNUMBER(B10)),NOT(ISNUMBER(B13)),NOT(ISNUMBER(B16)),NOT(ISNUMBER(B17)),NOT(ISNUMBER(B18)),NOT(ISNUMBER(B19)),NOT(ISNUMBER(B20))),"ОШИБКА: обязательные показатели вводятся числами",IF(OR(B5&lt;=0,B6&lt;0,B6&gt;100,B10&lt;0,B13&lt;0,B13&gt;100,B18&lt;0,B20&lt;0),"ОШИБКА: проверьте знак сумм и диапазон процентов",IF(OR(B16&lt;1,B16&gt;36,B16&lt;&gt;INT(B16),B17&lt;0,B17&gt;36,B17&lt;&gt;INT(B17),B19&lt;0,B19&gt;35,B19&lt;&gt;INT(B19)),"ОШИБКА: сроки — целые месяцы в пределах горизонта",IF(AND(B6&gt;0,OR(NOT(ISNUMBER(B7)),B7&lt;1,B7&gt;36,B7&lt;&gt;INT(B7))),"ОШИБКА: укажите целый месяц получения аванса 1–36",IF(AND(B6&gt;0,B25=0),"ОШИБКА: выберите порядок погашения из списка",IF(AND(B6&gt;0,B25=3,OR(LEN(B9)=0,NOT(ISNUMBER(B9)),B9&lt;0,B9&gt;=100)),"ОШИБКА: порог погашения от 0 до менее 100%",IF(AND(B6&gt;0,B10&gt;0,OR(NOT(ISNUMBER(B11)),B11&lt;=0,B11&lt;&gt;INT(B11),NOT(ISNUMBER(B12)),B12&lt;1,B12&gt;36,B12&lt;&gt;INT(B12))),"ОШИБКА: проверьте срок и месяц оплаты обеспечения",IF(AND(B13&gt;0,OR(NOT(ISNUMBER(B14)),B14&lt;0,B14&gt;36,B14&lt;&gt;INT(B14),NOT(ISNUMBER(B15)),B15&lt;0,B15&gt;100,LEN(B14)=0,LEN(B15)=0)),"ОШИБКА: проверьте месяц и долю возврата удержания",IF(COUNT('График КС'!B5:B40)&lt;&gt;COUNTA('График КС'!B5:B40),"ОШИБКА: доли графика должны быть числами",IF(OR(COUNTIF('График КС'!B5:B40,"&lt;0")&gt;0,COUNTIF('График КС'!B5:B40,"&gt;100")&gt;0),"ОШИБКА: доля графика вне диапазона 0–100%",IF(ABS(SUM('График КС'!B5:B40)-100)&gt;0.000001,"НЕ ЗАПОЛНЕНО: сумма долей графика должна быть 100%",IF(SUMIF('График КС'!$A$5:$A$40,"&gt;"&amp;B16,'График КС'!B5:B40)&gt;0,"ОШИБКА: работы в графике выходят за срок объекта","Условия заполнены"))))))))))))),"ОШИБКА: проверьте числовые исходные данные")</f>
+        <v/>
       </c>
       <c r="C26" s="13">
-        <f>IF('Условия'!$C$5="","Не заполнена сумма договора",IF('Условия'!$C$25=0,"Порядок погашения не выбран из списка",IF(AND('Условия'!$C$25=3,'Условия'!$C$9=""),"Для порядка с отсрочкой укажите долю выполнения",IF('Условия'!$C$16="","Не заполнен срок объекта",IF('Условия'!$C$10&gt;0,"Условия заполнены. Стоимость обеспечения учтена в денежных расходах.","Условия заполнены")))))</f>
+        <f>IFERROR(IF(OR(LEN(C5)=0,LEN(C6)=0,LEN(C10)=0,LEN(C13)=0,LEN(C16)=0,LEN(C17)=0,LEN(C18)=0,LEN(C19)=0,LEN(C20)=0),"НЕ ЗАПОЛНЕНО: обязательные суммы, проценты и сроки",IF(OR(NOT(ISNUMBER(C5)),NOT(ISNUMBER(C6)),NOT(ISNUMBER(C10)),NOT(ISNUMBER(C13)),NOT(ISNUMBER(C16)),NOT(ISNUMBER(C17)),NOT(ISNUMBER(C18)),NOT(ISNUMBER(C19)),NOT(ISNUMBER(C20))),"ОШИБКА: обязательные показатели вводятся числами",IF(OR(C5&lt;=0,C6&lt;0,C6&gt;100,C10&lt;0,C13&lt;0,C13&gt;100,C18&lt;0,C20&lt;0),"ОШИБКА: проверьте знак сумм и диапазон процентов",IF(OR(C16&lt;1,C16&gt;36,C16&lt;&gt;INT(C16),C17&lt;0,C17&gt;36,C17&lt;&gt;INT(C17),C19&lt;0,C19&gt;35,C19&lt;&gt;INT(C19)),"ОШИБКА: сроки — целые месяцы в пределах горизонта",IF(AND(C6&gt;0,OR(NOT(ISNUMBER(C7)),C7&lt;1,C7&gt;36,C7&lt;&gt;INT(C7))),"ОШИБКА: укажите целый месяц получения аванса 1–36",IF(AND(C6&gt;0,C25=0),"ОШИБКА: выберите порядок погашения из списка",IF(AND(C6&gt;0,C25=3,OR(LEN(C9)=0,NOT(ISNUMBER(C9)),C9&lt;0,C9&gt;=100)),"ОШИБКА: порог погашения от 0 до менее 100%",IF(AND(C6&gt;0,C10&gt;0,OR(NOT(ISNUMBER(C11)),C11&lt;=0,C11&lt;&gt;INT(C11),NOT(ISNUMBER(C12)),C12&lt;1,C12&gt;36,C12&lt;&gt;INT(C12))),"ОШИБКА: проверьте срок и месяц оплаты обеспечения",IF(AND(C13&gt;0,OR(NOT(ISNUMBER(C14)),C14&lt;0,C14&gt;36,C14&lt;&gt;INT(C14),NOT(ISNUMBER(C15)),C15&lt;0,C15&gt;100,LEN(C14)=0,LEN(C15)=0)),"ОШИБКА: проверьте месяц и долю возврата удержания",IF(COUNT('График КС'!C5:C40)&lt;&gt;COUNTA('График КС'!C5:C40),"ОШИБКА: доли графика должны быть числами",IF(OR(COUNTIF('График КС'!C5:C40,"&lt;0")&gt;0,COUNTIF('График КС'!C5:C40,"&gt;100")&gt;0),"ОШИБКА: доля графика вне диапазона 0–100%",IF(ABS(SUM('График КС'!C5:C40)-100)&gt;0.000001,"НЕ ЗАПОЛНЕНО: сумма долей графика должна быть 100%",IF(SUMIF('График КС'!$A$5:$A$40,"&gt;"&amp;C16,'График КС'!C5:C40)&gt;0,"ОШИБКА: работы в графике выходят за срок объекта","Условия заполнены"))))))))))))),"ОШИБКА: проверьте числовые исходные данные")</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -958,7 +960,7 @@
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Введите ставку обеспечения, сроки оплаты и гарантийное удержание из договора и банковского предложения на дату расчёта. Сверьте оба сценария.</t>
+          <t>Ставки и сроки берите из договора и предложения банка. Проценты вводите числом: 20 означает 20%, не 0,2. В календарных полях используются порядковые месяцы, а не даты.</t>
         </is>
       </c>
     </row>
@@ -972,7 +974,7 @@
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>Сверьте введённые условия с договором, графиком платежей и стоимостью обеспечения. Сравните сценарии по максимальному дефициту и месяцу его возникновения.</t>
+          <t>Готовность показана на листе «Сравнение», строка 18. При сообщении о профиле проверьте колонку P. Это месячный денежный расчёт, не прибыль и не внутримесячный максимум потребности.</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1021,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Заполните жёлтые колонки: доля объёма месяца в процентах от суммы договора. Сумма долей по сценарию должна быть 100. Если вы сравниваете только условия аванса, а не график, колонки А и Б заполняются одинаково.</t>
+          <t>В жёлтых колонках укажите долю выполненных работ каждого месяца, числом от 0 до 100. Сумма каждого сценария — 100. Месяцы без работ можно оставить пустыми или указать 0.</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1054,7 @@
       <c r="B5" s="6" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="18">
-        <f>IF(AND($B5="",$C5=""),"",IF(OR($B5&lt;0,$C5&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B5:C5)=0,"",IF(OR(AND(B5&lt;&gt;"",NOT(ISNUMBER(B5))),AND(C5&lt;&gt;"",NOT(ISNUMBER(C5)))),"ОШИБКА: доля должна быть числом",IF(OR(B5&lt;0,C5&lt;0,B5&gt;100,C5&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1063,7 +1065,7 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
       <c r="D6" s="18">
-        <f>IF(AND($B6="",$C6=""),"",IF(OR($B6&lt;0,$C6&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B6:C6)=0,"",IF(OR(AND(B6&lt;&gt;"",NOT(ISNUMBER(B6))),AND(C6&lt;&gt;"",NOT(ISNUMBER(C6)))),"ОШИБКА: доля должна быть числом",IF(OR(B6&lt;0,C6&lt;0,B6&gt;100,C6&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1074,7 +1076,7 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="18">
-        <f>IF(AND($B7="",$C7=""),"",IF(OR($B7&lt;0,$C7&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B7:C7)=0,"",IF(OR(AND(B7&lt;&gt;"",NOT(ISNUMBER(B7))),AND(C7&lt;&gt;"",NOT(ISNUMBER(C7)))),"ОШИБКА: доля должна быть числом",IF(OR(B7&lt;0,C7&lt;0,B7&gt;100,C7&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1085,7 +1087,7 @@
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="18">
-        <f>IF(AND($B8="",$C8=""),"",IF(OR($B8&lt;0,$C8&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B8:C8)=0,"",IF(OR(AND(B8&lt;&gt;"",NOT(ISNUMBER(B8))),AND(C8&lt;&gt;"",NOT(ISNUMBER(C8)))),"ОШИБКА: доля должна быть числом",IF(OR(B8&lt;0,C8&lt;0,B8&gt;100,C8&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1096,7 +1098,7 @@
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="18">
-        <f>IF(AND($B9="",$C9=""),"",IF(OR($B9&lt;0,$C9&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B9:C9)=0,"",IF(OR(AND(B9&lt;&gt;"",NOT(ISNUMBER(B9))),AND(C9&lt;&gt;"",NOT(ISNUMBER(C9)))),"ОШИБКА: доля должна быть числом",IF(OR(B9&lt;0,C9&lt;0,B9&gt;100,C9&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1107,7 +1109,7 @@
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="18">
-        <f>IF(AND($B10="",$C10=""),"",IF(OR($B10&lt;0,$C10&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B10:C10)=0,"",IF(OR(AND(B10&lt;&gt;"",NOT(ISNUMBER(B10))),AND(C10&lt;&gt;"",NOT(ISNUMBER(C10)))),"ОШИБКА: доля должна быть числом",IF(OR(B10&lt;0,C10&lt;0,B10&gt;100,C10&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1118,7 +1120,7 @@
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="18">
-        <f>IF(AND($B11="",$C11=""),"",IF(OR($B11&lt;0,$C11&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B11:C11)=0,"",IF(OR(AND(B11&lt;&gt;"",NOT(ISNUMBER(B11))),AND(C11&lt;&gt;"",NOT(ISNUMBER(C11)))),"ОШИБКА: доля должна быть числом",IF(OR(B11&lt;0,C11&lt;0,B11&gt;100,C11&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1129,7 +1131,7 @@
       <c r="B12" s="6" t="n"/>
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="18">
-        <f>IF(AND($B12="",$C12=""),"",IF(OR($B12&lt;0,$C12&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B12:C12)=0,"",IF(OR(AND(B12&lt;&gt;"",NOT(ISNUMBER(B12))),AND(C12&lt;&gt;"",NOT(ISNUMBER(C12)))),"ОШИБКА: доля должна быть числом",IF(OR(B12&lt;0,C12&lt;0,B12&gt;100,C12&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1140,7 +1142,7 @@
       <c r="B13" s="6" t="n"/>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="18">
-        <f>IF(AND($B13="",$C13=""),"",IF(OR($B13&lt;0,$C13&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B13:C13)=0,"",IF(OR(AND(B13&lt;&gt;"",NOT(ISNUMBER(B13))),AND(C13&lt;&gt;"",NOT(ISNUMBER(C13)))),"ОШИБКА: доля должна быть числом",IF(OR(B13&lt;0,C13&lt;0,B13&gt;100,C13&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1151,7 +1153,7 @@
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="18">
-        <f>IF(AND($B14="",$C14=""),"",IF(OR($B14&lt;0,$C14&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B14:C14)=0,"",IF(OR(AND(B14&lt;&gt;"",NOT(ISNUMBER(B14))),AND(C14&lt;&gt;"",NOT(ISNUMBER(C14)))),"ОШИБКА: доля должна быть числом",IF(OR(B14&lt;0,C14&lt;0,B14&gt;100,C14&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1162,7 +1164,7 @@
       <c r="B15" s="6" t="n"/>
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="18">
-        <f>IF(AND($B15="",$C15=""),"",IF(OR($B15&lt;0,$C15&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B15:C15)=0,"",IF(OR(AND(B15&lt;&gt;"",NOT(ISNUMBER(B15))),AND(C15&lt;&gt;"",NOT(ISNUMBER(C15)))),"ОШИБКА: доля должна быть числом",IF(OR(B15&lt;0,C15&lt;0,B15&gt;100,C15&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1173,7 +1175,7 @@
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="18">
-        <f>IF(AND($B16="",$C16=""),"",IF(OR($B16&lt;0,$C16&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B16:C16)=0,"",IF(OR(AND(B16&lt;&gt;"",NOT(ISNUMBER(B16))),AND(C16&lt;&gt;"",NOT(ISNUMBER(C16)))),"ОШИБКА: доля должна быть числом",IF(OR(B16&lt;0,C16&lt;0,B16&gt;100,C16&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1184,7 +1186,7 @@
       <c r="B17" s="6" t="n"/>
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="18">
-        <f>IF(AND($B17="",$C17=""),"",IF(OR($B17&lt;0,$C17&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B17:C17)=0,"",IF(OR(AND(B17&lt;&gt;"",NOT(ISNUMBER(B17))),AND(C17&lt;&gt;"",NOT(ISNUMBER(C17)))),"ОШИБКА: доля должна быть числом",IF(OR(B17&lt;0,C17&lt;0,B17&gt;100,C17&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1195,7 +1197,7 @@
       <c r="B18" s="6" t="n"/>
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="18">
-        <f>IF(AND($B18="",$C18=""),"",IF(OR($B18&lt;0,$C18&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B18:C18)=0,"",IF(OR(AND(B18&lt;&gt;"",NOT(ISNUMBER(B18))),AND(C18&lt;&gt;"",NOT(ISNUMBER(C18)))),"ОШИБКА: доля должна быть числом",IF(OR(B18&lt;0,C18&lt;0,B18&gt;100,C18&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1206,7 +1208,7 @@
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="18">
-        <f>IF(AND($B19="",$C19=""),"",IF(OR($B19&lt;0,$C19&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B19:C19)=0,"",IF(OR(AND(B19&lt;&gt;"",NOT(ISNUMBER(B19))),AND(C19&lt;&gt;"",NOT(ISNUMBER(C19)))),"ОШИБКА: доля должна быть числом",IF(OR(B19&lt;0,C19&lt;0,B19&gt;100,C19&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1217,7 +1219,7 @@
       <c r="B20" s="6" t="n"/>
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="18">
-        <f>IF(AND($B20="",$C20=""),"",IF(OR($B20&lt;0,$C20&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B20:C20)=0,"",IF(OR(AND(B20&lt;&gt;"",NOT(ISNUMBER(B20))),AND(C20&lt;&gt;"",NOT(ISNUMBER(C20)))),"ОШИБКА: доля должна быть числом",IF(OR(B20&lt;0,C20&lt;0,B20&gt;100,C20&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1228,7 +1230,7 @@
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="18">
-        <f>IF(AND($B21="",$C21=""),"",IF(OR($B21&lt;0,$C21&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B21:C21)=0,"",IF(OR(AND(B21&lt;&gt;"",NOT(ISNUMBER(B21))),AND(C21&lt;&gt;"",NOT(ISNUMBER(C21)))),"ОШИБКА: доля должна быть числом",IF(OR(B21&lt;0,C21&lt;0,B21&gt;100,C21&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1239,7 +1241,7 @@
       <c r="B22" s="6" t="n"/>
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="18">
-        <f>IF(AND($B22="",$C22=""),"",IF(OR($B22&lt;0,$C22&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B22:C22)=0,"",IF(OR(AND(B22&lt;&gt;"",NOT(ISNUMBER(B22))),AND(C22&lt;&gt;"",NOT(ISNUMBER(C22)))),"ОШИБКА: доля должна быть числом",IF(OR(B22&lt;0,C22&lt;0,B22&gt;100,C22&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1250,7 +1252,7 @@
       <c r="B23" s="6" t="n"/>
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="18">
-        <f>IF(AND($B23="",$C23=""),"",IF(OR($B23&lt;0,$C23&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B23:C23)=0,"",IF(OR(AND(B23&lt;&gt;"",NOT(ISNUMBER(B23))),AND(C23&lt;&gt;"",NOT(ISNUMBER(C23)))),"ОШИБКА: доля должна быть числом",IF(OR(B23&lt;0,C23&lt;0,B23&gt;100,C23&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1261,7 +1263,7 @@
       <c r="B24" s="6" t="n"/>
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="18">
-        <f>IF(AND($B24="",$C24=""),"",IF(OR($B24&lt;0,$C24&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B24:C24)=0,"",IF(OR(AND(B24&lt;&gt;"",NOT(ISNUMBER(B24))),AND(C24&lt;&gt;"",NOT(ISNUMBER(C24)))),"ОШИБКА: доля должна быть числом",IF(OR(B24&lt;0,C24&lt;0,B24&gt;100,C24&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1272,7 +1274,7 @@
       <c r="B25" s="6" t="n"/>
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="18">
-        <f>IF(AND($B25="",$C25=""),"",IF(OR($B25&lt;0,$C25&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B25:C25)=0,"",IF(OR(AND(B25&lt;&gt;"",NOT(ISNUMBER(B25))),AND(C25&lt;&gt;"",NOT(ISNUMBER(C25)))),"ОШИБКА: доля должна быть числом",IF(OR(B25&lt;0,C25&lt;0,B25&gt;100,C25&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1283,7 +1285,7 @@
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="18">
-        <f>IF(AND($B26="",$C26=""),"",IF(OR($B26&lt;0,$C26&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B26:C26)=0,"",IF(OR(AND(B26&lt;&gt;"",NOT(ISNUMBER(B26))),AND(C26&lt;&gt;"",NOT(ISNUMBER(C26)))),"ОШИБКА: доля должна быть числом",IF(OR(B26&lt;0,C26&lt;0,B26&gt;100,C26&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1294,7 +1296,7 @@
       <c r="B27" s="6" t="n"/>
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="18">
-        <f>IF(AND($B27="",$C27=""),"",IF(OR($B27&lt;0,$C27&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B27:C27)=0,"",IF(OR(AND(B27&lt;&gt;"",NOT(ISNUMBER(B27))),AND(C27&lt;&gt;"",NOT(ISNUMBER(C27)))),"ОШИБКА: доля должна быть числом",IF(OR(B27&lt;0,C27&lt;0,B27&gt;100,C27&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1307,7 @@
       <c r="B28" s="6" t="n"/>
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="18">
-        <f>IF(AND($B28="",$C28=""),"",IF(OR($B28&lt;0,$C28&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B28:C28)=0,"",IF(OR(AND(B28&lt;&gt;"",NOT(ISNUMBER(B28))),AND(C28&lt;&gt;"",NOT(ISNUMBER(C28)))),"ОШИБКА: доля должна быть числом",IF(OR(B28&lt;0,C28&lt;0,B28&gt;100,C28&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1316,7 +1318,7 @@
       <c r="B29" s="6" t="n"/>
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="18">
-        <f>IF(AND($B29="",$C29=""),"",IF(OR($B29&lt;0,$C29&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B29:C29)=0,"",IF(OR(AND(B29&lt;&gt;"",NOT(ISNUMBER(B29))),AND(C29&lt;&gt;"",NOT(ISNUMBER(C29)))),"ОШИБКА: доля должна быть числом",IF(OR(B29&lt;0,C29&lt;0,B29&gt;100,C29&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1327,7 +1329,7 @@
       <c r="B30" s="6" t="n"/>
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="18">
-        <f>IF(AND($B30="",$C30=""),"",IF(OR($B30&lt;0,$C30&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B30:C30)=0,"",IF(OR(AND(B30&lt;&gt;"",NOT(ISNUMBER(B30))),AND(C30&lt;&gt;"",NOT(ISNUMBER(C30)))),"ОШИБКА: доля должна быть числом",IF(OR(B30&lt;0,C30&lt;0,B30&gt;100,C30&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1338,7 +1340,7 @@
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="18">
-        <f>IF(AND($B31="",$C31=""),"",IF(OR($B31&lt;0,$C31&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B31:C31)=0,"",IF(OR(AND(B31&lt;&gt;"",NOT(ISNUMBER(B31))),AND(C31&lt;&gt;"",NOT(ISNUMBER(C31)))),"ОШИБКА: доля должна быть числом",IF(OR(B31&lt;0,C31&lt;0,B31&gt;100,C31&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1349,7 +1351,7 @@
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="18">
-        <f>IF(AND($B32="",$C32=""),"",IF(OR($B32&lt;0,$C32&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B32:C32)=0,"",IF(OR(AND(B32&lt;&gt;"",NOT(ISNUMBER(B32))),AND(C32&lt;&gt;"",NOT(ISNUMBER(C32)))),"ОШИБКА: доля должна быть числом",IF(OR(B32&lt;0,C32&lt;0,B32&gt;100,C32&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1360,7 +1362,7 @@
       <c r="B33" s="6" t="n"/>
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="18">
-        <f>IF(AND($B33="",$C33=""),"",IF(OR($B33&lt;0,$C33&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B33:C33)=0,"",IF(OR(AND(B33&lt;&gt;"",NOT(ISNUMBER(B33))),AND(C33&lt;&gt;"",NOT(ISNUMBER(C33)))),"ОШИБКА: доля должна быть числом",IF(OR(B33&lt;0,C33&lt;0,B33&gt;100,C33&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1371,7 +1373,7 @@
       <c r="B34" s="6" t="n"/>
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="18">
-        <f>IF(AND($B34="",$C34=""),"",IF(OR($B34&lt;0,$C34&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B34:C34)=0,"",IF(OR(AND(B34&lt;&gt;"",NOT(ISNUMBER(B34))),AND(C34&lt;&gt;"",NOT(ISNUMBER(C34)))),"ОШИБКА: доля должна быть числом",IF(OR(B34&lt;0,C34&lt;0,B34&gt;100,C34&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1382,7 +1384,7 @@
       <c r="B35" s="6" t="n"/>
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="18">
-        <f>IF(AND($B35="",$C35=""),"",IF(OR($B35&lt;0,$C35&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B35:C35)=0,"",IF(OR(AND(B35&lt;&gt;"",NOT(ISNUMBER(B35))),AND(C35&lt;&gt;"",NOT(ISNUMBER(C35)))),"ОШИБКА: доля должна быть числом",IF(OR(B35&lt;0,C35&lt;0,B35&gt;100,C35&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1393,7 +1395,7 @@
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="18">
-        <f>IF(AND($B36="",$C36=""),"",IF(OR($B36&lt;0,$C36&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B36:C36)=0,"",IF(OR(AND(B36&lt;&gt;"",NOT(ISNUMBER(B36))),AND(C36&lt;&gt;"",NOT(ISNUMBER(C36)))),"ОШИБКА: доля должна быть числом",IF(OR(B36&lt;0,C36&lt;0,B36&gt;100,C36&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1404,7 +1406,7 @@
       <c r="B37" s="6" t="n"/>
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="18">
-        <f>IF(AND($B37="",$C37=""),"",IF(OR($B37&lt;0,$C37&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B37:C37)=0,"",IF(OR(AND(B37&lt;&gt;"",NOT(ISNUMBER(B37))),AND(C37&lt;&gt;"",NOT(ISNUMBER(C37)))),"ОШИБКА: доля должна быть числом",IF(OR(B37&lt;0,C37&lt;0,B37&gt;100,C37&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1415,7 +1417,7 @@
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="18">
-        <f>IF(AND($B38="",$C38=""),"",IF(OR($B38&lt;0,$C38&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B38:C38)=0,"",IF(OR(AND(B38&lt;&gt;"",NOT(ISNUMBER(B38))),AND(C38&lt;&gt;"",NOT(ISNUMBER(C38)))),"ОШИБКА: доля должна быть числом",IF(OR(B38&lt;0,C38&lt;0,B38&gt;100,C38&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1426,7 +1428,7 @@
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="18">
-        <f>IF(AND($B39="",$C39=""),"",IF(OR($B39&lt;0,$C39&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B39:C39)=0,"",IF(OR(AND(B39&lt;&gt;"",NOT(ISNUMBER(B39))),AND(C39&lt;&gt;"",NOT(ISNUMBER(C39)))),"ОШИБКА: доля должна быть числом",IF(OR(B39&lt;0,C39&lt;0,B39&gt;100,C39&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1437,7 +1439,7 @@
       <c r="B40" s="6" t="n"/>
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="18">
-        <f>IF(AND($B40="",$C40=""),"",IF(OR($B40&lt;0,$C40&lt;0),"Доля не может быть отрицательной",""))</f>
+        <f>IF(COUNTA(B40:C40)=0,"",IF(OR(AND(B40&lt;&gt;"",NOT(ISNUMBER(B40))),AND(C40&lt;&gt;"",NOT(ISNUMBER(C40)))),"ОШИБКА: доля должна быть числом",IF(OR(B40&lt;0,C40&lt;0,B40&gt;100,C40&gt;100),"ОШИБКА: доля вне 0–100%","")))</f>
         <v/>
       </c>
     </row>
@@ -1513,7 +1515,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Расчёт по листам «Условия» и «График КС»: выполненные работы, погашение аванса, удержание, поступления и расходы. Отрицательный накопленный остаток показывает потребность в собственном или привлечённом финансировании.</t>
+          <t>Помесячные денежные потоки. Колонка P показывает противоречия по срокам и суммам; при них итог сравнения блокируется. Возврат удержания ограничен суммой, накопленной к плановой дате оплаты КС.</t>
         </is>
       </c>
     </row>
@@ -1604,63 +1606,64 @@
         <v>1</v>
       </c>
       <c r="B5" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A5,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A5,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C5" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A5)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A5))</f>
         <v/>
       </c>
       <c r="D5" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A5)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A5))</f>
         <v/>
       </c>
       <c r="E5" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D5/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D5&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D5-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D5/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D5&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D5-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F5" s="20">
-        <f>ROUND($E5,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E5,2))</f>
         <v/>
       </c>
       <c r="G5" s="20">
-        <f>ROUND($B5*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B5*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H5" s="20">
-        <f>ROUND($B5-$F5-$G5,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B5-$F5-$G5,2))</f>
         <v/>
       </c>
       <c r="I5" s="20">
-        <f>IF($A5='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A5='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J5" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A5-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A5-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K5" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A5='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A5='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A5-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L5" s="20">
-        <f>ROUND(SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;($A5+'Условия'!$B$19))*'Условия'!$B$18/100,2)+IF($A5=1,'Условия'!$B$20,0)+IF($A5='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;($A5+'Условия'!$B$19))*'Условия'!$B$18/100,2)+IF($A5=1,'Условия'!$B$20,0)+IF($A5='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M5" s="20">
-        <f>ROUND($I5+$J5+$K5-$L5,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I5+$J5+$K5-$L5,2))</f>
         <v/>
       </c>
       <c r="N5" s="20">
-        <f>ROUND($M5,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($M5,2))</f>
         <v/>
       </c>
       <c r="O5" s="22">
-        <f>IF($N5&lt;0,$A5,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N5&lt;0,$A5,""))</f>
         <v/>
       </c>
       <c r="P5" s="13">
-        <f>IF($H5&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B5&gt;0,'Условия'!$B$16&lt;&gt;"",$A5&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H5&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F5&gt;0.01,$A5&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A5='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A5-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1668,63 +1671,64 @@
         <v>2</v>
       </c>
       <c r="B6" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A6,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A6,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C6" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A6)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A6))</f>
         <v/>
       </c>
       <c r="D6" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A6)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A6))</f>
         <v/>
       </c>
       <c r="E6" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D6/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D6&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D6-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D6/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D6&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D6-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F6" s="20">
-        <f>ROUND($E6-$E5,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E6-$E5,2))</f>
         <v/>
       </c>
       <c r="G6" s="20">
-        <f>ROUND($B6*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B6*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H6" s="20">
-        <f>ROUND($B6-$F6-$G6,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B6-$F6-$G6,2))</f>
         <v/>
       </c>
       <c r="I6" s="20">
-        <f>IF($A6='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A6='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J6" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A6-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A6-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K6" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A6='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A6='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A6-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L6" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A6+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A6=1,'Условия'!$B$20,0)+IF($A6='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A6+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A6=1,'Условия'!$B$20,0)+IF($A6='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M6" s="20">
-        <f>ROUND($I6+$J6+$K6-$L6,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I6+$J6+$K6-$L6,2))</f>
         <v/>
       </c>
       <c r="N6" s="20">
-        <f>ROUND($N5+$M6,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N5+$M6,2))</f>
         <v/>
       </c>
       <c r="O6" s="22">
-        <f>IF($N6&lt;0,$A6,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N6&lt;0,$A6,""))</f>
         <v/>
       </c>
       <c r="P6" s="13">
-        <f>IF($H6&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B6&gt;0,'Условия'!$B$16&lt;&gt;"",$A6&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H6&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F6&gt;0.01,$A6&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A6='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A6-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -1732,63 +1736,64 @@
         <v>3</v>
       </c>
       <c r="B7" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A7,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A7,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C7" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A7)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A7))</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A7)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A7))</f>
         <v/>
       </c>
       <c r="E7" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D7/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D7&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D7-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D7/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D7&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D7-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F7" s="20">
-        <f>ROUND($E7-$E6,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E7-$E6,2))</f>
         <v/>
       </c>
       <c r="G7" s="20">
-        <f>ROUND($B7*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B7*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H7" s="20">
-        <f>ROUND($B7-$F7-$G7,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B7-$F7-$G7,2))</f>
         <v/>
       </c>
       <c r="I7" s="20">
-        <f>IF($A7='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A7='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J7" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A7-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A7-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K7" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A7='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A7='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A7-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L7" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A7+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A7=1,'Условия'!$B$20,0)+IF($A7='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A7+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A7=1,'Условия'!$B$20,0)+IF($A7='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M7" s="20">
-        <f>ROUND($I7+$J7+$K7-$L7,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I7+$J7+$K7-$L7,2))</f>
         <v/>
       </c>
       <c r="N7" s="20">
-        <f>ROUND($N6+$M7,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N6+$M7,2))</f>
         <v/>
       </c>
       <c r="O7" s="22">
-        <f>IF($N7&lt;0,$A7,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N7&lt;0,$A7,""))</f>
         <v/>
       </c>
       <c r="P7" s="13">
-        <f>IF($H7&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B7&gt;0,'Условия'!$B$16&lt;&gt;"",$A7&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H7&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F7&gt;0.01,$A7&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A7='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A7-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -1796,63 +1801,64 @@
         <v>4</v>
       </c>
       <c r="B8" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A8,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A8,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C8" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A8)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A8))</f>
         <v/>
       </c>
       <c r="D8" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A8)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A8))</f>
         <v/>
       </c>
       <c r="E8" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D8/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D8&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D8-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D8/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D8&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D8-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F8" s="20">
-        <f>ROUND($E8-$E7,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E8-$E7,2))</f>
         <v/>
       </c>
       <c r="G8" s="20">
-        <f>ROUND($B8*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B8*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H8" s="20">
-        <f>ROUND($B8-$F8-$G8,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B8-$F8-$G8,2))</f>
         <v/>
       </c>
       <c r="I8" s="20">
-        <f>IF($A8='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A8='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J8" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A8-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A8-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K8" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A8='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A8='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A8-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L8" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A8+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A8=1,'Условия'!$B$20,0)+IF($A8='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A8+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A8=1,'Условия'!$B$20,0)+IF($A8='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M8" s="20">
-        <f>ROUND($I8+$J8+$K8-$L8,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I8+$J8+$K8-$L8,2))</f>
         <v/>
       </c>
       <c r="N8" s="20">
-        <f>ROUND($N7+$M8,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N7+$M8,2))</f>
         <v/>
       </c>
       <c r="O8" s="22">
-        <f>IF($N8&lt;0,$A8,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N8&lt;0,$A8,""))</f>
         <v/>
       </c>
       <c r="P8" s="13">
-        <f>IF($H8&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B8&gt;0,'Условия'!$B$16&lt;&gt;"",$A8&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H8&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F8&gt;0.01,$A8&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A8='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A8-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -1860,63 +1866,64 @@
         <v>5</v>
       </c>
       <c r="B9" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A9,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A9,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C9" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A9)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A9))</f>
         <v/>
       </c>
       <c r="D9" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A9)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A9))</f>
         <v/>
       </c>
       <c r="E9" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D9/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D9&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D9-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D9/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D9&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D9-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F9" s="20">
-        <f>ROUND($E9-$E8,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E9-$E8,2))</f>
         <v/>
       </c>
       <c r="G9" s="20">
-        <f>ROUND($B9*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B9*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H9" s="20">
-        <f>ROUND($B9-$F9-$G9,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B9-$F9-$G9,2))</f>
         <v/>
       </c>
       <c r="I9" s="20">
-        <f>IF($A9='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A9='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J9" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A9-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A9-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K9" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A9='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A9='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A9-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L9" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A9+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A9=1,'Условия'!$B$20,0)+IF($A9='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A9+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A9=1,'Условия'!$B$20,0)+IF($A9='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M9" s="20">
-        <f>ROUND($I9+$J9+$K9-$L9,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I9+$J9+$K9-$L9,2))</f>
         <v/>
       </c>
       <c r="N9" s="20">
-        <f>ROUND($N8+$M9,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N8+$M9,2))</f>
         <v/>
       </c>
       <c r="O9" s="22">
-        <f>IF($N9&lt;0,$A9,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N9&lt;0,$A9,""))</f>
         <v/>
       </c>
       <c r="P9" s="13">
-        <f>IF($H9&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B9&gt;0,'Условия'!$B$16&lt;&gt;"",$A9&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H9&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F9&gt;0.01,$A9&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A9='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A9-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -1924,63 +1931,64 @@
         <v>6</v>
       </c>
       <c r="B10" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A10,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A10,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C10" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A10)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A10))</f>
         <v/>
       </c>
       <c r="D10" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A10)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A10))</f>
         <v/>
       </c>
       <c r="E10" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D10/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D10&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D10-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D10/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D10&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D10-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>ROUND($E10-$E9,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E10-$E9,2))</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f>ROUND($B10*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B10*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H10" s="20">
-        <f>ROUND($B10-$F10-$G10,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B10-$F10-$G10,2))</f>
         <v/>
       </c>
       <c r="I10" s="20">
-        <f>IF($A10='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A10='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J10" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A10-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A10-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K10" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A10='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A10='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A10-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L10" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A10+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A10=1,'Условия'!$B$20,0)+IF($A10='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A10+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A10=1,'Условия'!$B$20,0)+IF($A10='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M10" s="20">
-        <f>ROUND($I10+$J10+$K10-$L10,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I10+$J10+$K10-$L10,2))</f>
         <v/>
       </c>
       <c r="N10" s="20">
-        <f>ROUND($N9+$M10,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N9+$M10,2))</f>
         <v/>
       </c>
       <c r="O10" s="22">
-        <f>IF($N10&lt;0,$A10,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N10&lt;0,$A10,""))</f>
         <v/>
       </c>
       <c r="P10" s="13">
-        <f>IF($H10&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B10&gt;0,'Условия'!$B$16&lt;&gt;"",$A10&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H10&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F10&gt;0.01,$A10&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A10='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A10-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1988,63 +1996,64 @@
         <v>7</v>
       </c>
       <c r="B11" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A11,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A11,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C11" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A11)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A11))</f>
         <v/>
       </c>
       <c r="D11" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A11)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A11))</f>
         <v/>
       </c>
       <c r="E11" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D11/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D11&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D11-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D11/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D11&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D11-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F11" s="20">
-        <f>ROUND($E11-$E10,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E11-$E10,2))</f>
         <v/>
       </c>
       <c r="G11" s="20">
-        <f>ROUND($B11*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B11*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H11" s="20">
-        <f>ROUND($B11-$F11-$G11,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B11-$F11-$G11,2))</f>
         <v/>
       </c>
       <c r="I11" s="20">
-        <f>IF($A11='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A11='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J11" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A11-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A11-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K11" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A11='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A11='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A11-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L11" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A11+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A11=1,'Условия'!$B$20,0)+IF($A11='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A11+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A11=1,'Условия'!$B$20,0)+IF($A11='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M11" s="20">
-        <f>ROUND($I11+$J11+$K11-$L11,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I11+$J11+$K11-$L11,2))</f>
         <v/>
       </c>
       <c r="N11" s="20">
-        <f>ROUND($N10+$M11,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N10+$M11,2))</f>
         <v/>
       </c>
       <c r="O11" s="22">
-        <f>IF($N11&lt;0,$A11,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N11&lt;0,$A11,""))</f>
         <v/>
       </c>
       <c r="P11" s="13">
-        <f>IF($H11&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B11&gt;0,'Условия'!$B$16&lt;&gt;"",$A11&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H11&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F11&gt;0.01,$A11&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A11='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A11-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -2052,63 +2061,64 @@
         <v>8</v>
       </c>
       <c r="B12" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A12,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A12,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C12" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A12)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A12))</f>
         <v/>
       </c>
       <c r="D12" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A12)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A12))</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D12/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D12&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D12-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D12/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D12&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D12-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F12" s="20">
-        <f>ROUND($E12-$E11,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E12-$E11,2))</f>
         <v/>
       </c>
       <c r="G12" s="20">
-        <f>ROUND($B12*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B12*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H12" s="20">
-        <f>ROUND($B12-$F12-$G12,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B12-$F12-$G12,2))</f>
         <v/>
       </c>
       <c r="I12" s="20">
-        <f>IF($A12='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A12='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J12" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A12-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A12-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K12" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A12='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A12='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A12-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L12" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A12+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A12=1,'Условия'!$B$20,0)+IF($A12='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A12+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A12=1,'Условия'!$B$20,0)+IF($A12='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M12" s="20">
-        <f>ROUND($I12+$J12+$K12-$L12,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I12+$J12+$K12-$L12,2))</f>
         <v/>
       </c>
       <c r="N12" s="20">
-        <f>ROUND($N11+$M12,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N11+$M12,2))</f>
         <v/>
       </c>
       <c r="O12" s="22">
-        <f>IF($N12&lt;0,$A12,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N12&lt;0,$A12,""))</f>
         <v/>
       </c>
       <c r="P12" s="13">
-        <f>IF($H12&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B12&gt;0,'Условия'!$B$16&lt;&gt;"",$A12&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H12&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F12&gt;0.01,$A12&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A12='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A12-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -2116,63 +2126,64 @@
         <v>9</v>
       </c>
       <c r="B13" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A13,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A13,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C13" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A13)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A13))</f>
         <v/>
       </c>
       <c r="D13" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A13)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A13))</f>
         <v/>
       </c>
       <c r="E13" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D13/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D13&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D13-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D13/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D13&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D13-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>ROUND($E13-$E12,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E13-$E12,2))</f>
         <v/>
       </c>
       <c r="G13" s="20">
-        <f>ROUND($B13*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B13*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H13" s="20">
-        <f>ROUND($B13-$F13-$G13,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B13-$F13-$G13,2))</f>
         <v/>
       </c>
       <c r="I13" s="20">
-        <f>IF($A13='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A13='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J13" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A13-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A13-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K13" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A13='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A13='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A13-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L13" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A13+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A13=1,'Условия'!$B$20,0)+IF($A13='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A13+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A13=1,'Условия'!$B$20,0)+IF($A13='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M13" s="20">
-        <f>ROUND($I13+$J13+$K13-$L13,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I13+$J13+$K13-$L13,2))</f>
         <v/>
       </c>
       <c r="N13" s="20">
-        <f>ROUND($N12+$M13,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N12+$M13,2))</f>
         <v/>
       </c>
       <c r="O13" s="22">
-        <f>IF($N13&lt;0,$A13,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N13&lt;0,$A13,""))</f>
         <v/>
       </c>
       <c r="P13" s="13">
-        <f>IF($H13&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B13&gt;0,'Условия'!$B$16&lt;&gt;"",$A13&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H13&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F13&gt;0.01,$A13&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A13='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A13-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -2180,63 +2191,64 @@
         <v>10</v>
       </c>
       <c r="B14" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A14,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A14,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C14" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A14)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A14))</f>
         <v/>
       </c>
       <c r="D14" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A14)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A14))</f>
         <v/>
       </c>
       <c r="E14" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D14/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D14&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D14-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D14/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D14&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D14-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F14" s="20">
-        <f>ROUND($E14-$E13,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E14-$E13,2))</f>
         <v/>
       </c>
       <c r="G14" s="20">
-        <f>ROUND($B14*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B14*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H14" s="20">
-        <f>ROUND($B14-$F14-$G14,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B14-$F14-$G14,2))</f>
         <v/>
       </c>
       <c r="I14" s="20">
-        <f>IF($A14='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A14='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J14" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A14-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A14-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K14" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A14='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A14='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A14-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L14" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A14+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A14=1,'Условия'!$B$20,0)+IF($A14='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A14+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A14=1,'Условия'!$B$20,0)+IF($A14='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M14" s="20">
-        <f>ROUND($I14+$J14+$K14-$L14,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I14+$J14+$K14-$L14,2))</f>
         <v/>
       </c>
       <c r="N14" s="20">
-        <f>ROUND($N13+$M14,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N13+$M14,2))</f>
         <v/>
       </c>
       <c r="O14" s="22">
-        <f>IF($N14&lt;0,$A14,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N14&lt;0,$A14,""))</f>
         <v/>
       </c>
       <c r="P14" s="13">
-        <f>IF($H14&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B14&gt;0,'Условия'!$B$16&lt;&gt;"",$A14&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H14&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F14&gt;0.01,$A14&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A14='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A14-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -2244,63 +2256,64 @@
         <v>11</v>
       </c>
       <c r="B15" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A15,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A15,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C15" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A15)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A15))</f>
         <v/>
       </c>
       <c r="D15" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A15)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A15))</f>
         <v/>
       </c>
       <c r="E15" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D15/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D15&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D15-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D15/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D15&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D15-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>ROUND($E15-$E14,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E15-$E14,2))</f>
         <v/>
       </c>
       <c r="G15" s="20">
-        <f>ROUND($B15*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B15*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H15" s="20">
-        <f>ROUND($B15-$F15-$G15,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B15-$F15-$G15,2))</f>
         <v/>
       </c>
       <c r="I15" s="20">
-        <f>IF($A15='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A15='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J15" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A15-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A15-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K15" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A15='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A15='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A15-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L15" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A15+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A15=1,'Условия'!$B$20,0)+IF($A15='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A15+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A15=1,'Условия'!$B$20,0)+IF($A15='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M15" s="20">
-        <f>ROUND($I15+$J15+$K15-$L15,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I15+$J15+$K15-$L15,2))</f>
         <v/>
       </c>
       <c r="N15" s="20">
-        <f>ROUND($N14+$M15,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N14+$M15,2))</f>
         <v/>
       </c>
       <c r="O15" s="22">
-        <f>IF($N15&lt;0,$A15,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N15&lt;0,$A15,""))</f>
         <v/>
       </c>
       <c r="P15" s="13">
-        <f>IF($H15&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B15&gt;0,'Условия'!$B$16&lt;&gt;"",$A15&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H15&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F15&gt;0.01,$A15&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A15='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A15-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -2308,63 +2321,64 @@
         <v>12</v>
       </c>
       <c r="B16" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A16,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A16,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A16)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A16))</f>
         <v/>
       </c>
       <c r="D16" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A16)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A16))</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D16/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D16&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D16-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D16/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D16&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D16-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f>ROUND($E16-$E15,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E16-$E15,2))</f>
         <v/>
       </c>
       <c r="G16" s="20">
-        <f>ROUND($B16*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B16*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H16" s="20">
-        <f>ROUND($B16-$F16-$G16,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B16-$F16-$G16,2))</f>
         <v/>
       </c>
       <c r="I16" s="20">
-        <f>IF($A16='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A16='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J16" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A16-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A16-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K16" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A16='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A16='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A16-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L16" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A16+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A16=1,'Условия'!$B$20,0)+IF($A16='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A16+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A16=1,'Условия'!$B$20,0)+IF($A16='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M16" s="20">
-        <f>ROUND($I16+$J16+$K16-$L16,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I16+$J16+$K16-$L16,2))</f>
         <v/>
       </c>
       <c r="N16" s="20">
-        <f>ROUND($N15+$M16,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N15+$M16,2))</f>
         <v/>
       </c>
       <c r="O16" s="22">
-        <f>IF($N16&lt;0,$A16,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N16&lt;0,$A16,""))</f>
         <v/>
       </c>
       <c r="P16" s="13">
-        <f>IF($H16&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B16&gt;0,'Условия'!$B$16&lt;&gt;"",$A16&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H16&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F16&gt;0.01,$A16&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A16='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A16-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -2372,63 +2386,64 @@
         <v>13</v>
       </c>
       <c r="B17" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A17,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A17,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A17)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A17))</f>
         <v/>
       </c>
       <c r="D17" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A17)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A17))</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D17/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D17&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D17-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D17/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D17&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D17-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F17" s="20">
-        <f>ROUND($E17-$E16,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E17-$E16,2))</f>
         <v/>
       </c>
       <c r="G17" s="20">
-        <f>ROUND($B17*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B17*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H17" s="20">
-        <f>ROUND($B17-$F17-$G17,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B17-$F17-$G17,2))</f>
         <v/>
       </c>
       <c r="I17" s="20">
-        <f>IF($A17='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A17='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J17" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A17-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A17-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K17" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A17='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A17='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A17-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L17" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A17+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A17=1,'Условия'!$B$20,0)+IF($A17='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A17+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A17=1,'Условия'!$B$20,0)+IF($A17='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M17" s="20">
-        <f>ROUND($I17+$J17+$K17-$L17,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I17+$J17+$K17-$L17,2))</f>
         <v/>
       </c>
       <c r="N17" s="20">
-        <f>ROUND($N16+$M17,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N16+$M17,2))</f>
         <v/>
       </c>
       <c r="O17" s="22">
-        <f>IF($N17&lt;0,$A17,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N17&lt;0,$A17,""))</f>
         <v/>
       </c>
       <c r="P17" s="13">
-        <f>IF($H17&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B17&gt;0,'Условия'!$B$16&lt;&gt;"",$A17&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H17&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F17&gt;0.01,$A17&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A17='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A17-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -2436,63 +2451,64 @@
         <v>14</v>
       </c>
       <c r="B18" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A18,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A18,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C18" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A18)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A18))</f>
         <v/>
       </c>
       <c r="D18" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A18)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A18))</f>
         <v/>
       </c>
       <c r="E18" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D18/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D18&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D18-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D18/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D18&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D18-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F18" s="20">
-        <f>ROUND($E18-$E17,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E18-$E17,2))</f>
         <v/>
       </c>
       <c r="G18" s="20">
-        <f>ROUND($B18*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B18*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H18" s="20">
-        <f>ROUND($B18-$F18-$G18,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B18-$F18-$G18,2))</f>
         <v/>
       </c>
       <c r="I18" s="20">
-        <f>IF($A18='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A18='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J18" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A18-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A18-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K18" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A18='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A18='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A18-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L18" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A18+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A18=1,'Условия'!$B$20,0)+IF($A18='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A18+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A18=1,'Условия'!$B$20,0)+IF($A18='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M18" s="20">
-        <f>ROUND($I18+$J18+$K18-$L18,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I18+$J18+$K18-$L18,2))</f>
         <v/>
       </c>
       <c r="N18" s="20">
-        <f>ROUND($N17+$M18,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N17+$M18,2))</f>
         <v/>
       </c>
       <c r="O18" s="22">
-        <f>IF($N18&lt;0,$A18,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N18&lt;0,$A18,""))</f>
         <v/>
       </c>
       <c r="P18" s="13">
-        <f>IF($H18&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B18&gt;0,'Условия'!$B$16&lt;&gt;"",$A18&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H18&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F18&gt;0.01,$A18&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A18='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A18-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -2500,63 +2516,64 @@
         <v>15</v>
       </c>
       <c r="B19" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A19,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A19,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A19)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A19))</f>
         <v/>
       </c>
       <c r="D19" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A19)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A19))</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D19/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D19&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D19-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D19/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D19&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D19-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F19" s="20">
-        <f>ROUND($E19-$E18,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E19-$E18,2))</f>
         <v/>
       </c>
       <c r="G19" s="20">
-        <f>ROUND($B19*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B19*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>ROUND($B19-$F19-$G19,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B19-$F19-$G19,2))</f>
         <v/>
       </c>
       <c r="I19" s="20">
-        <f>IF($A19='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A19='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J19" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A19-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A19-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K19" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A19='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A19='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A19-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L19" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A19+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A19=1,'Условия'!$B$20,0)+IF($A19='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A19+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A19=1,'Условия'!$B$20,0)+IF($A19='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M19" s="20">
-        <f>ROUND($I19+$J19+$K19-$L19,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I19+$J19+$K19-$L19,2))</f>
         <v/>
       </c>
       <c r="N19" s="20">
-        <f>ROUND($N18+$M19,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N18+$M19,2))</f>
         <v/>
       </c>
       <c r="O19" s="22">
-        <f>IF($N19&lt;0,$A19,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N19&lt;0,$A19,""))</f>
         <v/>
       </c>
       <c r="P19" s="13">
-        <f>IF($H19&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B19&gt;0,'Условия'!$B$16&lt;&gt;"",$A19&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H19&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F19&gt;0.01,$A19&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A19='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A19-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -2564,63 +2581,64 @@
         <v>16</v>
       </c>
       <c r="B20" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A20,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A20,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C20" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A20)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A20))</f>
         <v/>
       </c>
       <c r="D20" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A20)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A20))</f>
         <v/>
       </c>
       <c r="E20" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D20/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D20&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D20-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D20/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D20&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D20-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F20" s="20">
-        <f>ROUND($E20-$E19,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E20-$E19,2))</f>
         <v/>
       </c>
       <c r="G20" s="20">
-        <f>ROUND($B20*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B20*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>ROUND($B20-$F20-$G20,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B20-$F20-$G20,2))</f>
         <v/>
       </c>
       <c r="I20" s="20">
-        <f>IF($A20='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A20='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J20" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A20-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A20-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K20" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A20='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A20='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A20-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L20" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A20+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A20=1,'Условия'!$B$20,0)+IF($A20='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A20+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A20=1,'Условия'!$B$20,0)+IF($A20='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M20" s="20">
-        <f>ROUND($I20+$J20+$K20-$L20,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I20+$J20+$K20-$L20,2))</f>
         <v/>
       </c>
       <c r="N20" s="20">
-        <f>ROUND($N19+$M20,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N19+$M20,2))</f>
         <v/>
       </c>
       <c r="O20" s="22">
-        <f>IF($N20&lt;0,$A20,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N20&lt;0,$A20,""))</f>
         <v/>
       </c>
       <c r="P20" s="13">
-        <f>IF($H20&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B20&gt;0,'Условия'!$B$16&lt;&gt;"",$A20&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H20&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F20&gt;0.01,$A20&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A20='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A20-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -2628,63 +2646,64 @@
         <v>17</v>
       </c>
       <c r="B21" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A21,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A21,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A21)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A21))</f>
         <v/>
       </c>
       <c r="D21" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A21)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A21))</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D21/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D21&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D21-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D21/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D21&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D21-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F21" s="20">
-        <f>ROUND($E21-$E20,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E21-$E20,2))</f>
         <v/>
       </c>
       <c r="G21" s="20">
-        <f>ROUND($B21*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B21*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H21" s="20">
-        <f>ROUND($B21-$F21-$G21,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B21-$F21-$G21,2))</f>
         <v/>
       </c>
       <c r="I21" s="20">
-        <f>IF($A21='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A21='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J21" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A21-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A21-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K21" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A21='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A21='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A21-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L21" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A21+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A21=1,'Условия'!$B$20,0)+IF($A21='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A21+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A21=1,'Условия'!$B$20,0)+IF($A21='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M21" s="20">
-        <f>ROUND($I21+$J21+$K21-$L21,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I21+$J21+$K21-$L21,2))</f>
         <v/>
       </c>
       <c r="N21" s="20">
-        <f>ROUND($N20+$M21,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N20+$M21,2))</f>
         <v/>
       </c>
       <c r="O21" s="22">
-        <f>IF($N21&lt;0,$A21,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N21&lt;0,$A21,""))</f>
         <v/>
       </c>
       <c r="P21" s="13">
-        <f>IF($H21&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B21&gt;0,'Условия'!$B$16&lt;&gt;"",$A21&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H21&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F21&gt;0.01,$A21&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A21='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A21-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -2692,63 +2711,64 @@
         <v>18</v>
       </c>
       <c r="B22" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A22,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A22,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C22" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A22)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A22))</f>
         <v/>
       </c>
       <c r="D22" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A22)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A22))</f>
         <v/>
       </c>
       <c r="E22" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D22/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D22&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D22-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D22/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D22&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D22-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F22" s="20">
-        <f>ROUND($E22-$E21,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E22-$E21,2))</f>
         <v/>
       </c>
       <c r="G22" s="20">
-        <f>ROUND($B22*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B22*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H22" s="20">
-        <f>ROUND($B22-$F22-$G22,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B22-$F22-$G22,2))</f>
         <v/>
       </c>
       <c r="I22" s="20">
-        <f>IF($A22='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A22='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J22" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A22-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A22-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K22" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A22='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A22='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A22-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L22" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A22+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A22=1,'Условия'!$B$20,0)+IF($A22='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A22+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A22=1,'Условия'!$B$20,0)+IF($A22='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M22" s="20">
-        <f>ROUND($I22+$J22+$K22-$L22,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I22+$J22+$K22-$L22,2))</f>
         <v/>
       </c>
       <c r="N22" s="20">
-        <f>ROUND($N21+$M22,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N21+$M22,2))</f>
         <v/>
       </c>
       <c r="O22" s="22">
-        <f>IF($N22&lt;0,$A22,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N22&lt;0,$A22,""))</f>
         <v/>
       </c>
       <c r="P22" s="13">
-        <f>IF($H22&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B22&gt;0,'Условия'!$B$16&lt;&gt;"",$A22&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H22&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F22&gt;0.01,$A22&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A22='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A22-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -2756,63 +2776,64 @@
         <v>19</v>
       </c>
       <c r="B23" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A23,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A23,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A23)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A23))</f>
         <v/>
       </c>
       <c r="D23" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A23)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A23))</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D23/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D23&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D23-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D23/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D23&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D23-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F23" s="20">
-        <f>ROUND($E23-$E22,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E23-$E22,2))</f>
         <v/>
       </c>
       <c r="G23" s="20">
-        <f>ROUND($B23*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B23*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H23" s="20">
-        <f>ROUND($B23-$F23-$G23,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B23-$F23-$G23,2))</f>
         <v/>
       </c>
       <c r="I23" s="20">
-        <f>IF($A23='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A23='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J23" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A23-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A23-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K23" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A23='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A23='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A23-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L23" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A23+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A23=1,'Условия'!$B$20,0)+IF($A23='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A23+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A23=1,'Условия'!$B$20,0)+IF($A23='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M23" s="20">
-        <f>ROUND($I23+$J23+$K23-$L23,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I23+$J23+$K23-$L23,2))</f>
         <v/>
       </c>
       <c r="N23" s="20">
-        <f>ROUND($N22+$M23,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N22+$M23,2))</f>
         <v/>
       </c>
       <c r="O23" s="22">
-        <f>IF($N23&lt;0,$A23,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N23&lt;0,$A23,""))</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IF($H23&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B23&gt;0,'Условия'!$B$16&lt;&gt;"",$A23&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H23&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F23&gt;0.01,$A23&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A23='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A23-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -2820,63 +2841,64 @@
         <v>20</v>
       </c>
       <c r="B24" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A24,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A24,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C24" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A24)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A24))</f>
         <v/>
       </c>
       <c r="D24" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A24)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A24))</f>
         <v/>
       </c>
       <c r="E24" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D24/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D24&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D24-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D24/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D24&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D24-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F24" s="20">
-        <f>ROUND($E24-$E23,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E24-$E23,2))</f>
         <v/>
       </c>
       <c r="G24" s="20">
-        <f>ROUND($B24*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B24*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H24" s="20">
-        <f>ROUND($B24-$F24-$G24,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B24-$F24-$G24,2))</f>
         <v/>
       </c>
       <c r="I24" s="20">
-        <f>IF($A24='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A24='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J24" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A24-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A24-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K24" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A24='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A24='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A24-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L24" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A24+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A24=1,'Условия'!$B$20,0)+IF($A24='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A24+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A24=1,'Условия'!$B$20,0)+IF($A24='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M24" s="20">
-        <f>ROUND($I24+$J24+$K24-$L24,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I24+$J24+$K24-$L24,2))</f>
         <v/>
       </c>
       <c r="N24" s="20">
-        <f>ROUND($N23+$M24,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N23+$M24,2))</f>
         <v/>
       </c>
       <c r="O24" s="22">
-        <f>IF($N24&lt;0,$A24,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N24&lt;0,$A24,""))</f>
         <v/>
       </c>
       <c r="P24" s="13">
-        <f>IF($H24&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B24&gt;0,'Условия'!$B$16&lt;&gt;"",$A24&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H24&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F24&gt;0.01,$A24&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A24='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A24-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -2884,63 +2906,64 @@
         <v>21</v>
       </c>
       <c r="B25" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A25,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A25,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A25)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A25))</f>
         <v/>
       </c>
       <c r="D25" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A25)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A25))</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D25/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D25&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D25-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D25/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D25&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D25-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F25" s="20">
-        <f>ROUND($E25-$E24,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E25-$E24,2))</f>
         <v/>
       </c>
       <c r="G25" s="20">
-        <f>ROUND($B25*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B25*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H25" s="20">
-        <f>ROUND($B25-$F25-$G25,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B25-$F25-$G25,2))</f>
         <v/>
       </c>
       <c r="I25" s="20">
-        <f>IF($A25='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A25='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J25" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A25-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A25-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K25" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A25='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A25='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A25-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L25" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A25+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A25=1,'Условия'!$B$20,0)+IF($A25='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A25+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A25=1,'Условия'!$B$20,0)+IF($A25='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M25" s="20">
-        <f>ROUND($I25+$J25+$K25-$L25,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I25+$J25+$K25-$L25,2))</f>
         <v/>
       </c>
       <c r="N25" s="20">
-        <f>ROUND($N24+$M25,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N24+$M25,2))</f>
         <v/>
       </c>
       <c r="O25" s="22">
-        <f>IF($N25&lt;0,$A25,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N25&lt;0,$A25,""))</f>
         <v/>
       </c>
       <c r="P25" s="13">
-        <f>IF($H25&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B25&gt;0,'Условия'!$B$16&lt;&gt;"",$A25&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H25&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F25&gt;0.01,$A25&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A25='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A25-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -2948,63 +2971,64 @@
         <v>22</v>
       </c>
       <c r="B26" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A26,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A26,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C26" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A26)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A26))</f>
         <v/>
       </c>
       <c r="D26" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A26)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A26))</f>
         <v/>
       </c>
       <c r="E26" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D26/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D26&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D26-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D26/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D26&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D26-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F26" s="20">
-        <f>ROUND($E26-$E25,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E26-$E25,2))</f>
         <v/>
       </c>
       <c r="G26" s="20">
-        <f>ROUND($B26*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B26*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H26" s="20">
-        <f>ROUND($B26-$F26-$G26,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B26-$F26-$G26,2))</f>
         <v/>
       </c>
       <c r="I26" s="20">
-        <f>IF($A26='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A26='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J26" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A26-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A26-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K26" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A26='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A26='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A26-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L26" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A26+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A26=1,'Условия'!$B$20,0)+IF($A26='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A26+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A26=1,'Условия'!$B$20,0)+IF($A26='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M26" s="20">
-        <f>ROUND($I26+$J26+$K26-$L26,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I26+$J26+$K26-$L26,2))</f>
         <v/>
       </c>
       <c r="N26" s="20">
-        <f>ROUND($N25+$M26,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N25+$M26,2))</f>
         <v/>
       </c>
       <c r="O26" s="22">
-        <f>IF($N26&lt;0,$A26,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N26&lt;0,$A26,""))</f>
         <v/>
       </c>
       <c r="P26" s="13">
-        <f>IF($H26&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B26&gt;0,'Условия'!$B$16&lt;&gt;"",$A26&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H26&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F26&gt;0.01,$A26&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A26='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A26-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -3012,63 +3036,64 @@
         <v>23</v>
       </c>
       <c r="B27" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A27,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A27,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C27" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A27)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A27))</f>
         <v/>
       </c>
       <c r="D27" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A27)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A27))</f>
         <v/>
       </c>
       <c r="E27" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D27/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D27&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D27-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D27/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D27&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D27-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F27" s="20">
-        <f>ROUND($E27-$E26,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E27-$E26,2))</f>
         <v/>
       </c>
       <c r="G27" s="20">
-        <f>ROUND($B27*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B27*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H27" s="20">
-        <f>ROUND($B27-$F27-$G27,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B27-$F27-$G27,2))</f>
         <v/>
       </c>
       <c r="I27" s="20">
-        <f>IF($A27='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A27='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J27" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A27-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A27-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K27" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A27='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A27='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A27-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L27" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A27+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A27=1,'Условия'!$B$20,0)+IF($A27='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A27+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A27=1,'Условия'!$B$20,0)+IF($A27='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M27" s="20">
-        <f>ROUND($I27+$J27+$K27-$L27,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I27+$J27+$K27-$L27,2))</f>
         <v/>
       </c>
       <c r="N27" s="20">
-        <f>ROUND($N26+$M27,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N26+$M27,2))</f>
         <v/>
       </c>
       <c r="O27" s="22">
-        <f>IF($N27&lt;0,$A27,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N27&lt;0,$A27,""))</f>
         <v/>
       </c>
       <c r="P27" s="13">
-        <f>IF($H27&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B27&gt;0,'Условия'!$B$16&lt;&gt;"",$A27&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H27&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F27&gt;0.01,$A27&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A27='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A27-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -3076,63 +3101,64 @@
         <v>24</v>
       </c>
       <c r="B28" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A28,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A28,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C28" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A28)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A28))</f>
         <v/>
       </c>
       <c r="D28" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A28)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A28))</f>
         <v/>
       </c>
       <c r="E28" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D28/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D28&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D28-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D28/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D28&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D28-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F28" s="20">
-        <f>ROUND($E28-$E27,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E28-$E27,2))</f>
         <v/>
       </c>
       <c r="G28" s="20">
-        <f>ROUND($B28*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B28*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H28" s="20">
-        <f>ROUND($B28-$F28-$G28,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B28-$F28-$G28,2))</f>
         <v/>
       </c>
       <c r="I28" s="20">
-        <f>IF($A28='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A28='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J28" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A28-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A28-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K28" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A28='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A28='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A28-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L28" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A28+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A28=1,'Условия'!$B$20,0)+IF($A28='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A28+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A28=1,'Условия'!$B$20,0)+IF($A28='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M28" s="20">
-        <f>ROUND($I28+$J28+$K28-$L28,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I28+$J28+$K28-$L28,2))</f>
         <v/>
       </c>
       <c r="N28" s="20">
-        <f>ROUND($N27+$M28,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N27+$M28,2))</f>
         <v/>
       </c>
       <c r="O28" s="22">
-        <f>IF($N28&lt;0,$A28,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N28&lt;0,$A28,""))</f>
         <v/>
       </c>
       <c r="P28" s="13">
-        <f>IF($H28&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B28&gt;0,'Условия'!$B$16&lt;&gt;"",$A28&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H28&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F28&gt;0.01,$A28&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A28='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A28-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -3140,63 +3166,64 @@
         <v>25</v>
       </c>
       <c r="B29" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A29,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A29,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C29" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A29)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A29))</f>
         <v/>
       </c>
       <c r="D29" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A29)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A29))</f>
         <v/>
       </c>
       <c r="E29" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D29/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D29&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D29-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D29/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D29&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D29-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F29" s="20">
-        <f>ROUND($E29-$E28,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E29-$E28,2))</f>
         <v/>
       </c>
       <c r="G29" s="20">
-        <f>ROUND($B29*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B29*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H29" s="20">
-        <f>ROUND($B29-$F29-$G29,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B29-$F29-$G29,2))</f>
         <v/>
       </c>
       <c r="I29" s="20">
-        <f>IF($A29='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A29='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J29" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A29-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A29-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K29" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A29='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A29='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A29-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L29" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A29+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A29=1,'Условия'!$B$20,0)+IF($A29='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A29+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A29=1,'Условия'!$B$20,0)+IF($A29='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M29" s="20">
-        <f>ROUND($I29+$J29+$K29-$L29,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I29+$J29+$K29-$L29,2))</f>
         <v/>
       </c>
       <c r="N29" s="20">
-        <f>ROUND($N28+$M29,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N28+$M29,2))</f>
         <v/>
       </c>
       <c r="O29" s="22">
-        <f>IF($N29&lt;0,$A29,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N29&lt;0,$A29,""))</f>
         <v/>
       </c>
       <c r="P29" s="13">
-        <f>IF($H29&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B29&gt;0,'Условия'!$B$16&lt;&gt;"",$A29&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H29&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F29&gt;0.01,$A29&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A29='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A29-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -3204,63 +3231,64 @@
         <v>26</v>
       </c>
       <c r="B30" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A30,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A30,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A30)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A30))</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A30)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A30))</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D30/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D30&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D30-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D30/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D30&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D30-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F30" s="20">
-        <f>ROUND($E30-$E29,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E30-$E29,2))</f>
         <v/>
       </c>
       <c r="G30" s="20">
-        <f>ROUND($B30*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B30*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H30" s="20">
-        <f>ROUND($B30-$F30-$G30,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B30-$F30-$G30,2))</f>
         <v/>
       </c>
       <c r="I30" s="20">
-        <f>IF($A30='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A30='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J30" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A30-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A30-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K30" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A30='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A30='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A30-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L30" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A30+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A30=1,'Условия'!$B$20,0)+IF($A30='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A30+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A30=1,'Условия'!$B$20,0)+IF($A30='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M30" s="20">
-        <f>ROUND($I30+$J30+$K30-$L30,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I30+$J30+$K30-$L30,2))</f>
         <v/>
       </c>
       <c r="N30" s="20">
-        <f>ROUND($N29+$M30,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N29+$M30,2))</f>
         <v/>
       </c>
       <c r="O30" s="22">
-        <f>IF($N30&lt;0,$A30,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N30&lt;0,$A30,""))</f>
         <v/>
       </c>
       <c r="P30" s="13">
-        <f>IF($H30&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B30&gt;0,'Условия'!$B$16&lt;&gt;"",$A30&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H30&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F30&gt;0.01,$A30&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A30='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A30-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -3268,63 +3296,64 @@
         <v>27</v>
       </c>
       <c r="B31" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A31,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A31,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C31" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A31)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A31))</f>
         <v/>
       </c>
       <c r="D31" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A31)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A31))</f>
         <v/>
       </c>
       <c r="E31" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D31/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D31&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D31-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D31/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D31&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D31-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F31" s="20">
-        <f>ROUND($E31-$E30,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E31-$E30,2))</f>
         <v/>
       </c>
       <c r="G31" s="20">
-        <f>ROUND($B31*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B31*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H31" s="20">
-        <f>ROUND($B31-$F31-$G31,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B31-$F31-$G31,2))</f>
         <v/>
       </c>
       <c r="I31" s="20">
-        <f>IF($A31='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A31='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J31" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A31-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A31-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K31" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A31='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A31='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A31-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L31" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A31+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A31=1,'Условия'!$B$20,0)+IF($A31='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A31+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A31=1,'Условия'!$B$20,0)+IF($A31='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M31" s="20">
-        <f>ROUND($I31+$J31+$K31-$L31,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I31+$J31+$K31-$L31,2))</f>
         <v/>
       </c>
       <c r="N31" s="20">
-        <f>ROUND($N30+$M31,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N30+$M31,2))</f>
         <v/>
       </c>
       <c r="O31" s="22">
-        <f>IF($N31&lt;0,$A31,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N31&lt;0,$A31,""))</f>
         <v/>
       </c>
       <c r="P31" s="13">
-        <f>IF($H31&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B31&gt;0,'Условия'!$B$16&lt;&gt;"",$A31&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H31&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F31&gt;0.01,$A31&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A31='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A31-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -3332,63 +3361,64 @@
         <v>28</v>
       </c>
       <c r="B32" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A32,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A32,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A32)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A32))</f>
         <v/>
       </c>
       <c r="D32" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A32)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A32))</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D32/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D32&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D32-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D32/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D32&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D32-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F32" s="20">
-        <f>ROUND($E32-$E31,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E32-$E31,2))</f>
         <v/>
       </c>
       <c r="G32" s="20">
-        <f>ROUND($B32*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B32*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H32" s="20">
-        <f>ROUND($B32-$F32-$G32,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B32-$F32-$G32,2))</f>
         <v/>
       </c>
       <c r="I32" s="20">
-        <f>IF($A32='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A32='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J32" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A32-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A32-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K32" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A32='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A32='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A32-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L32" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A32+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A32=1,'Условия'!$B$20,0)+IF($A32='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A32+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A32=1,'Условия'!$B$20,0)+IF($A32='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M32" s="20">
-        <f>ROUND($I32+$J32+$K32-$L32,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I32+$J32+$K32-$L32,2))</f>
         <v/>
       </c>
       <c r="N32" s="20">
-        <f>ROUND($N31+$M32,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N31+$M32,2))</f>
         <v/>
       </c>
       <c r="O32" s="22">
-        <f>IF($N32&lt;0,$A32,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N32&lt;0,$A32,""))</f>
         <v/>
       </c>
       <c r="P32" s="13">
-        <f>IF($H32&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B32&gt;0,'Условия'!$B$16&lt;&gt;"",$A32&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H32&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F32&gt;0.01,$A32&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A32='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A32-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -3396,63 +3426,64 @@
         <v>29</v>
       </c>
       <c r="B33" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A33,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A33,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C33" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A33)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A33))</f>
         <v/>
       </c>
       <c r="D33" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A33)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A33))</f>
         <v/>
       </c>
       <c r="E33" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D33/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D33&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D33-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D33/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D33&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D33-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F33" s="20">
-        <f>ROUND($E33-$E32,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E33-$E32,2))</f>
         <v/>
       </c>
       <c r="G33" s="20">
-        <f>ROUND($B33*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B33*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H33" s="20">
-        <f>ROUND($B33-$F33-$G33,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B33-$F33-$G33,2))</f>
         <v/>
       </c>
       <c r="I33" s="20">
-        <f>IF($A33='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A33='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J33" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A33-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A33-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K33" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A33='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A33='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A33-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L33" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A33+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A33=1,'Условия'!$B$20,0)+IF($A33='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A33+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A33=1,'Условия'!$B$20,0)+IF($A33='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M33" s="20">
-        <f>ROUND($I33+$J33+$K33-$L33,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I33+$J33+$K33-$L33,2))</f>
         <v/>
       </c>
       <c r="N33" s="20">
-        <f>ROUND($N32+$M33,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N32+$M33,2))</f>
         <v/>
       </c>
       <c r="O33" s="22">
-        <f>IF($N33&lt;0,$A33,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N33&lt;0,$A33,""))</f>
         <v/>
       </c>
       <c r="P33" s="13">
-        <f>IF($H33&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B33&gt;0,'Условия'!$B$16&lt;&gt;"",$A33&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H33&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F33&gt;0.01,$A33&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A33='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A33-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -3460,63 +3491,64 @@
         <v>30</v>
       </c>
       <c r="B34" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A34,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A34,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A34)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A34))</f>
         <v/>
       </c>
       <c r="D34" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A34)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A34))</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D34/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D34&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D34-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D34/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D34&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D34-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F34" s="20">
-        <f>ROUND($E34-$E33,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E34-$E33,2))</f>
         <v/>
       </c>
       <c r="G34" s="20">
-        <f>ROUND($B34*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B34*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H34" s="20">
-        <f>ROUND($B34-$F34-$G34,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B34-$F34-$G34,2))</f>
         <v/>
       </c>
       <c r="I34" s="20">
-        <f>IF($A34='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A34='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J34" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A34-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A34-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K34" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A34='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A34='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A34-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L34" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A34+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A34=1,'Условия'!$B$20,0)+IF($A34='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A34+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A34=1,'Условия'!$B$20,0)+IF($A34='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M34" s="20">
-        <f>ROUND($I34+$J34+$K34-$L34,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I34+$J34+$K34-$L34,2))</f>
         <v/>
       </c>
       <c r="N34" s="20">
-        <f>ROUND($N33+$M34,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N33+$M34,2))</f>
         <v/>
       </c>
       <c r="O34" s="22">
-        <f>IF($N34&lt;0,$A34,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N34&lt;0,$A34,""))</f>
         <v/>
       </c>
       <c r="P34" s="13">
-        <f>IF($H34&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B34&gt;0,'Условия'!$B$16&lt;&gt;"",$A34&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H34&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F34&gt;0.01,$A34&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A34='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A34-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -3524,63 +3556,64 @@
         <v>31</v>
       </c>
       <c r="B35" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A35,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A35,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C35" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A35)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A35))</f>
         <v/>
       </c>
       <c r="D35" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A35)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A35))</f>
         <v/>
       </c>
       <c r="E35" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D35/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D35&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D35-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D35/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D35&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D35-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F35" s="20">
-        <f>ROUND($E35-$E34,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E35-$E34,2))</f>
         <v/>
       </c>
       <c r="G35" s="20">
-        <f>ROUND($B35*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B35*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H35" s="20">
-        <f>ROUND($B35-$F35-$G35,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B35-$F35-$G35,2))</f>
         <v/>
       </c>
       <c r="I35" s="20">
-        <f>IF($A35='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A35='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J35" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A35-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A35-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K35" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A35='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A35='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A35-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L35" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A35+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A35=1,'Условия'!$B$20,0)+IF($A35='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A35+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A35=1,'Условия'!$B$20,0)+IF($A35='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M35" s="20">
-        <f>ROUND($I35+$J35+$K35-$L35,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I35+$J35+$K35-$L35,2))</f>
         <v/>
       </c>
       <c r="N35" s="20">
-        <f>ROUND($N34+$M35,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N34+$M35,2))</f>
         <v/>
       </c>
       <c r="O35" s="22">
-        <f>IF($N35&lt;0,$A35,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N35&lt;0,$A35,""))</f>
         <v/>
       </c>
       <c r="P35" s="13">
-        <f>IF($H35&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B35&gt;0,'Условия'!$B$16&lt;&gt;"",$A35&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H35&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F35&gt;0.01,$A35&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A35='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A35-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -3588,63 +3621,64 @@
         <v>32</v>
       </c>
       <c r="B36" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A36,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A36,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A36)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A36))</f>
         <v/>
       </c>
       <c r="D36" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A36)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A36))</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D36/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D36&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D36-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D36/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D36&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D36-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F36" s="20">
-        <f>ROUND($E36-$E35,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E36-$E35,2))</f>
         <v/>
       </c>
       <c r="G36" s="20">
-        <f>ROUND($B36*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B36*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H36" s="20">
-        <f>ROUND($B36-$F36-$G36,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B36-$F36-$G36,2))</f>
         <v/>
       </c>
       <c r="I36" s="20">
-        <f>IF($A36='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A36='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J36" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A36-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A36-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K36" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A36='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A36='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A36-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L36" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A36+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A36=1,'Условия'!$B$20,0)+IF($A36='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A36+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A36=1,'Условия'!$B$20,0)+IF($A36='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M36" s="20">
-        <f>ROUND($I36+$J36+$K36-$L36,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I36+$J36+$K36-$L36,2))</f>
         <v/>
       </c>
       <c r="N36" s="20">
-        <f>ROUND($N35+$M36,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N35+$M36,2))</f>
         <v/>
       </c>
       <c r="O36" s="22">
-        <f>IF($N36&lt;0,$A36,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N36&lt;0,$A36,""))</f>
         <v/>
       </c>
       <c r="P36" s="13">
-        <f>IF($H36&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B36&gt;0,'Условия'!$B$16&lt;&gt;"",$A36&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H36&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F36&gt;0.01,$A36&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A36='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A36-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -3652,63 +3686,64 @@
         <v>33</v>
       </c>
       <c r="B37" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A37,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A37,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C37" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A37)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A37))</f>
         <v/>
       </c>
       <c r="D37" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A37)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A37))</f>
         <v/>
       </c>
       <c r="E37" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D37/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D37&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D37-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D37/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D37&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D37-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F37" s="20">
-        <f>ROUND($E37-$E36,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E37-$E36,2))</f>
         <v/>
       </c>
       <c r="G37" s="20">
-        <f>ROUND($B37*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B37*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H37" s="20">
-        <f>ROUND($B37-$F37-$G37,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B37-$F37-$G37,2))</f>
         <v/>
       </c>
       <c r="I37" s="20">
-        <f>IF($A37='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A37='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J37" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A37-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A37-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K37" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A37='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A37='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A37-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L37" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A37+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A37=1,'Условия'!$B$20,0)+IF($A37='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A37+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A37=1,'Условия'!$B$20,0)+IF($A37='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M37" s="20">
-        <f>ROUND($I37+$J37+$K37-$L37,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I37+$J37+$K37-$L37,2))</f>
         <v/>
       </c>
       <c r="N37" s="20">
-        <f>ROUND($N36+$M37,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N36+$M37,2))</f>
         <v/>
       </c>
       <c r="O37" s="22">
-        <f>IF($N37&lt;0,$A37,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N37&lt;0,$A37,""))</f>
         <v/>
       </c>
       <c r="P37" s="13">
-        <f>IF($H37&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B37&gt;0,'Условия'!$B$16&lt;&gt;"",$A37&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H37&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F37&gt;0.01,$A37&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A37='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A37-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -3716,63 +3751,64 @@
         <v>34</v>
       </c>
       <c r="B38" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A38,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A38,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C38" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A38)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A38))</f>
         <v/>
       </c>
       <c r="D38" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A38)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A38))</f>
         <v/>
       </c>
       <c r="E38" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D38/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D38&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D38-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D38/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D38&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D38-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F38" s="20">
-        <f>ROUND($E38-$E37,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E38-$E37,2))</f>
         <v/>
       </c>
       <c r="G38" s="20">
-        <f>ROUND($B38*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B38*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H38" s="20">
-        <f>ROUND($B38-$F38-$G38,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B38-$F38-$G38,2))</f>
         <v/>
       </c>
       <c r="I38" s="20">
-        <f>IF($A38='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A38='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J38" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A38-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A38-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K38" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A38='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A38='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A38-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L38" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A38+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A38=1,'Условия'!$B$20,0)+IF($A38='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A38+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A38=1,'Условия'!$B$20,0)+IF($A38='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M38" s="20">
-        <f>ROUND($I38+$J38+$K38-$L38,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I38+$J38+$K38-$L38,2))</f>
         <v/>
       </c>
       <c r="N38" s="20">
-        <f>ROUND($N37+$M38,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N37+$M38,2))</f>
         <v/>
       </c>
       <c r="O38" s="22">
-        <f>IF($N38&lt;0,$A38,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N38&lt;0,$A38,""))</f>
         <v/>
       </c>
       <c r="P38" s="13">
-        <f>IF($H38&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B38&gt;0,'Условия'!$B$16&lt;&gt;"",$A38&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H38&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F38&gt;0.01,$A38&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A38='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A38-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -3780,63 +3816,64 @@
         <v>35</v>
       </c>
       <c r="B39" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A39,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A39,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C39" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A39)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A39))</f>
         <v/>
       </c>
       <c r="D39" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A39)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A39))</f>
         <v/>
       </c>
       <c r="E39" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D39/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D39&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D39-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D39/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D39&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D39-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F39" s="20">
-        <f>ROUND($E39-$E38,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E39-$E38,2))</f>
         <v/>
       </c>
       <c r="G39" s="20">
-        <f>ROUND($B39*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B39*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H39" s="20">
-        <f>ROUND($B39-$F39-$G39,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B39-$F39-$G39,2))</f>
         <v/>
       </c>
       <c r="I39" s="20">
-        <f>IF($A39='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A39='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J39" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A39-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A39-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K39" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A39='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A39='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A39-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L39" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A39+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A39=1,'Условия'!$B$20,0)+IF($A39='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A39+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A39=1,'Условия'!$B$20,0)+IF($A39='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M39" s="20">
-        <f>ROUND($I39+$J39+$K39-$L39,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I39+$J39+$K39-$L39,2))</f>
         <v/>
       </c>
       <c r="N39" s="20">
-        <f>ROUND($N38+$M39,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N38+$M39,2))</f>
         <v/>
       </c>
       <c r="O39" s="22">
-        <f>IF($N39&lt;0,$A39,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N39&lt;0,$A39,""))</f>
         <v/>
       </c>
       <c r="P39" s="13">
-        <f>IF($H39&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B39&gt;0,'Условия'!$B$16&lt;&gt;"",$A39&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H39&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F39&gt;0.01,$A39&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A39='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A39-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -3844,63 +3881,64 @@
         <v>36</v>
       </c>
       <c r="B40" s="20">
-        <f>ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A40,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$B$5*INDEX('График КС'!$B$5:$B$40,MATCH($A40,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C40" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A40)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A40))</f>
         <v/>
       </c>
       <c r="D40" s="21">
-        <f>SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A40)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$B$5:$B$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A40))</f>
         <v/>
       </c>
       <c r="E40" s="20">
-        <f>IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D40/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D40&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D40-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF('Условия'!$B$25=0,0,IFERROR(MAX(0,MIN('Условия'!$B$23,IF('Условия'!$B$25=1,ROUND('Условия'!$B$23*$D40/'График КС'!$B$42,2),IF('Условия'!$B$25=2,IF($D40&gt;='График КС'!$B$42,'Условия'!$B$23,0),ROUND('Условия'!$B$23*($D40-'Условия'!$B$9)/('График КС'!$B$42-'Условия'!$B$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F40" s="20">
-        <f>ROUND($E40-$E39,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($E40-$E39,2))</f>
         <v/>
       </c>
       <c r="G40" s="20">
-        <f>ROUND($B40*'Условия'!$B$13/100,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B40*'Условия'!$B$13/100,2))</f>
         <v/>
       </c>
       <c r="H40" s="20">
-        <f>ROUND($B40-$F40-$G40,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($B40-$F40-$G40,2))</f>
         <v/>
       </c>
       <c r="I40" s="20">
-        <f>IF($A40='Условия'!$B$7,'Условия'!$B$23,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($A40='Условия'!$B$7,'Условия'!$B$23,0))</f>
         <v/>
       </c>
       <c r="J40" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A40-'Условия'!$B$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A40-'Условия'!$B$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K40" s="20">
-        <f>IF(AND('Условия'!$B$14&gt;0,$A40='Условия'!$B$14),ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A40='Условия'!$B$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A40-'Условия'!$B$17))),2),0))</f>
         <v/>
       </c>
       <c r="L40" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A40+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A40=1,'Условия'!$B$20,0)+IF($A40='Условия'!$B$12,'Условия'!$B$24,0)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A40+'Условия'!$B$19,$A$5:$A$40,0)),0)*'Условия'!$B$18/100,2)+IF($A40=1,'Условия'!$B$20,0)+IF($A40='Условия'!$B$12,'Условия'!$B$24,0))</f>
         <v/>
       </c>
       <c r="M40" s="20">
-        <f>ROUND($I40+$J40+$K40-$L40,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($I40+$J40+$K40-$L40,2))</f>
         <v/>
       </c>
       <c r="N40" s="20">
-        <f>ROUND($N39+$M40,2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND($N39+$M40,2))</f>
         <v/>
       </c>
       <c r="O40" s="22">
-        <f>IF($N40&lt;0,$A40,"")</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($N40&lt;0,$A40,""))</f>
         <v/>
       </c>
       <c r="P40" s="13">
-        <f>IF($H40&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B40&gt;0,'Условия'!$B$16&lt;&gt;"",$A40&gt;'Условия'!$B$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",IF($H40&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F40&gt;0.01,$A40&lt;'Условия'!$B$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$B$13&gt;0,'Условия'!$B$14&gt;0,$A40='Условия'!$B$14,ROUND(SUM($G$5:$G$40)*'Условия'!$B$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A40-'Условия'!$B$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -3910,43 +3948,43 @@
         </is>
       </c>
       <c r="B42" s="23">
-        <f>ROUND(SUM($B$5:$B$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($B$5:$B$40),2))</f>
         <v/>
       </c>
       <c r="F42" s="23">
-        <f>ROUND(SUM($F$5:$F$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($F$5:$F$40),2))</f>
         <v/>
       </c>
       <c r="G42" s="23">
-        <f>ROUND(SUM($G$5:$G$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($G$5:$G$40),2))</f>
         <v/>
       </c>
       <c r="H42" s="23">
-        <f>ROUND(SUM($H$5:$H$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($H$5:$H$40),2))</f>
         <v/>
       </c>
       <c r="I42" s="23">
-        <f>ROUND(SUM($I$5:$I$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($I$5:$I$40),2))</f>
         <v/>
       </c>
       <c r="J42" s="23">
-        <f>ROUND(SUM($J$5:$J$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($J$5:$J$40),2))</f>
         <v/>
       </c>
       <c r="K42" s="23">
-        <f>ROUND(SUM($K$5:$K$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($K$5:$K$40),2))</f>
         <v/>
       </c>
       <c r="L42" s="23">
-        <f>ROUND(SUM($L$5:$L$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($L$5:$L$40),2))</f>
         <v/>
       </c>
       <c r="M42" s="23">
-        <f>ROUND(SUM($M$5:$M$40),2)</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",ROUND(SUM($M$5:$M$40),2))</f>
         <v/>
       </c>
       <c r="N42" s="23">
-        <f>$N$40</f>
+        <f>IF('Условия'!$B$26&lt;&gt;"Условия заполнены","",$N$40)</f>
         <v/>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -4001,7 +4039,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Расчёт по листам «Условия» и «График КС»: выполненные работы, погашение аванса, удержание, поступления и расходы. Отрицательный накопленный остаток показывает потребность в собственном или привлечённом финансировании.</t>
+          <t>Помесячные денежные потоки. Колонка P показывает противоречия по срокам и суммам; при них итог сравнения блокируется. Возврат удержания ограничен суммой, накопленной к плановой дате оплаты КС.</t>
         </is>
       </c>
     </row>
@@ -4092,63 +4130,64 @@
         <v>1</v>
       </c>
       <c r="B5" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A5,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A5,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C5" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A5)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A5))</f>
         <v/>
       </c>
       <c r="D5" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A5)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A5))</f>
         <v/>
       </c>
       <c r="E5" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D5/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D5&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D5-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D5/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D5&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D5-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F5" s="20">
-        <f>ROUND($E5,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E5,2))</f>
         <v/>
       </c>
       <c r="G5" s="20">
-        <f>ROUND($B5*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B5*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H5" s="20">
-        <f>ROUND($B5-$F5-$G5,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B5-$F5-$G5,2))</f>
         <v/>
       </c>
       <c r="I5" s="20">
-        <f>IF($A5='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A5='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J5" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A5-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A5-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K5" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A5='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A5='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A5-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L5" s="20">
-        <f>ROUND(SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;($A5+'Условия'!$C$19))*'Условия'!$C$18/100,2)+IF($A5=1,'Условия'!$C$20,0)+IF($A5='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;($A5+'Условия'!$C$19))*'Условия'!$C$18/100,2)+IF($A5=1,'Условия'!$C$20,0)+IF($A5='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M5" s="20">
-        <f>ROUND($I5+$J5+$K5-$L5,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I5+$J5+$K5-$L5,2))</f>
         <v/>
       </c>
       <c r="N5" s="20">
-        <f>ROUND($M5,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($M5,2))</f>
         <v/>
       </c>
       <c r="O5" s="22">
-        <f>IF($N5&lt;0,$A5,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N5&lt;0,$A5,""))</f>
         <v/>
       </c>
       <c r="P5" s="13">
-        <f>IF($H5&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B5&gt;0,'Условия'!$C$16&lt;&gt;"",$A5&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H5&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F5&gt;0.01,$A5&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A5='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A5-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -4156,63 +4195,64 @@
         <v>2</v>
       </c>
       <c r="B6" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A6,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A6,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C6" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A6)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A6))</f>
         <v/>
       </c>
       <c r="D6" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A6)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A6))</f>
         <v/>
       </c>
       <c r="E6" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D6/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D6&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D6-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D6/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D6&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D6-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F6" s="20">
-        <f>ROUND($E6-$E5,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E6-$E5,2))</f>
         <v/>
       </c>
       <c r="G6" s="20">
-        <f>ROUND($B6*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B6*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H6" s="20">
-        <f>ROUND($B6-$F6-$G6,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B6-$F6-$G6,2))</f>
         <v/>
       </c>
       <c r="I6" s="20">
-        <f>IF($A6='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A6='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J6" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A6-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A6-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K6" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A6='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A6='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A6-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L6" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A6+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A6=1,'Условия'!$C$20,0)+IF($A6='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A6+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A6=1,'Условия'!$C$20,0)+IF($A6='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M6" s="20">
-        <f>ROUND($I6+$J6+$K6-$L6,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I6+$J6+$K6-$L6,2))</f>
         <v/>
       </c>
       <c r="N6" s="20">
-        <f>ROUND($N5+$M6,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N5+$M6,2))</f>
         <v/>
       </c>
       <c r="O6" s="22">
-        <f>IF($N6&lt;0,$A6,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N6&lt;0,$A6,""))</f>
         <v/>
       </c>
       <c r="P6" s="13">
-        <f>IF($H6&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B6&gt;0,'Условия'!$C$16&lt;&gt;"",$A6&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H6&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F6&gt;0.01,$A6&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A6='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A6-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -4220,63 +4260,64 @@
         <v>3</v>
       </c>
       <c r="B7" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A7,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A7,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C7" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A7)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A7))</f>
         <v/>
       </c>
       <c r="D7" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A7)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A7))</f>
         <v/>
       </c>
       <c r="E7" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D7/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D7&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D7-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D7/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D7&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D7-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F7" s="20">
-        <f>ROUND($E7-$E6,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E7-$E6,2))</f>
         <v/>
       </c>
       <c r="G7" s="20">
-        <f>ROUND($B7*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B7*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H7" s="20">
-        <f>ROUND($B7-$F7-$G7,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B7-$F7-$G7,2))</f>
         <v/>
       </c>
       <c r="I7" s="20">
-        <f>IF($A7='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A7='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J7" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A7-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A7-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K7" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A7='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A7='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A7-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L7" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A7+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A7=1,'Условия'!$C$20,0)+IF($A7='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A7+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A7=1,'Условия'!$C$20,0)+IF($A7='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M7" s="20">
-        <f>ROUND($I7+$J7+$K7-$L7,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I7+$J7+$K7-$L7,2))</f>
         <v/>
       </c>
       <c r="N7" s="20">
-        <f>ROUND($N6+$M7,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N6+$M7,2))</f>
         <v/>
       </c>
       <c r="O7" s="22">
-        <f>IF($N7&lt;0,$A7,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N7&lt;0,$A7,""))</f>
         <v/>
       </c>
       <c r="P7" s="13">
-        <f>IF($H7&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B7&gt;0,'Условия'!$C$16&lt;&gt;"",$A7&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H7&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F7&gt;0.01,$A7&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A7='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A7-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -4284,63 +4325,64 @@
         <v>4</v>
       </c>
       <c r="B8" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A8,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A8,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C8" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A8)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A8))</f>
         <v/>
       </c>
       <c r="D8" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A8)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A8))</f>
         <v/>
       </c>
       <c r="E8" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D8/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D8&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D8-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D8/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D8&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D8-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F8" s="20">
-        <f>ROUND($E8-$E7,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E8-$E7,2))</f>
         <v/>
       </c>
       <c r="G8" s="20">
-        <f>ROUND($B8*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B8*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H8" s="20">
-        <f>ROUND($B8-$F8-$G8,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B8-$F8-$G8,2))</f>
         <v/>
       </c>
       <c r="I8" s="20">
-        <f>IF($A8='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A8='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J8" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A8-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A8-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K8" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A8='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A8='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A8-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L8" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A8+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A8=1,'Условия'!$C$20,0)+IF($A8='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A8+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A8=1,'Условия'!$C$20,0)+IF($A8='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M8" s="20">
-        <f>ROUND($I8+$J8+$K8-$L8,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I8+$J8+$K8-$L8,2))</f>
         <v/>
       </c>
       <c r="N8" s="20">
-        <f>ROUND($N7+$M8,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N7+$M8,2))</f>
         <v/>
       </c>
       <c r="O8" s="22">
-        <f>IF($N8&lt;0,$A8,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N8&lt;0,$A8,""))</f>
         <v/>
       </c>
       <c r="P8" s="13">
-        <f>IF($H8&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B8&gt;0,'Условия'!$C$16&lt;&gt;"",$A8&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H8&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F8&gt;0.01,$A8&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A8='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A8-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -4348,63 +4390,64 @@
         <v>5</v>
       </c>
       <c r="B9" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A9,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A9,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C9" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A9)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A9))</f>
         <v/>
       </c>
       <c r="D9" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A9)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A9))</f>
         <v/>
       </c>
       <c r="E9" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D9/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D9&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D9-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D9/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D9&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D9-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F9" s="20">
-        <f>ROUND($E9-$E8,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E9-$E8,2))</f>
         <v/>
       </c>
       <c r="G9" s="20">
-        <f>ROUND($B9*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B9*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H9" s="20">
-        <f>ROUND($B9-$F9-$G9,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B9-$F9-$G9,2))</f>
         <v/>
       </c>
       <c r="I9" s="20">
-        <f>IF($A9='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A9='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J9" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A9-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A9-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K9" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A9='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A9='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A9-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L9" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A9+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A9=1,'Условия'!$C$20,0)+IF($A9='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A9+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A9=1,'Условия'!$C$20,0)+IF($A9='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M9" s="20">
-        <f>ROUND($I9+$J9+$K9-$L9,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I9+$J9+$K9-$L9,2))</f>
         <v/>
       </c>
       <c r="N9" s="20">
-        <f>ROUND($N8+$M9,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N8+$M9,2))</f>
         <v/>
       </c>
       <c r="O9" s="22">
-        <f>IF($N9&lt;0,$A9,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N9&lt;0,$A9,""))</f>
         <v/>
       </c>
       <c r="P9" s="13">
-        <f>IF($H9&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B9&gt;0,'Условия'!$C$16&lt;&gt;"",$A9&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H9&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F9&gt;0.01,$A9&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A9='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A9-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -4412,63 +4455,64 @@
         <v>6</v>
       </c>
       <c r="B10" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A10,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A10,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C10" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A10)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A10))</f>
         <v/>
       </c>
       <c r="D10" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A10)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A10))</f>
         <v/>
       </c>
       <c r="E10" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D10/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D10&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D10-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D10/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D10&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D10-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F10" s="20">
-        <f>ROUND($E10-$E9,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E10-$E9,2))</f>
         <v/>
       </c>
       <c r="G10" s="20">
-        <f>ROUND($B10*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B10*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H10" s="20">
-        <f>ROUND($B10-$F10-$G10,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B10-$F10-$G10,2))</f>
         <v/>
       </c>
       <c r="I10" s="20">
-        <f>IF($A10='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A10='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J10" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A10-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A10-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K10" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A10='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A10='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A10-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L10" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A10+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A10=1,'Условия'!$C$20,0)+IF($A10='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A10+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A10=1,'Условия'!$C$20,0)+IF($A10='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M10" s="20">
-        <f>ROUND($I10+$J10+$K10-$L10,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I10+$J10+$K10-$L10,2))</f>
         <v/>
       </c>
       <c r="N10" s="20">
-        <f>ROUND($N9+$M10,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N9+$M10,2))</f>
         <v/>
       </c>
       <c r="O10" s="22">
-        <f>IF($N10&lt;0,$A10,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N10&lt;0,$A10,""))</f>
         <v/>
       </c>
       <c r="P10" s="13">
-        <f>IF($H10&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B10&gt;0,'Условия'!$C$16&lt;&gt;"",$A10&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H10&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F10&gt;0.01,$A10&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A10='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A10-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -4476,63 +4520,64 @@
         <v>7</v>
       </c>
       <c r="B11" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A11,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A11,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C11" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A11)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A11))</f>
         <v/>
       </c>
       <c r="D11" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A11)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A11))</f>
         <v/>
       </c>
       <c r="E11" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D11/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D11&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D11-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D11/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D11&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D11-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F11" s="20">
-        <f>ROUND($E11-$E10,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E11-$E10,2))</f>
         <v/>
       </c>
       <c r="G11" s="20">
-        <f>ROUND($B11*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B11*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H11" s="20">
-        <f>ROUND($B11-$F11-$G11,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B11-$F11-$G11,2))</f>
         <v/>
       </c>
       <c r="I11" s="20">
-        <f>IF($A11='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A11='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J11" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A11-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A11-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K11" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A11='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A11='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A11-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L11" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A11+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A11=1,'Условия'!$C$20,0)+IF($A11='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A11+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A11=1,'Условия'!$C$20,0)+IF($A11='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M11" s="20">
-        <f>ROUND($I11+$J11+$K11-$L11,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I11+$J11+$K11-$L11,2))</f>
         <v/>
       </c>
       <c r="N11" s="20">
-        <f>ROUND($N10+$M11,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N10+$M11,2))</f>
         <v/>
       </c>
       <c r="O11" s="22">
-        <f>IF($N11&lt;0,$A11,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N11&lt;0,$A11,""))</f>
         <v/>
       </c>
       <c r="P11" s="13">
-        <f>IF($H11&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B11&gt;0,'Условия'!$C$16&lt;&gt;"",$A11&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H11&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F11&gt;0.01,$A11&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A11='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A11-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -4540,63 +4585,64 @@
         <v>8</v>
       </c>
       <c r="B12" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A12,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A12,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C12" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A12)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A12))</f>
         <v/>
       </c>
       <c r="D12" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A12)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A12))</f>
         <v/>
       </c>
       <c r="E12" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D12/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D12&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D12-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D12/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D12&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D12-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F12" s="20">
-        <f>ROUND($E12-$E11,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E12-$E11,2))</f>
         <v/>
       </c>
       <c r="G12" s="20">
-        <f>ROUND($B12*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B12*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H12" s="20">
-        <f>ROUND($B12-$F12-$G12,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B12-$F12-$G12,2))</f>
         <v/>
       </c>
       <c r="I12" s="20">
-        <f>IF($A12='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A12='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J12" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A12-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A12-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K12" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A12='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A12='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A12-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L12" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A12+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A12=1,'Условия'!$C$20,0)+IF($A12='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A12+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A12=1,'Условия'!$C$20,0)+IF($A12='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M12" s="20">
-        <f>ROUND($I12+$J12+$K12-$L12,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I12+$J12+$K12-$L12,2))</f>
         <v/>
       </c>
       <c r="N12" s="20">
-        <f>ROUND($N11+$M12,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N11+$M12,2))</f>
         <v/>
       </c>
       <c r="O12" s="22">
-        <f>IF($N12&lt;0,$A12,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N12&lt;0,$A12,""))</f>
         <v/>
       </c>
       <c r="P12" s="13">
-        <f>IF($H12&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B12&gt;0,'Условия'!$C$16&lt;&gt;"",$A12&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H12&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F12&gt;0.01,$A12&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A12='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A12-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -4604,63 +4650,64 @@
         <v>9</v>
       </c>
       <c r="B13" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A13,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A13,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C13" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A13)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A13))</f>
         <v/>
       </c>
       <c r="D13" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A13)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A13))</f>
         <v/>
       </c>
       <c r="E13" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D13/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D13&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D13-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D13/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D13&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D13-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F13" s="20">
-        <f>ROUND($E13-$E12,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E13-$E12,2))</f>
         <v/>
       </c>
       <c r="G13" s="20">
-        <f>ROUND($B13*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B13*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H13" s="20">
-        <f>ROUND($B13-$F13-$G13,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B13-$F13-$G13,2))</f>
         <v/>
       </c>
       <c r="I13" s="20">
-        <f>IF($A13='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A13='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J13" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A13-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A13-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K13" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A13='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A13='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A13-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L13" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A13+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A13=1,'Условия'!$C$20,0)+IF($A13='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A13+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A13=1,'Условия'!$C$20,0)+IF($A13='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M13" s="20">
-        <f>ROUND($I13+$J13+$K13-$L13,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I13+$J13+$K13-$L13,2))</f>
         <v/>
       </c>
       <c r="N13" s="20">
-        <f>ROUND($N12+$M13,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N12+$M13,2))</f>
         <v/>
       </c>
       <c r="O13" s="22">
-        <f>IF($N13&lt;0,$A13,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N13&lt;0,$A13,""))</f>
         <v/>
       </c>
       <c r="P13" s="13">
-        <f>IF($H13&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B13&gt;0,'Условия'!$C$16&lt;&gt;"",$A13&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H13&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F13&gt;0.01,$A13&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A13='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A13-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -4668,63 +4715,64 @@
         <v>10</v>
       </c>
       <c r="B14" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A14,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A14,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C14" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A14)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A14))</f>
         <v/>
       </c>
       <c r="D14" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A14)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A14))</f>
         <v/>
       </c>
       <c r="E14" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D14/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D14&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D14-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D14/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D14&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D14-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F14" s="20">
-        <f>ROUND($E14-$E13,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E14-$E13,2))</f>
         <v/>
       </c>
       <c r="G14" s="20">
-        <f>ROUND($B14*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B14*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H14" s="20">
-        <f>ROUND($B14-$F14-$G14,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B14-$F14-$G14,2))</f>
         <v/>
       </c>
       <c r="I14" s="20">
-        <f>IF($A14='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A14='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J14" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A14-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A14-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K14" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A14='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A14='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A14-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L14" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A14+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A14=1,'Условия'!$C$20,0)+IF($A14='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A14+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A14=1,'Условия'!$C$20,0)+IF($A14='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M14" s="20">
-        <f>ROUND($I14+$J14+$K14-$L14,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I14+$J14+$K14-$L14,2))</f>
         <v/>
       </c>
       <c r="N14" s="20">
-        <f>ROUND($N13+$M14,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N13+$M14,2))</f>
         <v/>
       </c>
       <c r="O14" s="22">
-        <f>IF($N14&lt;0,$A14,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N14&lt;0,$A14,""))</f>
         <v/>
       </c>
       <c r="P14" s="13">
-        <f>IF($H14&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B14&gt;0,'Условия'!$C$16&lt;&gt;"",$A14&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H14&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F14&gt;0.01,$A14&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A14='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A14-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -4732,63 +4780,64 @@
         <v>11</v>
       </c>
       <c r="B15" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A15,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A15,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C15" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A15)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A15))</f>
         <v/>
       </c>
       <c r="D15" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A15)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A15))</f>
         <v/>
       </c>
       <c r="E15" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D15/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D15&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D15-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D15/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D15&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D15-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>ROUND($E15-$E14,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E15-$E14,2))</f>
         <v/>
       </c>
       <c r="G15" s="20">
-        <f>ROUND($B15*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B15*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H15" s="20">
-        <f>ROUND($B15-$F15-$G15,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B15-$F15-$G15,2))</f>
         <v/>
       </c>
       <c r="I15" s="20">
-        <f>IF($A15='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A15='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J15" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A15-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A15-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K15" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A15='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A15='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A15-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L15" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A15+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A15=1,'Условия'!$C$20,0)+IF($A15='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A15+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A15=1,'Условия'!$C$20,0)+IF($A15='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M15" s="20">
-        <f>ROUND($I15+$J15+$K15-$L15,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I15+$J15+$K15-$L15,2))</f>
         <v/>
       </c>
       <c r="N15" s="20">
-        <f>ROUND($N14+$M15,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N14+$M15,2))</f>
         <v/>
       </c>
       <c r="O15" s="22">
-        <f>IF($N15&lt;0,$A15,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N15&lt;0,$A15,""))</f>
         <v/>
       </c>
       <c r="P15" s="13">
-        <f>IF($H15&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B15&gt;0,'Условия'!$C$16&lt;&gt;"",$A15&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H15&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F15&gt;0.01,$A15&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A15='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A15-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -4796,63 +4845,64 @@
         <v>12</v>
       </c>
       <c r="B16" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A16,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A16,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C16" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A16)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A16))</f>
         <v/>
       </c>
       <c r="D16" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A16)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A16))</f>
         <v/>
       </c>
       <c r="E16" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D16/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D16&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D16-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D16/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D16&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D16-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F16" s="20">
-        <f>ROUND($E16-$E15,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E16-$E15,2))</f>
         <v/>
       </c>
       <c r="G16" s="20">
-        <f>ROUND($B16*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B16*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H16" s="20">
-        <f>ROUND($B16-$F16-$G16,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B16-$F16-$G16,2))</f>
         <v/>
       </c>
       <c r="I16" s="20">
-        <f>IF($A16='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A16='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J16" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A16-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A16-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K16" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A16='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A16='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A16-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L16" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A16+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A16=1,'Условия'!$C$20,0)+IF($A16='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A16+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A16=1,'Условия'!$C$20,0)+IF($A16='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M16" s="20">
-        <f>ROUND($I16+$J16+$K16-$L16,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I16+$J16+$K16-$L16,2))</f>
         <v/>
       </c>
       <c r="N16" s="20">
-        <f>ROUND($N15+$M16,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N15+$M16,2))</f>
         <v/>
       </c>
       <c r="O16" s="22">
-        <f>IF($N16&lt;0,$A16,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N16&lt;0,$A16,""))</f>
         <v/>
       </c>
       <c r="P16" s="13">
-        <f>IF($H16&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B16&gt;0,'Условия'!$C$16&lt;&gt;"",$A16&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H16&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F16&gt;0.01,$A16&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A16='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A16-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -4860,63 +4910,64 @@
         <v>13</v>
       </c>
       <c r="B17" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A17,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A17,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A17)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A17))</f>
         <v/>
       </c>
       <c r="D17" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A17)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A17))</f>
         <v/>
       </c>
       <c r="E17" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D17/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D17&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D17-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D17/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D17&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D17-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F17" s="20">
-        <f>ROUND($E17-$E16,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E17-$E16,2))</f>
         <v/>
       </c>
       <c r="G17" s="20">
-        <f>ROUND($B17*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B17*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H17" s="20">
-        <f>ROUND($B17-$F17-$G17,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B17-$F17-$G17,2))</f>
         <v/>
       </c>
       <c r="I17" s="20">
-        <f>IF($A17='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A17='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J17" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A17-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A17-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K17" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A17='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A17='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A17-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L17" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A17+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A17=1,'Условия'!$C$20,0)+IF($A17='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A17+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A17=1,'Условия'!$C$20,0)+IF($A17='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M17" s="20">
-        <f>ROUND($I17+$J17+$K17-$L17,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I17+$J17+$K17-$L17,2))</f>
         <v/>
       </c>
       <c r="N17" s="20">
-        <f>ROUND($N16+$M17,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N16+$M17,2))</f>
         <v/>
       </c>
       <c r="O17" s="22">
-        <f>IF($N17&lt;0,$A17,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N17&lt;0,$A17,""))</f>
         <v/>
       </c>
       <c r="P17" s="13">
-        <f>IF($H17&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B17&gt;0,'Условия'!$C$16&lt;&gt;"",$A17&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H17&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F17&gt;0.01,$A17&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A17='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A17-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -4924,63 +4975,64 @@
         <v>14</v>
       </c>
       <c r="B18" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A18,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A18,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C18" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A18)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A18))</f>
         <v/>
       </c>
       <c r="D18" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A18)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A18))</f>
         <v/>
       </c>
       <c r="E18" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D18/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D18&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D18-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D18/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D18&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D18-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F18" s="20">
-        <f>ROUND($E18-$E17,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E18-$E17,2))</f>
         <v/>
       </c>
       <c r="G18" s="20">
-        <f>ROUND($B18*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B18*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H18" s="20">
-        <f>ROUND($B18-$F18-$G18,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B18-$F18-$G18,2))</f>
         <v/>
       </c>
       <c r="I18" s="20">
-        <f>IF($A18='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A18='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J18" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A18-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A18-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K18" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A18='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A18='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A18-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L18" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A18+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A18=1,'Условия'!$C$20,0)+IF($A18='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A18+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A18=1,'Условия'!$C$20,0)+IF($A18='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M18" s="20">
-        <f>ROUND($I18+$J18+$K18-$L18,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I18+$J18+$K18-$L18,2))</f>
         <v/>
       </c>
       <c r="N18" s="20">
-        <f>ROUND($N17+$M18,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N17+$M18,2))</f>
         <v/>
       </c>
       <c r="O18" s="22">
-        <f>IF($N18&lt;0,$A18,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N18&lt;0,$A18,""))</f>
         <v/>
       </c>
       <c r="P18" s="13">
-        <f>IF($H18&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B18&gt;0,'Условия'!$C$16&lt;&gt;"",$A18&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H18&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F18&gt;0.01,$A18&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A18='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A18-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -4988,63 +5040,64 @@
         <v>15</v>
       </c>
       <c r="B19" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A19,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A19,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C19" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A19)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A19))</f>
         <v/>
       </c>
       <c r="D19" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A19)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A19))</f>
         <v/>
       </c>
       <c r="E19" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D19/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D19&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D19-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D19/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D19&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D19-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F19" s="20">
-        <f>ROUND($E19-$E18,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E19-$E18,2))</f>
         <v/>
       </c>
       <c r="G19" s="20">
-        <f>ROUND($B19*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B19*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>ROUND($B19-$F19-$G19,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B19-$F19-$G19,2))</f>
         <v/>
       </c>
       <c r="I19" s="20">
-        <f>IF($A19='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A19='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J19" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A19-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A19-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K19" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A19='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A19='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A19-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L19" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A19+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A19=1,'Условия'!$C$20,0)+IF($A19='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A19+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A19=1,'Условия'!$C$20,0)+IF($A19='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M19" s="20">
-        <f>ROUND($I19+$J19+$K19-$L19,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I19+$J19+$K19-$L19,2))</f>
         <v/>
       </c>
       <c r="N19" s="20">
-        <f>ROUND($N18+$M19,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N18+$M19,2))</f>
         <v/>
       </c>
       <c r="O19" s="22">
-        <f>IF($N19&lt;0,$A19,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N19&lt;0,$A19,""))</f>
         <v/>
       </c>
       <c r="P19" s="13">
-        <f>IF($H19&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B19&gt;0,'Условия'!$C$16&lt;&gt;"",$A19&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H19&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F19&gt;0.01,$A19&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A19='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A19-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -5052,63 +5105,64 @@
         <v>16</v>
       </c>
       <c r="B20" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A20,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A20,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C20" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A20)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A20))</f>
         <v/>
       </c>
       <c r="D20" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A20)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A20))</f>
         <v/>
       </c>
       <c r="E20" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D20/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D20&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D20-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D20/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D20&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D20-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F20" s="20">
-        <f>ROUND($E20-$E19,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E20-$E19,2))</f>
         <v/>
       </c>
       <c r="G20" s="20">
-        <f>ROUND($B20*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B20*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>ROUND($B20-$F20-$G20,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B20-$F20-$G20,2))</f>
         <v/>
       </c>
       <c r="I20" s="20">
-        <f>IF($A20='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A20='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J20" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A20-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A20-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K20" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A20='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A20='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A20-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L20" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A20+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A20=1,'Условия'!$C$20,0)+IF($A20='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A20+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A20=1,'Условия'!$C$20,0)+IF($A20='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M20" s="20">
-        <f>ROUND($I20+$J20+$K20-$L20,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I20+$J20+$K20-$L20,2))</f>
         <v/>
       </c>
       <c r="N20" s="20">
-        <f>ROUND($N19+$M20,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N19+$M20,2))</f>
         <v/>
       </c>
       <c r="O20" s="22">
-        <f>IF($N20&lt;0,$A20,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N20&lt;0,$A20,""))</f>
         <v/>
       </c>
       <c r="P20" s="13">
-        <f>IF($H20&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B20&gt;0,'Условия'!$C$16&lt;&gt;"",$A20&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H20&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F20&gt;0.01,$A20&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A20='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A20-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -5116,63 +5170,64 @@
         <v>17</v>
       </c>
       <c r="B21" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A21,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A21,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C21" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A21)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A21))</f>
         <v/>
       </c>
       <c r="D21" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A21)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A21))</f>
         <v/>
       </c>
       <c r="E21" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D21/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D21&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D21-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D21/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D21&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D21-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F21" s="20">
-        <f>ROUND($E21-$E20,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E21-$E20,2))</f>
         <v/>
       </c>
       <c r="G21" s="20">
-        <f>ROUND($B21*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B21*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H21" s="20">
-        <f>ROUND($B21-$F21-$G21,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B21-$F21-$G21,2))</f>
         <v/>
       </c>
       <c r="I21" s="20">
-        <f>IF($A21='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A21='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J21" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A21-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A21-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K21" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A21='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A21='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A21-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L21" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A21+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A21=1,'Условия'!$C$20,0)+IF($A21='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A21+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A21=1,'Условия'!$C$20,0)+IF($A21='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M21" s="20">
-        <f>ROUND($I21+$J21+$K21-$L21,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I21+$J21+$K21-$L21,2))</f>
         <v/>
       </c>
       <c r="N21" s="20">
-        <f>ROUND($N20+$M21,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N20+$M21,2))</f>
         <v/>
       </c>
       <c r="O21" s="22">
-        <f>IF($N21&lt;0,$A21,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N21&lt;0,$A21,""))</f>
         <v/>
       </c>
       <c r="P21" s="13">
-        <f>IF($H21&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B21&gt;0,'Условия'!$C$16&lt;&gt;"",$A21&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H21&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F21&gt;0.01,$A21&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A21='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A21-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -5180,63 +5235,64 @@
         <v>18</v>
       </c>
       <c r="B22" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A22,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A22,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C22" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A22)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A22))</f>
         <v/>
       </c>
       <c r="D22" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A22)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A22))</f>
         <v/>
       </c>
       <c r="E22" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D22/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D22&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D22-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D22/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D22&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D22-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F22" s="20">
-        <f>ROUND($E22-$E21,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E22-$E21,2))</f>
         <v/>
       </c>
       <c r="G22" s="20">
-        <f>ROUND($B22*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B22*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H22" s="20">
-        <f>ROUND($B22-$F22-$G22,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B22-$F22-$G22,2))</f>
         <v/>
       </c>
       <c r="I22" s="20">
-        <f>IF($A22='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A22='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J22" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A22-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A22-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K22" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A22='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A22='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A22-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L22" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A22+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A22=1,'Условия'!$C$20,0)+IF($A22='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A22+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A22=1,'Условия'!$C$20,0)+IF($A22='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M22" s="20">
-        <f>ROUND($I22+$J22+$K22-$L22,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I22+$J22+$K22-$L22,2))</f>
         <v/>
       </c>
       <c r="N22" s="20">
-        <f>ROUND($N21+$M22,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N21+$M22,2))</f>
         <v/>
       </c>
       <c r="O22" s="22">
-        <f>IF($N22&lt;0,$A22,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N22&lt;0,$A22,""))</f>
         <v/>
       </c>
       <c r="P22" s="13">
-        <f>IF($H22&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B22&gt;0,'Условия'!$C$16&lt;&gt;"",$A22&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H22&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F22&gt;0.01,$A22&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A22='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A22-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -5244,63 +5300,64 @@
         <v>19</v>
       </c>
       <c r="B23" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A23,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A23,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C23" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A23)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A23))</f>
         <v/>
       </c>
       <c r="D23" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A23)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A23))</f>
         <v/>
       </c>
       <c r="E23" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D23/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D23&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D23-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D23/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D23&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D23-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F23" s="20">
-        <f>ROUND($E23-$E22,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E23-$E22,2))</f>
         <v/>
       </c>
       <c r="G23" s="20">
-        <f>ROUND($B23*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B23*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H23" s="20">
-        <f>ROUND($B23-$F23-$G23,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B23-$F23-$G23,2))</f>
         <v/>
       </c>
       <c r="I23" s="20">
-        <f>IF($A23='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A23='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J23" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A23-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A23-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K23" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A23='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A23='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A23-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L23" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A23+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A23=1,'Условия'!$C$20,0)+IF($A23='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A23+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A23=1,'Условия'!$C$20,0)+IF($A23='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M23" s="20">
-        <f>ROUND($I23+$J23+$K23-$L23,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I23+$J23+$K23-$L23,2))</f>
         <v/>
       </c>
       <c r="N23" s="20">
-        <f>ROUND($N22+$M23,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N22+$M23,2))</f>
         <v/>
       </c>
       <c r="O23" s="22">
-        <f>IF($N23&lt;0,$A23,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N23&lt;0,$A23,""))</f>
         <v/>
       </c>
       <c r="P23" s="13">
-        <f>IF($H23&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B23&gt;0,'Условия'!$C$16&lt;&gt;"",$A23&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H23&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F23&gt;0.01,$A23&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A23='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A23-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -5308,63 +5365,64 @@
         <v>20</v>
       </c>
       <c r="B24" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A24,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A24,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C24" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A24)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A24))</f>
         <v/>
       </c>
       <c r="D24" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A24)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A24))</f>
         <v/>
       </c>
       <c r="E24" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D24/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D24&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D24-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D24/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D24&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D24-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F24" s="20">
-        <f>ROUND($E24-$E23,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E24-$E23,2))</f>
         <v/>
       </c>
       <c r="G24" s="20">
-        <f>ROUND($B24*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B24*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H24" s="20">
-        <f>ROUND($B24-$F24-$G24,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B24-$F24-$G24,2))</f>
         <v/>
       </c>
       <c r="I24" s="20">
-        <f>IF($A24='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A24='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J24" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A24-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A24-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K24" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A24='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A24='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A24-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L24" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A24+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A24=1,'Условия'!$C$20,0)+IF($A24='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A24+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A24=1,'Условия'!$C$20,0)+IF($A24='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M24" s="20">
-        <f>ROUND($I24+$J24+$K24-$L24,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I24+$J24+$K24-$L24,2))</f>
         <v/>
       </c>
       <c r="N24" s="20">
-        <f>ROUND($N23+$M24,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N23+$M24,2))</f>
         <v/>
       </c>
       <c r="O24" s="22">
-        <f>IF($N24&lt;0,$A24,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N24&lt;0,$A24,""))</f>
         <v/>
       </c>
       <c r="P24" s="13">
-        <f>IF($H24&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B24&gt;0,'Условия'!$C$16&lt;&gt;"",$A24&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H24&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F24&gt;0.01,$A24&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A24='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A24-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -5372,63 +5430,64 @@
         <v>21</v>
       </c>
       <c r="B25" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A25,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A25,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C25" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A25)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A25))</f>
         <v/>
       </c>
       <c r="D25" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A25)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A25))</f>
         <v/>
       </c>
       <c r="E25" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D25/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D25&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D25-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D25/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D25&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D25-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F25" s="20">
-        <f>ROUND($E25-$E24,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E25-$E24,2))</f>
         <v/>
       </c>
       <c r="G25" s="20">
-        <f>ROUND($B25*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B25*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H25" s="20">
-        <f>ROUND($B25-$F25-$G25,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B25-$F25-$G25,2))</f>
         <v/>
       </c>
       <c r="I25" s="20">
-        <f>IF($A25='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A25='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J25" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A25-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A25-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K25" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A25='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A25='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A25-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L25" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A25+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A25=1,'Условия'!$C$20,0)+IF($A25='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A25+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A25=1,'Условия'!$C$20,0)+IF($A25='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M25" s="20">
-        <f>ROUND($I25+$J25+$K25-$L25,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I25+$J25+$K25-$L25,2))</f>
         <v/>
       </c>
       <c r="N25" s="20">
-        <f>ROUND($N24+$M25,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N24+$M25,2))</f>
         <v/>
       </c>
       <c r="O25" s="22">
-        <f>IF($N25&lt;0,$A25,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N25&lt;0,$A25,""))</f>
         <v/>
       </c>
       <c r="P25" s="13">
-        <f>IF($H25&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B25&gt;0,'Условия'!$C$16&lt;&gt;"",$A25&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H25&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F25&gt;0.01,$A25&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A25='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A25-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -5436,63 +5495,64 @@
         <v>22</v>
       </c>
       <c r="B26" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A26,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A26,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C26" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A26)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A26))</f>
         <v/>
       </c>
       <c r="D26" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A26)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A26))</f>
         <v/>
       </c>
       <c r="E26" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D26/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D26&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D26-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D26/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D26&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D26-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F26" s="20">
-        <f>ROUND($E26-$E25,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E26-$E25,2))</f>
         <v/>
       </c>
       <c r="G26" s="20">
-        <f>ROUND($B26*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B26*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H26" s="20">
-        <f>ROUND($B26-$F26-$G26,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B26-$F26-$G26,2))</f>
         <v/>
       </c>
       <c r="I26" s="20">
-        <f>IF($A26='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A26='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J26" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A26-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A26-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K26" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A26='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A26='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A26-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L26" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A26+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A26=1,'Условия'!$C$20,0)+IF($A26='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A26+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A26=1,'Условия'!$C$20,0)+IF($A26='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M26" s="20">
-        <f>ROUND($I26+$J26+$K26-$L26,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I26+$J26+$K26-$L26,2))</f>
         <v/>
       </c>
       <c r="N26" s="20">
-        <f>ROUND($N25+$M26,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N25+$M26,2))</f>
         <v/>
       </c>
       <c r="O26" s="22">
-        <f>IF($N26&lt;0,$A26,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N26&lt;0,$A26,""))</f>
         <v/>
       </c>
       <c r="P26" s="13">
-        <f>IF($H26&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B26&gt;0,'Условия'!$C$16&lt;&gt;"",$A26&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H26&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F26&gt;0.01,$A26&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A26='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A26-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -5500,63 +5560,64 @@
         <v>23</v>
       </c>
       <c r="B27" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A27,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A27,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C27" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A27)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A27))</f>
         <v/>
       </c>
       <c r="D27" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A27)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A27))</f>
         <v/>
       </c>
       <c r="E27" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D27/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D27&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D27-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D27/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D27&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D27-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F27" s="20">
-        <f>ROUND($E27-$E26,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E27-$E26,2))</f>
         <v/>
       </c>
       <c r="G27" s="20">
-        <f>ROUND($B27*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B27*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H27" s="20">
-        <f>ROUND($B27-$F27-$G27,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B27-$F27-$G27,2))</f>
         <v/>
       </c>
       <c r="I27" s="20">
-        <f>IF($A27='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A27='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J27" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A27-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A27-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K27" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A27='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A27='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A27-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L27" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A27+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A27=1,'Условия'!$C$20,0)+IF($A27='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A27+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A27=1,'Условия'!$C$20,0)+IF($A27='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M27" s="20">
-        <f>ROUND($I27+$J27+$K27-$L27,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I27+$J27+$K27-$L27,2))</f>
         <v/>
       </c>
       <c r="N27" s="20">
-        <f>ROUND($N26+$M27,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N26+$M27,2))</f>
         <v/>
       </c>
       <c r="O27" s="22">
-        <f>IF($N27&lt;0,$A27,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N27&lt;0,$A27,""))</f>
         <v/>
       </c>
       <c r="P27" s="13">
-        <f>IF($H27&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B27&gt;0,'Условия'!$C$16&lt;&gt;"",$A27&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H27&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F27&gt;0.01,$A27&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A27='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A27-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -5564,63 +5625,64 @@
         <v>24</v>
       </c>
       <c r="B28" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A28,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A28,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C28" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A28)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A28))</f>
         <v/>
       </c>
       <c r="D28" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A28)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A28))</f>
         <v/>
       </c>
       <c r="E28" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D28/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D28&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D28-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D28/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D28&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D28-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F28" s="20">
-        <f>ROUND($E28-$E27,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E28-$E27,2))</f>
         <v/>
       </c>
       <c r="G28" s="20">
-        <f>ROUND($B28*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B28*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H28" s="20">
-        <f>ROUND($B28-$F28-$G28,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B28-$F28-$G28,2))</f>
         <v/>
       </c>
       <c r="I28" s="20">
-        <f>IF($A28='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A28='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J28" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A28-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A28-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K28" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A28='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A28='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A28-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L28" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A28+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A28=1,'Условия'!$C$20,0)+IF($A28='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A28+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A28=1,'Условия'!$C$20,0)+IF($A28='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M28" s="20">
-        <f>ROUND($I28+$J28+$K28-$L28,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I28+$J28+$K28-$L28,2))</f>
         <v/>
       </c>
       <c r="N28" s="20">
-        <f>ROUND($N27+$M28,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N27+$M28,2))</f>
         <v/>
       </c>
       <c r="O28" s="22">
-        <f>IF($N28&lt;0,$A28,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N28&lt;0,$A28,""))</f>
         <v/>
       </c>
       <c r="P28" s="13">
-        <f>IF($H28&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B28&gt;0,'Условия'!$C$16&lt;&gt;"",$A28&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H28&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F28&gt;0.01,$A28&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A28='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A28-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -5628,63 +5690,64 @@
         <v>25</v>
       </c>
       <c r="B29" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A29,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A29,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C29" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A29)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A29))</f>
         <v/>
       </c>
       <c r="D29" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A29)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A29))</f>
         <v/>
       </c>
       <c r="E29" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D29/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D29&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D29-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D29/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D29&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D29-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F29" s="20">
-        <f>ROUND($E29-$E28,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E29-$E28,2))</f>
         <v/>
       </c>
       <c r="G29" s="20">
-        <f>ROUND($B29*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B29*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H29" s="20">
-        <f>ROUND($B29-$F29-$G29,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B29-$F29-$G29,2))</f>
         <v/>
       </c>
       <c r="I29" s="20">
-        <f>IF($A29='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A29='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J29" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A29-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A29-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K29" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A29='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A29='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A29-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L29" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A29+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A29=1,'Условия'!$C$20,0)+IF($A29='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A29+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A29=1,'Условия'!$C$20,0)+IF($A29='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M29" s="20">
-        <f>ROUND($I29+$J29+$K29-$L29,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I29+$J29+$K29-$L29,2))</f>
         <v/>
       </c>
       <c r="N29" s="20">
-        <f>ROUND($N28+$M29,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N28+$M29,2))</f>
         <v/>
       </c>
       <c r="O29" s="22">
-        <f>IF($N29&lt;0,$A29,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N29&lt;0,$A29,""))</f>
         <v/>
       </c>
       <c r="P29" s="13">
-        <f>IF($H29&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B29&gt;0,'Условия'!$C$16&lt;&gt;"",$A29&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H29&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F29&gt;0.01,$A29&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A29='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A29-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -5692,63 +5755,64 @@
         <v>26</v>
       </c>
       <c r="B30" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A30,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A30,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A30)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A30))</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A30)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A30))</f>
         <v/>
       </c>
       <c r="E30" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D30/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D30&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D30-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D30/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D30&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D30-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F30" s="20">
-        <f>ROUND($E30-$E29,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E30-$E29,2))</f>
         <v/>
       </c>
       <c r="G30" s="20">
-        <f>ROUND($B30*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B30*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H30" s="20">
-        <f>ROUND($B30-$F30-$G30,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B30-$F30-$G30,2))</f>
         <v/>
       </c>
       <c r="I30" s="20">
-        <f>IF($A30='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A30='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J30" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A30-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A30-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K30" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A30='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A30='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A30-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L30" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A30+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A30=1,'Условия'!$C$20,0)+IF($A30='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A30+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A30=1,'Условия'!$C$20,0)+IF($A30='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M30" s="20">
-        <f>ROUND($I30+$J30+$K30-$L30,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I30+$J30+$K30-$L30,2))</f>
         <v/>
       </c>
       <c r="N30" s="20">
-        <f>ROUND($N29+$M30,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N29+$M30,2))</f>
         <v/>
       </c>
       <c r="O30" s="22">
-        <f>IF($N30&lt;0,$A30,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N30&lt;0,$A30,""))</f>
         <v/>
       </c>
       <c r="P30" s="13">
-        <f>IF($H30&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B30&gt;0,'Условия'!$C$16&lt;&gt;"",$A30&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H30&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F30&gt;0.01,$A30&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A30='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A30-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -5756,63 +5820,64 @@
         <v>27</v>
       </c>
       <c r="B31" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A31,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A31,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C31" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A31)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A31))</f>
         <v/>
       </c>
       <c r="D31" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A31)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A31))</f>
         <v/>
       </c>
       <c r="E31" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D31/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D31&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D31-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D31/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D31&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D31-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F31" s="20">
-        <f>ROUND($E31-$E30,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E31-$E30,2))</f>
         <v/>
       </c>
       <c r="G31" s="20">
-        <f>ROUND($B31*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B31*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H31" s="20">
-        <f>ROUND($B31-$F31-$G31,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B31-$F31-$G31,2))</f>
         <v/>
       </c>
       <c r="I31" s="20">
-        <f>IF($A31='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A31='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J31" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A31-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A31-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K31" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A31='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A31='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A31-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L31" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A31+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A31=1,'Условия'!$C$20,0)+IF($A31='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A31+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A31=1,'Условия'!$C$20,0)+IF($A31='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M31" s="20">
-        <f>ROUND($I31+$J31+$K31-$L31,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I31+$J31+$K31-$L31,2))</f>
         <v/>
       </c>
       <c r="N31" s="20">
-        <f>ROUND($N30+$M31,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N30+$M31,2))</f>
         <v/>
       </c>
       <c r="O31" s="22">
-        <f>IF($N31&lt;0,$A31,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N31&lt;0,$A31,""))</f>
         <v/>
       </c>
       <c r="P31" s="13">
-        <f>IF($H31&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B31&gt;0,'Условия'!$C$16&lt;&gt;"",$A31&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H31&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F31&gt;0.01,$A31&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A31='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A31-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -5820,63 +5885,64 @@
         <v>28</v>
       </c>
       <c r="B32" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A32,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A32,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A32)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A32))</f>
         <v/>
       </c>
       <c r="D32" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A32)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A32))</f>
         <v/>
       </c>
       <c r="E32" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D32/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D32&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D32-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D32/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D32&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D32-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F32" s="20">
-        <f>ROUND($E32-$E31,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E32-$E31,2))</f>
         <v/>
       </c>
       <c r="G32" s="20">
-        <f>ROUND($B32*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B32*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H32" s="20">
-        <f>ROUND($B32-$F32-$G32,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B32-$F32-$G32,2))</f>
         <v/>
       </c>
       <c r="I32" s="20">
-        <f>IF($A32='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A32='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J32" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A32-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A32-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K32" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A32='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A32='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A32-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L32" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A32+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A32=1,'Условия'!$C$20,0)+IF($A32='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A32+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A32=1,'Условия'!$C$20,0)+IF($A32='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M32" s="20">
-        <f>ROUND($I32+$J32+$K32-$L32,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I32+$J32+$K32-$L32,2))</f>
         <v/>
       </c>
       <c r="N32" s="20">
-        <f>ROUND($N31+$M32,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N31+$M32,2))</f>
         <v/>
       </c>
       <c r="O32" s="22">
-        <f>IF($N32&lt;0,$A32,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N32&lt;0,$A32,""))</f>
         <v/>
       </c>
       <c r="P32" s="13">
-        <f>IF($H32&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B32&gt;0,'Условия'!$C$16&lt;&gt;"",$A32&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H32&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F32&gt;0.01,$A32&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A32='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A32-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -5884,63 +5950,64 @@
         <v>29</v>
       </c>
       <c r="B33" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A33,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A33,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C33" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A33)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A33))</f>
         <v/>
       </c>
       <c r="D33" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A33)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A33))</f>
         <v/>
       </c>
       <c r="E33" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D33/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D33&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D33-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D33/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D33&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D33-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F33" s="20">
-        <f>ROUND($E33-$E32,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E33-$E32,2))</f>
         <v/>
       </c>
       <c r="G33" s="20">
-        <f>ROUND($B33*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B33*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H33" s="20">
-        <f>ROUND($B33-$F33-$G33,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B33-$F33-$G33,2))</f>
         <v/>
       </c>
       <c r="I33" s="20">
-        <f>IF($A33='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A33='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J33" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A33-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A33-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K33" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A33='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A33='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A33-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L33" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A33+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A33=1,'Условия'!$C$20,0)+IF($A33='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A33+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A33=1,'Условия'!$C$20,0)+IF($A33='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M33" s="20">
-        <f>ROUND($I33+$J33+$K33-$L33,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I33+$J33+$K33-$L33,2))</f>
         <v/>
       </c>
       <c r="N33" s="20">
-        <f>ROUND($N32+$M33,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N32+$M33,2))</f>
         <v/>
       </c>
       <c r="O33" s="22">
-        <f>IF($N33&lt;0,$A33,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N33&lt;0,$A33,""))</f>
         <v/>
       </c>
       <c r="P33" s="13">
-        <f>IF($H33&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B33&gt;0,'Условия'!$C$16&lt;&gt;"",$A33&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H33&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F33&gt;0.01,$A33&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A33='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A33-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -5948,63 +6015,64 @@
         <v>30</v>
       </c>
       <c r="B34" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A34,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A34,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C34" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A34)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A34))</f>
         <v/>
       </c>
       <c r="D34" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A34)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A34))</f>
         <v/>
       </c>
       <c r="E34" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D34/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D34&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D34-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D34/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D34&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D34-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F34" s="20">
-        <f>ROUND($E34-$E33,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E34-$E33,2))</f>
         <v/>
       </c>
       <c r="G34" s="20">
-        <f>ROUND($B34*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B34*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H34" s="20">
-        <f>ROUND($B34-$F34-$G34,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B34-$F34-$G34,2))</f>
         <v/>
       </c>
       <c r="I34" s="20">
-        <f>IF($A34='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A34='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J34" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A34-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A34-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K34" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A34='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A34='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A34-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L34" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A34+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A34=1,'Условия'!$C$20,0)+IF($A34='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A34+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A34=1,'Условия'!$C$20,0)+IF($A34='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M34" s="20">
-        <f>ROUND($I34+$J34+$K34-$L34,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I34+$J34+$K34-$L34,2))</f>
         <v/>
       </c>
       <c r="N34" s="20">
-        <f>ROUND($N33+$M34,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N33+$M34,2))</f>
         <v/>
       </c>
       <c r="O34" s="22">
-        <f>IF($N34&lt;0,$A34,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N34&lt;0,$A34,""))</f>
         <v/>
       </c>
       <c r="P34" s="13">
-        <f>IF($H34&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B34&gt;0,'Условия'!$C$16&lt;&gt;"",$A34&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H34&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F34&gt;0.01,$A34&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A34='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A34-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -6012,63 +6080,64 @@
         <v>31</v>
       </c>
       <c r="B35" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A35,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A35,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C35" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A35)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A35))</f>
         <v/>
       </c>
       <c r="D35" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A35)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A35))</f>
         <v/>
       </c>
       <c r="E35" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D35/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D35&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D35-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D35/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D35&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D35-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F35" s="20">
-        <f>ROUND($E35-$E34,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E35-$E34,2))</f>
         <v/>
       </c>
       <c r="G35" s="20">
-        <f>ROUND($B35*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B35*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H35" s="20">
-        <f>ROUND($B35-$F35-$G35,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B35-$F35-$G35,2))</f>
         <v/>
       </c>
       <c r="I35" s="20">
-        <f>IF($A35='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A35='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J35" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A35-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A35-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K35" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A35='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A35='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A35-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L35" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A35+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A35=1,'Условия'!$C$20,0)+IF($A35='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A35+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A35=1,'Условия'!$C$20,0)+IF($A35='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M35" s="20">
-        <f>ROUND($I35+$J35+$K35-$L35,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I35+$J35+$K35-$L35,2))</f>
         <v/>
       </c>
       <c r="N35" s="20">
-        <f>ROUND($N34+$M35,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N34+$M35,2))</f>
         <v/>
       </c>
       <c r="O35" s="22">
-        <f>IF($N35&lt;0,$A35,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N35&lt;0,$A35,""))</f>
         <v/>
       </c>
       <c r="P35" s="13">
-        <f>IF($H35&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B35&gt;0,'Условия'!$C$16&lt;&gt;"",$A35&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H35&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F35&gt;0.01,$A35&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A35='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A35-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -6076,63 +6145,64 @@
         <v>32</v>
       </c>
       <c r="B36" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A36,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A36,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C36" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A36)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A36))</f>
         <v/>
       </c>
       <c r="D36" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A36)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A36))</f>
         <v/>
       </c>
       <c r="E36" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D36/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D36&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D36-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D36/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D36&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D36-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F36" s="20">
-        <f>ROUND($E36-$E35,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E36-$E35,2))</f>
         <v/>
       </c>
       <c r="G36" s="20">
-        <f>ROUND($B36*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B36*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H36" s="20">
-        <f>ROUND($B36-$F36-$G36,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B36-$F36-$G36,2))</f>
         <v/>
       </c>
       <c r="I36" s="20">
-        <f>IF($A36='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A36='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J36" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A36-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A36-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K36" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A36='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A36='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A36-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L36" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A36+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A36=1,'Условия'!$C$20,0)+IF($A36='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A36+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A36=1,'Условия'!$C$20,0)+IF($A36='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M36" s="20">
-        <f>ROUND($I36+$J36+$K36-$L36,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I36+$J36+$K36-$L36,2))</f>
         <v/>
       </c>
       <c r="N36" s="20">
-        <f>ROUND($N35+$M36,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N35+$M36,2))</f>
         <v/>
       </c>
       <c r="O36" s="22">
-        <f>IF($N36&lt;0,$A36,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N36&lt;0,$A36,""))</f>
         <v/>
       </c>
       <c r="P36" s="13">
-        <f>IF($H36&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B36&gt;0,'Условия'!$C$16&lt;&gt;"",$A36&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H36&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F36&gt;0.01,$A36&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A36='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A36-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -6140,63 +6210,64 @@
         <v>33</v>
       </c>
       <c r="B37" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A37,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A37,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C37" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A37)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A37))</f>
         <v/>
       </c>
       <c r="D37" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A37)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A37))</f>
         <v/>
       </c>
       <c r="E37" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D37/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D37&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D37-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D37/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D37&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D37-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F37" s="20">
-        <f>ROUND($E37-$E36,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E37-$E36,2))</f>
         <v/>
       </c>
       <c r="G37" s="20">
-        <f>ROUND($B37*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B37*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H37" s="20">
-        <f>ROUND($B37-$F37-$G37,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B37-$F37-$G37,2))</f>
         <v/>
       </c>
       <c r="I37" s="20">
-        <f>IF($A37='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A37='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J37" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A37-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A37-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K37" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A37='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A37='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A37-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L37" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A37+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A37=1,'Условия'!$C$20,0)+IF($A37='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A37+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A37=1,'Условия'!$C$20,0)+IF($A37='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M37" s="20">
-        <f>ROUND($I37+$J37+$K37-$L37,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I37+$J37+$K37-$L37,2))</f>
         <v/>
       </c>
       <c r="N37" s="20">
-        <f>ROUND($N36+$M37,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N36+$M37,2))</f>
         <v/>
       </c>
       <c r="O37" s="22">
-        <f>IF($N37&lt;0,$A37,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N37&lt;0,$A37,""))</f>
         <v/>
       </c>
       <c r="P37" s="13">
-        <f>IF($H37&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B37&gt;0,'Условия'!$C$16&lt;&gt;"",$A37&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H37&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F37&gt;0.01,$A37&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A37='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A37-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -6204,63 +6275,64 @@
         <v>34</v>
       </c>
       <c r="B38" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A38,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A38,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C38" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A38)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A38))</f>
         <v/>
       </c>
       <c r="D38" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A38)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A38))</f>
         <v/>
       </c>
       <c r="E38" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D38/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D38&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D38-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D38/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D38&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D38-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F38" s="20">
-        <f>ROUND($E38-$E37,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E38-$E37,2))</f>
         <v/>
       </c>
       <c r="G38" s="20">
-        <f>ROUND($B38*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B38*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H38" s="20">
-        <f>ROUND($B38-$F38-$G38,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B38-$F38-$G38,2))</f>
         <v/>
       </c>
       <c r="I38" s="20">
-        <f>IF($A38='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A38='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J38" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A38-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A38-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K38" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A38='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A38='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A38-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L38" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A38+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A38=1,'Условия'!$C$20,0)+IF($A38='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A38+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A38=1,'Условия'!$C$20,0)+IF($A38='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M38" s="20">
-        <f>ROUND($I38+$J38+$K38-$L38,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I38+$J38+$K38-$L38,2))</f>
         <v/>
       </c>
       <c r="N38" s="20">
-        <f>ROUND($N37+$M38,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N37+$M38,2))</f>
         <v/>
       </c>
       <c r="O38" s="22">
-        <f>IF($N38&lt;0,$A38,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N38&lt;0,$A38,""))</f>
         <v/>
       </c>
       <c r="P38" s="13">
-        <f>IF($H38&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B38&gt;0,'Условия'!$C$16&lt;&gt;"",$A38&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H38&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F38&gt;0.01,$A38&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A38='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A38-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -6268,63 +6340,64 @@
         <v>35</v>
       </c>
       <c r="B39" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A39,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A39,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C39" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A39)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A39))</f>
         <v/>
       </c>
       <c r="D39" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A39)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A39))</f>
         <v/>
       </c>
       <c r="E39" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D39/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D39&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D39-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D39/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D39&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D39-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F39" s="20">
-        <f>ROUND($E39-$E38,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E39-$E38,2))</f>
         <v/>
       </c>
       <c r="G39" s="20">
-        <f>ROUND($B39*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B39*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H39" s="20">
-        <f>ROUND($B39-$F39-$G39,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B39-$F39-$G39,2))</f>
         <v/>
       </c>
       <c r="I39" s="20">
-        <f>IF($A39='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A39='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J39" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A39-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A39-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K39" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A39='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A39='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A39-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L39" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A39+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A39=1,'Условия'!$C$20,0)+IF($A39='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A39+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A39=1,'Условия'!$C$20,0)+IF($A39='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M39" s="20">
-        <f>ROUND($I39+$J39+$K39-$L39,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I39+$J39+$K39-$L39,2))</f>
         <v/>
       </c>
       <c r="N39" s="20">
-        <f>ROUND($N38+$M39,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N38+$M39,2))</f>
         <v/>
       </c>
       <c r="O39" s="22">
-        <f>IF($N39&lt;0,$A39,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N39&lt;0,$A39,""))</f>
         <v/>
       </c>
       <c r="P39" s="13">
-        <f>IF($H39&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B39&gt;0,'Условия'!$C$16&lt;&gt;"",$A39&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H39&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F39&gt;0.01,$A39&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A39='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A39-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -6332,63 +6405,64 @@
         <v>36</v>
       </c>
       <c r="B40" s="20">
-        <f>ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A40,'График КС'!$A$5:$A$40,0))/100,0),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR('Условия'!$C$5*INDEX('График КС'!$C$5:$C$40,MATCH($A40,'График КС'!$A$5:$A$40,0))/100,0),2))</f>
         <v/>
       </c>
       <c r="C40" s="20">
-        <f>SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A40)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS($B$5:$B$40,$A$5:$A$40,"&lt;="&amp;$A40))</f>
         <v/>
       </c>
       <c r="D40" s="21">
-        <f>SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A40)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",SUMIFS('График КС'!$C$5:$C$40,'График КС'!$A$5:$A$40,"&lt;="&amp;$A40))</f>
         <v/>
       </c>
       <c r="E40" s="20">
-        <f>IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D40/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D40&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D40-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF('Условия'!$C$25=0,0,IFERROR(MAX(0,MIN('Условия'!$C$23,IF('Условия'!$C$25=1,ROUND('Условия'!$C$23*$D40/'График КС'!$C$42,2),IF('Условия'!$C$25=2,IF($D40&gt;='График КС'!$C$42,'Условия'!$C$23,0),ROUND('Условия'!$C$23*($D40-'Условия'!$C$9)/('График КС'!$C$42-'Условия'!$C$9),2))))),0)))</f>
         <v/>
       </c>
       <c r="F40" s="20">
-        <f>ROUND($E40-$E39,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($E40-$E39,2))</f>
         <v/>
       </c>
       <c r="G40" s="20">
-        <f>ROUND($B40*'Условия'!$C$13/100,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B40*'Условия'!$C$13/100,2))</f>
         <v/>
       </c>
       <c r="H40" s="20">
-        <f>ROUND($B40-$F40-$G40,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($B40-$F40-$G40,2))</f>
         <v/>
       </c>
       <c r="I40" s="20">
-        <f>IF($A40='Условия'!$C$7,'Условия'!$C$23,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($A40='Условия'!$C$7,'Условия'!$C$23,0))</f>
         <v/>
       </c>
       <c r="J40" s="20">
-        <f>IFERROR(INDEX($H$5:$H$40,MATCH($A40-'Условия'!$C$17,$A$5:$A$40,0)),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IFERROR(INDEX($H$5:$H$40,MATCH($A40-'Условия'!$C$17,$A$5:$A$40,0)),0))</f>
         <v/>
       </c>
       <c r="K40" s="20">
-        <f>IF(AND('Условия'!$C$14&gt;0,$A40='Условия'!$C$14),ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A40='Условия'!$C$14),ROUND(MIN(ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2),SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A40-'Условия'!$C$17))),2),0))</f>
         <v/>
       </c>
       <c r="L40" s="20">
-        <f>ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A40+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A40=1,'Условия'!$C$20,0)+IF($A40='Условия'!$C$12,'Условия'!$C$24,0)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(IFERROR(INDEX($B$5:$B$40,MATCH($A40+'Условия'!$C$19,$A$5:$A$40,0)),0)*'Условия'!$C$18/100,2)+IF($A40=1,'Условия'!$C$20,0)+IF($A40='Условия'!$C$12,'Условия'!$C$24,0))</f>
         <v/>
       </c>
       <c r="M40" s="20">
-        <f>ROUND($I40+$J40+$K40-$L40,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($I40+$J40+$K40-$L40,2))</f>
         <v/>
       </c>
       <c r="N40" s="20">
-        <f>ROUND($N39+$M40,2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND($N39+$M40,2))</f>
         <v/>
       </c>
       <c r="O40" s="22">
-        <f>IF($N40&lt;0,$A40,"")</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($N40&lt;0,$A40,""))</f>
         <v/>
       </c>
       <c r="P40" s="13">
-        <f>IF($H40&lt;0,"Погашение аванса и гарантийное удержание превышают стоимость работ данного месяца.",IF(AND($B40&gt;0,'Условия'!$C$16&lt;&gt;"",$A40&gt;'Условия'!$C$16),"Объём работ указан за пределами срока выполнения: сверьте график и условия.",""))</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",IF($H40&lt;-0.01,"ОШИБКА: погашение и удержание больше стоимости КС",IF(AND($F40&gt;0.01,$A40&lt;'Условия'!$C$7),"ОШИБКА: аванс погашается до поступления",IF(AND('Условия'!$C$13&gt;0,'Условия'!$C$14&gt;0,$A40='Условия'!$C$14,ROUND(SUM($G$5:$G$40)*'Условия'!$C$15/100,2)&gt;SUMIFS($G$5:$G$40,$A$5:$A$40,"&lt;="&amp;($A40-'Условия'!$C$17))+0.01),"ОШИБКА: возврат больше накопленного удержания",""))))</f>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -6398,43 +6472,43 @@
         </is>
       </c>
       <c r="B42" s="23">
-        <f>ROUND(SUM($B$5:$B$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($B$5:$B$40),2))</f>
         <v/>
       </c>
       <c r="F42" s="23">
-        <f>ROUND(SUM($F$5:$F$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($F$5:$F$40),2))</f>
         <v/>
       </c>
       <c r="G42" s="23">
-        <f>ROUND(SUM($G$5:$G$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($G$5:$G$40),2))</f>
         <v/>
       </c>
       <c r="H42" s="23">
-        <f>ROUND(SUM($H$5:$H$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($H$5:$H$40),2))</f>
         <v/>
       </c>
       <c r="I42" s="23">
-        <f>ROUND(SUM($I$5:$I$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($I$5:$I$40),2))</f>
         <v/>
       </c>
       <c r="J42" s="23">
-        <f>ROUND(SUM($J$5:$J$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($J$5:$J$40),2))</f>
         <v/>
       </c>
       <c r="K42" s="23">
-        <f>ROUND(SUM($K$5:$K$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($K$5:$K$40),2))</f>
         <v/>
       </c>
       <c r="L42" s="23">
-        <f>ROUND(SUM($L$5:$L$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($L$5:$L$40),2))</f>
         <v/>
       </c>
       <c r="M42" s="23">
-        <f>ROUND(SUM($M$5:$M$40),2)</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",ROUND(SUM($M$5:$M$40),2))</f>
         <v/>
       </c>
       <c r="N42" s="23">
-        <f>$N$40</f>
+        <f>IF('Условия'!$C$26&lt;&gt;"Условия заполнены","",$N$40)</f>
         <v/>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -6478,7 +6552,7 @@
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сопоставьте максимальную потребность в финансировании, срок отрицательного остатка и стоимость обеспечения. Изменение условий оценивайте по совокупности этих показателей.</t>
+          <t>Сначала проверьте готовность каждого сценария в строке 18. При неполных условиях или противоречиях профиля его денежные итоги не выводятся. Сравнивайте финансирование, обеспечение и конечный остаток, а не только размер аванса.</t>
         </is>
       </c>
     </row>
@@ -6516,15 +6590,15 @@
         </is>
       </c>
       <c r="B5" s="24">
-        <f>'Профиль А'!$I$42</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",'Профиль А'!$I$42)</f>
         <v/>
       </c>
       <c r="C5" s="24">
-        <f>'Профиль Б'!$I$42</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",'Профиль Б'!$I$42)</f>
         <v/>
       </c>
       <c r="D5" s="23">
-        <f>ROUND($C5-$B5,2)</f>
+        <f>IF(OR(NOT(ISNUMBER(B5)),NOT(ISNUMBER(C5))),"",ROUND(C5-B5,2))</f>
         <v/>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6540,15 +6614,15 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>'Условия'!$B$24</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",'Условия'!$B$24)</f>
         <v/>
       </c>
       <c r="C6" s="24">
-        <f>'Условия'!$C$24</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",'Условия'!$C$24)</f>
         <v/>
       </c>
       <c r="D6" s="23">
-        <f>ROUND($C6-$B6,2)</f>
+        <f>IF(OR(NOT(ISNUMBER(B6)),NOT(ISNUMBER(C6))),"",ROUND(C6-B6,2))</f>
         <v/>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6564,20 +6638,20 @@
         </is>
       </c>
       <c r="B7" s="24">
-        <f>IF(MIN('Профиль А'!$N$5:$N$40)&lt;0,-MIN('Профиль А'!$N$5:$N$40),0)</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",IF(MIN('Профиль А'!$N$5:$N$40)&lt;0,-MIN('Профиль А'!$N$5:$N$40),0))</f>
         <v/>
       </c>
       <c r="C7" s="24">
-        <f>IF(MIN('Профиль Б'!$N$5:$N$40)&lt;0,-MIN('Профиль Б'!$N$5:$N$40),0)</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",IF(MIN('Профиль Б'!$N$5:$N$40)&lt;0,-MIN('Профиль Б'!$N$5:$N$40),0))</f>
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>ROUND($C7-$B7,2)</f>
+        <f>IF(OR(NOT(ISNUMBER(B7)),NOT(ISNUMBER(C7))),"",ROUND(C7-B7,2))</f>
         <v/>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Наибольший отрицательный накопленный остаток. Определяет требуемый объём собственных или заёмных средств.</t>
+          <t>Максимальный отрицательный остаток по итогам месяцев. Внутримесячные кассовые разрывы проверяйте отдельно.</t>
         </is>
       </c>
     </row>
@@ -6588,10 +6662,12 @@
         </is>
       </c>
       <c r="B8" s="25">
-        <f>IF(MIN('Профиль А'!$N$5:$N$40)&lt;0,INDEX('Профиль А'!$A$5:$A$40,MATCH(MIN('Профиль А'!$N$5:$N$40),'Профиль А'!$N$5:$N$40,0)),"Отсутствует")</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",IF(MIN('Профиль А'!$N$5:$N$40)&lt;0,INDEX('Профиль А'!$A$5:$A$40,MATCH(MIN('Профиль А'!$N$5:$N$40),'Профиль А'!$N$5:$N$40,0)),"Отсутствует"))</f>
+        <v/>
       </c>
       <c r="C8" s="25">
-        <f>IF(MIN('Профиль Б'!$N$5:$N$40)&lt;0,INDEX('Профиль Б'!$A$5:$A$40,MATCH(MIN('Профиль Б'!$N$5:$N$40),'Профиль Б'!$N$5:$N$40,0)),"Отсутствует")</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",IF(MIN('Профиль Б'!$N$5:$N$40)&lt;0,INDEX('Профиль Б'!$A$5:$A$40,MATCH(MIN('Профиль Б'!$N$5:$N$40),'Профиль Б'!$N$5:$N$40,0)),"Отсутствует"))</f>
+        <v/>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
@@ -6611,10 +6687,12 @@
         </is>
       </c>
       <c r="B9" s="25">
-        <f>IF(COUNT('Профиль А'!$O$5:$O$40)=0,"Отсутствует",MIN('Профиль А'!$O$5:$O$40))</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",IF(COUNT('Профиль А'!$O$5:$O$40)=0,"Отсутствует",MIN('Профиль А'!$O$5:$O$40)))</f>
+        <v/>
       </c>
       <c r="C9" s="25">
-        <f>IF(COUNT('Профиль Б'!$O$5:$O$40)=0,"Отсутствует",MIN('Профиль Б'!$O$5:$O$40))</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",IF(COUNT('Профиль Б'!$O$5:$O$40)=0,"Отсутствует",MIN('Профиль Б'!$O$5:$O$40)))</f>
+        <v/>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
@@ -6634,11 +6712,11 @@
         </is>
       </c>
       <c r="B10" s="25">
-        <f>SUMPRODUCT(('Профиль А'!$N$5:$N$40&lt;0)*('Профиль А'!$A$5:$A$40&lt;&gt;""))</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",COUNTIF('Профиль А'!$N$5:$N$40,"&lt;0"))</f>
         <v/>
       </c>
       <c r="C10" s="25">
-        <f>SUMPRODUCT(('Профиль Б'!$N$5:$N$40&lt;0)*('Профиль Б'!$A$5:$A$40&lt;&gt;""))</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",COUNTIF('Профиль Б'!$N$5:$N$40,"&lt;0"))</f>
         <v/>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -6659,20 +6737,20 @@
         </is>
       </c>
       <c r="B11" s="24">
-        <f>'Профиль А'!$F$42</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",'Профиль А'!$F$42)</f>
         <v/>
       </c>
       <c r="C11" s="24">
-        <f>'Профиль Б'!$F$42</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",'Профиль Б'!$F$42)</f>
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>ROUND($C11-$B11,2)</f>
+        <f>IF(OR(NOT(ISNUMBER(B11)),NOT(ISNUMBER(C11))),"",ROUND(C11-B11,2))</f>
         <v/>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>К концу горизонта должно совпасть с полученным авансом. Если меньше — часть погашения приходится на месяцы за горизонтом расчёта.</t>
+          <t>Полученный аванс должен быть погашен по графику. Данная модель не допускает погашения раньше получения.</t>
         </is>
       </c>
     </row>
@@ -6683,20 +6761,20 @@
         </is>
       </c>
       <c r="B12" s="24">
-        <f>ROUND('Профиль А'!$G$42-'Профиль А'!$K$42,2)</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",ROUND('Профиль А'!$G$42-'Профиль А'!$K$42,2))</f>
         <v/>
       </c>
       <c r="C12" s="24">
-        <f>ROUND('Профиль Б'!$G$42-'Профиль Б'!$K$42,2)</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",ROUND('Профиль Б'!$G$42-'Профиль Б'!$K$42,2))</f>
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>ROUND($C12-$B12,2)</f>
+        <f>IF(OR(NOT(ISNUMBER(B12)),NOT(ISNUMBER(C12))),"",ROUND(C12-B12,2))</f>
         <v/>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Гарантийное удержание, не возвращённое до конца расчётного периода.</t>
+          <t>Начисленное по КС удержание минус возврат. Досрочный возврат будущих удержаний блокирует сравнение.</t>
         </is>
       </c>
     </row>
@@ -6707,15 +6785,15 @@
         </is>
       </c>
       <c r="B13" s="24">
-        <f>ROUND('Профиль А'!$H$42-'Профиль А'!$J$42,2)</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",ROUND('Профиль А'!$H$42-'Профиль А'!$J$42,2))</f>
         <v/>
       </c>
       <c r="C13" s="24">
-        <f>ROUND('Профиль Б'!$H$42-'Профиль Б'!$J$42,2)</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",ROUND('Профиль Б'!$H$42-'Профиль Б'!$J$42,2))</f>
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>ROUND($C13-$B13,2)</f>
+        <f>IF(OR(NOT(ISNUMBER(B13)),NOT(ISNUMBER(C13))),"",ROUND(C13-B13,2))</f>
         <v/>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -6731,15 +6809,15 @@
         </is>
       </c>
       <c r="B14" s="24">
-        <f>'Профиль А'!$L$42</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",'Профиль А'!$L$42)</f>
         <v/>
       </c>
       <c r="C14" s="24">
-        <f>'Профиль Б'!$L$42</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",'Профиль Б'!$L$42)</f>
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>ROUND($C14-$B14,2)</f>
+        <f>IF(OR(NOT(ISNUMBER(B14)),NOT(ISNUMBER(C14))),"",ROUND(C14-B14,2))</f>
         <v/>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6755,15 +6833,15 @@
         </is>
       </c>
       <c r="B15" s="24">
-        <f>'Профиль А'!$N$42</f>
+        <f>IF(B$18&lt;&gt;"Готово к сравнению","",'Профиль А'!$N$42)</f>
         <v/>
       </c>
       <c r="C15" s="24">
-        <f>'Профиль Б'!$N$42</f>
+        <f>IF(C$18&lt;&gt;"Готово к сравнению","",'Профиль Б'!$N$42)</f>
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>ROUND($C15-$B15,2)</f>
+        <f>IF(OR(NOT(ISNUMBER(B15)),NOT(ISNUMBER(C15))),"",ROUND(C15-B15,2))</f>
         <v/>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -6779,7 +6857,23 @@
         </is>
       </c>
       <c r="B17" s="26">
-        <f>IF(OR($B7="",$C7=""),"",IF(ROUND($C7-$B7,2)&lt;0,"Сценарий Б снижает максимальную потребность в финансировании.",IF(ROUND($C7-$B7,2)&gt;0,"Сценарий Б увеличивает максимальную потребность в финансировании.","Максимальная потребность в финансировании одинакова.")))</f>
+        <f>IF(OR(NOT(ISNUMBER(B7)),NOT(ISNUMBER(C7))),"Сравнение не завершено: проверьте условия и профили",IF(C7&lt;B7,"Сценарий Б снижает потребность в финансировании",IF(C7&gt;B7,"Сценарий Б увеличивает потребность в финансировании","Потребность в финансировании одинакова")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Контроль готовности</t>
+        </is>
+      </c>
+      <c r="B18" s="13">
+        <f>IF('Условия'!B26&lt;&gt;"Условия заполнены","Проверьте условия",IF(COUNTIF('Профиль А'!P5:P40,"ОШИБКА: погашение и удержание больше стоимости КС")+COUNTIF('Профиль А'!P5:P40,"ОШИБКА: аванс погашается до поступления")+COUNTIF('Профиль А'!P5:P40,"ОШИБКА: возврат больше накопленного удержания")&gt;0,"Проверьте профиль","Готово к сравнению"))</f>
+        <v/>
+      </c>
+      <c r="C18" s="13">
+        <f>IF('Условия'!C26&lt;&gt;"Условия заполнены","Проверьте условия",IF(COUNTIF('Профиль Б'!P5:P40,"ОШИБКА: погашение и удержание больше стоимости КС")+COUNTIF('Профиль Б'!P5:P40,"ОШИБКА: аванс погашается до поступления")+COUNTIF('Профиль Б'!P5:P40,"ОШИБКА: возврат больше накопленного удержания")&gt;0,"Проверьте профиль","Готово к сравнению"))</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -6859,7 +6953,7 @@
       </c>
       <c r="B3" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Внесите в сценарий А условия предложенного проекта договора или подписанного договора.</t>
+          <t>Заполните числовые условия А и Б. При отсутствии расходов в обязательных полях укажите 0; неизвестную сумму не подменяйте нулём.</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6989,7 @@
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">На листе «Сравнение» проверьте максимальную потребность в финансировании и месяц её возникновения. Сопоставьте их со стоимостью обеспечения.</t>
+          <t>На «Сравнение» сначала проверьте строку 18. При ошибке условий откройте строку 26 «Условия», при ошибке профиля — колонку P.</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7094,7 @@
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>После заполнения проверьте итоговые строки в Excel или LibreOffice; при переносе файла сохраните формулы и исходные данные.</t>
+          <t>Редакция для проверки 22.10.2026. Введите данные, сохраните XLSX, повторно откройте и проверьте пересчёт. Печатный вид проверяется в Excel.</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7108,7 @@
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сравните сценарии с авансом и без него. Отдельно рассчитайте стоимость финансирования по сумме, ставке и периоду привлечения средств. Решение принимайте с учётом ликвидности, комиссии за обеспечение и совокупных расходов.</t>
+          <t>Расчёт помесячный, не определяет прибыль и внутримесячный пик. Налоги и стоимость финансирования учитывайте отдельно. Помощь: nastoronepodryadchika@yandex.ru.</t>
         </is>
       </c>
     </row>
@@ -7046,14 +7140,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Пример: как выглядят заполненные условия</t>
+          <t>Контрольный пример: аванс 20% / без аванса</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Учебный пример показывает формат исходных данных. Для рабочего расчёта используйте условия своего договора, график выполнения и предложение банка.</t>
+          <t>Все числа учебные. Перенесите значения в лист «Условия», а на «График КС» укажите по 50 в первом и втором месяцах обоих сценариев. Пустые остальные месяцы означают отсутствие работ.</t>
         </is>
       </c>
     </row>
@@ -7080,15 +7174,11 @@
           <t>Сумма договора, руб.</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
-        <is>
-          <t>10 000 000,00</t>
-        </is>
-      </c>
-      <c r="C5" s="30" t="inlineStr">
-        <is>
-          <t>10 000 000,00</t>
-        </is>
+      <c r="B5" s="30" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="6">
@@ -7097,15 +7187,11 @@
           <t>Размер аванса, % от суммы договора</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="B6" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7114,18 +7200,14 @@
           <t>Месяц поступления аванса</t>
         </is>
       </c>
-      <c r="B7" s="30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" s="30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+      <c r="B7" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Порядок погашения аванса</t>
@@ -7138,7 +7220,7 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>пропорционально из каждой КС</t>
         </is>
       </c>
     </row>
@@ -7148,15 +7230,11 @@
           <t>Доля выполнения, с которой начинается погашение, %</t>
         </is>
       </c>
-      <c r="B9" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B9" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -7165,15 +7243,11 @@
           <t>Ставка обеспечения аванса, % годовых</t>
         </is>
       </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>из предложения банка</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="B10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -7182,15 +7256,11 @@
           <t>Срок действия обеспечения, мес.</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C11" s="30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B11" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7199,15 +7269,11 @@
           <t>Месяц оплаты обеспечения</t>
         </is>
       </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B12" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7216,15 +7282,11 @@
           <t>Гарантийное удержание, % от каждой КС</t>
         </is>
       </c>
-      <c r="B13" s="30" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="B13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7233,15 +7295,11 @@
           <t>Месяц возврата гарантийного удержания</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C14" s="30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="B14" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -7250,15 +7308,11 @@
           <t>Доля возвращаемого удержания, %</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
-      </c>
-      <c r="C15" s="30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="B15" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -7267,15 +7321,11 @@
           <t>Срок объекта, мес.</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="B16" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -7284,15 +7334,11 @@
           <t>Отсрочка оплаты КС, мес.</t>
         </is>
       </c>
-      <c r="B17" s="30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C17" s="30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -7301,15 +7347,11 @@
           <t>Себестоимость работ, % от суммы договора</t>
         </is>
       </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>80,00</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="inlineStr">
-        <is>
-          <t>80,00</t>
-        </is>
+      <c r="B18" s="30" t="n">
+        <v>80</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -7318,15 +7360,11 @@
           <t>Опережение расходов, мес.</t>
         </is>
       </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -7335,15 +7373,11 @@
           <t>Стартовые затраты до первой КС, руб.</t>
         </is>
       </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>500 000,00</t>
-        </is>
-      </c>
-      <c r="C20" s="30" t="inlineStr">
-        <is>
-          <t>500 000,00</t>
-        </is>
+      <c r="B20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -7356,7 +7390,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Десять месяцев по 10% в каждом, колонки А и Б одинаковые: сравниваются условия аванса, а не график.</t>
+          <t>Первый и второй месяцы: по 50% в каждом сценарии. Остальные месяцы — пусто или 0. Не копируйте формулы из расчётных листов в поля ввода.</t>
         </is>
       </c>
     </row>
@@ -7367,10 +7401,10 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
+    <row r="26" ht="72" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Сценарий А использует аванс в первом месяце; сценарий Б показывает финансирование собственными средствами. Сравните максимальный отрицательный остаток и стоимость обеспечения на ваших данных.</t>
+          <t>Ожидается: финансирование А 20 000 ₽, Б 40 000 ₽; расходы обоих 80 000 ₽; конечный остаток обоих 20 000 ₽. Без аванса можно не выбирать порядок погашения. Данные примера не являются ставками банка или условиями вашего договора.</t>
         </is>
       </c>
     </row>
